--- a/Design-Files/OFP_MCM_v1.5/BOM/eSpark-BOM-OFP_MCM_v1.5.xlsx
+++ b/Design-Files/OFP_MCM_v1.5/BOM/eSpark-BOM-OFP_MCM_v1.5.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="10 Boards" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3088" uniqueCount="879">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3113" uniqueCount="884">
   <si>
     <t>Component list</t>
   </si>
@@ -2657,6 +2657,21 @@
   </si>
   <si>
     <t>1.0434</t>
+  </si>
+  <si>
+    <t>RC0603FR-0730KL</t>
+  </si>
+  <si>
+    <t>FPC FFC Flexible Flat Cable Extension Board PCB Pitch 0.5 mm (40 Pin) Connector</t>
+  </si>
+  <si>
+    <t>CA-2660</t>
+  </si>
+  <si>
+    <t>RZCONNE</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
   </si>
 </sst>
 </file>
@@ -3034,7 +3049,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3139,21 +3154,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3182,6 +3183,17 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3471,7 +3483,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R150"/>
+  <dimension ref="A1:R151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4" style="10" bestFit="1" customWidth="1"/>
@@ -3505,14 +3517,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1">
       <c r="A2" s="1"/>
@@ -3719,7 +3731,7 @@
       <c r="N8" s="14">
         <v>60</v>
       </c>
-      <c r="O8" s="54" t="s">
+      <c r="O8" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P8" s="15" t="s">
@@ -3734,7 +3746,7 @@
     <row r="9" spans="1:18" ht="24">
       <c r="A9" s="1"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B136" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B137" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
@@ -3774,7 +3786,7 @@
       <c r="N9" s="20">
         <v>102</v>
       </c>
-      <c r="O9" s="54" t="s">
+      <c r="O9" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P9" s="21" t="s">
@@ -3829,7 +3841,7 @@
       <c r="N10" s="14">
         <v>130</v>
       </c>
-      <c r="O10" s="54" t="s">
+      <c r="O10" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P10" s="15" t="s">
@@ -3884,7 +3896,7 @@
       <c r="N11" s="20">
         <v>400</v>
       </c>
-      <c r="O11" s="54" t="s">
+      <c r="O11" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P11" s="21" t="s">
@@ -3939,7 +3951,7 @@
       <c r="N12" s="14">
         <v>11</v>
       </c>
-      <c r="O12" s="54" t="s">
+      <c r="O12" s="50" t="s">
         <v>793</v>
       </c>
       <c r="P12" s="15">
@@ -3994,7 +4006,7 @@
       <c r="N13" s="20" t="s">
         <v>785</v>
       </c>
-      <c r="O13" s="54" t="s">
+      <c r="O13" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P13" s="21" t="s">
@@ -4049,7 +4061,7 @@
       <c r="N14" s="14" t="s">
         <v>786</v>
       </c>
-      <c r="O14" s="54" t="s">
+      <c r="O14" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P14" s="15" t="s">
@@ -4104,7 +4116,7 @@
       <c r="N15" s="20" t="s">
         <v>786</v>
       </c>
-      <c r="O15" s="54" t="s">
+      <c r="O15" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P15" s="21" t="s">
@@ -4159,7 +4171,7 @@
       <c r="N16" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O16" s="54" t="s">
+      <c r="O16" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P16" s="15" t="s">
@@ -4214,7 +4226,7 @@
       <c r="N17" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O17" s="54" t="s">
+      <c r="O17" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P17" s="21" t="s">
@@ -4269,7 +4281,7 @@
       <c r="N18" s="14">
         <v>95</v>
       </c>
-      <c r="O18" s="54" t="s">
+      <c r="O18" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P18" s="15" t="s">
@@ -4324,7 +4336,7 @@
       <c r="N19" s="20">
         <v>25</v>
       </c>
-      <c r="O19" s="54" t="s">
+      <c r="O19" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P19" s="21" t="s">
@@ -4379,7 +4391,7 @@
       <c r="N20" s="14">
         <v>40</v>
       </c>
-      <c r="O20" s="54" t="s">
+      <c r="O20" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P20" s="15" t="s">
@@ -4434,7 +4446,7 @@
       <c r="N21" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O21" s="54" t="s">
+      <c r="O21" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P21" s="21" t="s">
@@ -4489,7 +4501,7 @@
       <c r="N22" s="14">
         <v>20</v>
       </c>
-      <c r="O22" s="54" t="s">
+      <c r="O22" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P22" s="15" t="s">
@@ -4544,7 +4556,7 @@
       <c r="N23" s="20">
         <v>85</v>
       </c>
-      <c r="O23" s="54" t="s">
+      <c r="O23" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P23" s="21" t="s">
@@ -4599,7 +4611,7 @@
       <c r="N24" s="14">
         <v>100</v>
       </c>
-      <c r="O24" s="54" t="s">
+      <c r="O24" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P24" s="15" t="s">
@@ -4654,7 +4666,7 @@
       <c r="N25" s="20">
         <v>20</v>
       </c>
-      <c r="O25" s="54" t="s">
+      <c r="O25" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P25" s="21" t="s">
@@ -4709,7 +4721,7 @@
       <c r="N26" s="14" t="s">
         <v>783</v>
       </c>
-      <c r="O26" s="54" t="s">
+      <c r="O26" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P26" s="15" t="s">
@@ -4764,7 +4776,7 @@
       <c r="N27" s="20" t="s">
         <v>786</v>
       </c>
-      <c r="O27" s="54" t="s">
+      <c r="O27" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P27" s="21" t="s">
@@ -4819,7 +4831,7 @@
       <c r="N28" s="14" t="s">
         <v>783</v>
       </c>
-      <c r="O28" s="54" t="s">
+      <c r="O28" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P28" s="15" t="s">
@@ -4874,7 +4886,7 @@
       <c r="N29" s="20" t="s">
         <v>787</v>
       </c>
-      <c r="O29" s="54" t="s">
+      <c r="O29" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P29" s="21" t="s">
@@ -4929,7 +4941,7 @@
       <c r="N30" s="14">
         <v>25</v>
       </c>
-      <c r="O30" s="54" t="s">
+      <c r="O30" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P30" s="15" t="s">
@@ -4984,7 +4996,7 @@
       <c r="N31" s="20" t="s">
         <v>786</v>
       </c>
-      <c r="O31" s="54" t="s">
+      <c r="O31" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P31" s="21" t="s">
@@ -5039,7 +5051,7 @@
       <c r="N32" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O32" s="54" t="s">
+      <c r="O32" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P32" s="15" t="s">
@@ -5094,7 +5106,7 @@
       <c r="N33" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O33" s="54" t="s">
+      <c r="O33" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P33" s="21" t="s">
@@ -5149,7 +5161,7 @@
       <c r="N34" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O34" s="54" t="s">
+      <c r="O34" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P34" s="15" t="s">
@@ -5204,7 +5216,7 @@
       <c r="N35" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O35" s="54" t="s">
+      <c r="O35" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P35" s="21" t="s">
@@ -5259,7 +5271,7 @@
       <c r="N36" s="14" t="s">
         <v>787</v>
       </c>
-      <c r="O36" s="54" t="s">
+      <c r="O36" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P36" s="15" t="s">
@@ -5280,50 +5292,50 @@
       <c r="C37" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D37" s="50" t="s">
+      <c r="D37" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="50" t="s">
+      <c r="E37" s="46" t="s">
         <v>186</v>
       </c>
-      <c r="F37" s="50" t="s">
+      <c r="F37" s="46" t="s">
         <v>280</v>
       </c>
-      <c r="G37" s="50" t="s">
+      <c r="G37" s="46" t="s">
         <v>356</v>
       </c>
-      <c r="H37" s="50" t="s">
+      <c r="H37" s="46" t="s">
         <v>435</v>
       </c>
-      <c r="I37" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J37" s="50" t="s">
+      <c r="I37" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J37" s="46" t="s">
         <v>498</v>
       </c>
-      <c r="K37" s="50" t="s">
+      <c r="K37" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L37" s="50">
+      <c r="L37" s="46">
         <v>7</v>
       </c>
-      <c r="M37" s="45">
+      <c r="M37" s="42">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="N37" s="50" t="s">
+      <c r="N37" s="46" t="s">
         <v>789</v>
       </c>
-      <c r="O37" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P37" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q37" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R37" s="53" t="s">
+      <c r="O37" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P37" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q37" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R37" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -5336,50 +5348,50 @@
       <c r="C38" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="45" t="s">
+      <c r="D38" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="45" t="s">
+      <c r="E38" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="F38" s="45" t="s">
+      <c r="F38" s="42" t="s">
         <v>281</v>
       </c>
-      <c r="G38" s="45" t="s">
+      <c r="G38" s="42" t="s">
         <v>332</v>
       </c>
-      <c r="H38" s="45" t="s">
+      <c r="H38" s="42" t="s">
         <v>435</v>
       </c>
-      <c r="I38" s="45" t="s">
-        <v>672</v>
-      </c>
-      <c r="J38" s="45" t="s">
+      <c r="I38" s="42" t="s">
+        <v>672</v>
+      </c>
+      <c r="J38" s="42" t="s">
         <v>476</v>
       </c>
-      <c r="K38" s="45" t="s">
+      <c r="K38" s="42" t="s">
         <v>609</v>
       </c>
-      <c r="L38" s="45">
+      <c r="L38" s="42">
         <v>1</v>
       </c>
-      <c r="M38" s="45">
+      <c r="M38" s="42">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N38" s="45" t="s">
+      <c r="N38" s="42" t="s">
         <v>786</v>
       </c>
-      <c r="O38" s="55" t="s">
-        <v>672</v>
-      </c>
-      <c r="P38" s="52" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q38" s="52" t="s">
-        <v>672</v>
-      </c>
-      <c r="R38" s="53" t="s">
+      <c r="O38" s="51" t="s">
+        <v>672</v>
+      </c>
+      <c r="P38" s="48" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q38" s="48" t="s">
+        <v>672</v>
+      </c>
+      <c r="R38" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -5426,7 +5438,7 @@
       <c r="N39" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O39" s="54" t="s">
+      <c r="O39" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P39" s="21" t="s">
@@ -5481,7 +5493,7 @@
       <c r="N40" s="14" t="s">
         <v>787</v>
       </c>
-      <c r="O40" s="54" t="s">
+      <c r="O40" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P40" s="15" t="s">
@@ -5502,50 +5514,50 @@
       <c r="C41" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="50" t="s">
+      <c r="D41" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="E41" s="50" t="s">
+      <c r="E41" s="46" t="s">
         <v>189</v>
       </c>
-      <c r="F41" s="50" t="s">
+      <c r="F41" s="46" t="s">
         <v>288</v>
       </c>
-      <c r="G41" s="50" t="s">
+      <c r="G41" s="46" t="s">
         <v>359</v>
       </c>
-      <c r="H41" s="50" t="s">
+      <c r="H41" s="46" t="s">
         <v>442</v>
       </c>
-      <c r="I41" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J41" s="50" t="s">
+      <c r="I41" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J41" s="46" t="s">
         <v>501</v>
       </c>
-      <c r="K41" s="50" t="s">
+      <c r="K41" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L41" s="50">
+      <c r="L41" s="46">
         <v>1</v>
       </c>
-      <c r="M41" s="45">
+      <c r="M41" s="42">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N41" s="50" t="s">
+      <c r="N41" s="46" t="s">
         <v>787</v>
       </c>
-      <c r="O41" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P41" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q41" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R41" s="53" t="s">
+      <c r="O41" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P41" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q41" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R41" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -5592,7 +5604,7 @@
       <c r="N42" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O42" s="54" t="s">
+      <c r="O42" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P42" s="15" t="s">
@@ -5647,7 +5659,7 @@
       <c r="N43" s="20">
         <v>11</v>
       </c>
-      <c r="O43" s="54" t="s">
+      <c r="O43" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P43" s="21" t="s">
@@ -5702,7 +5714,7 @@
       <c r="N44" s="14">
         <v>15</v>
       </c>
-      <c r="O44" s="54" t="s">
+      <c r="O44" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P44" s="15" t="s">
@@ -5757,7 +5769,7 @@
       <c r="N45" s="20">
         <v>15</v>
       </c>
-      <c r="O45" s="54" t="s">
+      <c r="O45" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P45" s="21" t="s">
@@ -5812,7 +5824,7 @@
       <c r="N46" s="14">
         <v>11</v>
       </c>
-      <c r="O46" s="54" t="s">
+      <c r="O46" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P46" s="15" t="s">
@@ -5867,7 +5879,7 @@
       <c r="N47" s="20">
         <v>25</v>
       </c>
-      <c r="O47" s="54" t="s">
+      <c r="O47" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P47" s="21" t="s">
@@ -5888,50 +5900,50 @@
       <c r="C48" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D48" s="50" t="s">
+      <c r="D48" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="E48" s="50" t="s">
+      <c r="E48" s="46" t="s">
         <v>195</v>
       </c>
       <c r="F48" s="20" t="s">
         <v>674</v>
       </c>
-      <c r="G48" s="50" t="s">
+      <c r="G48" s="46" t="s">
         <v>293</v>
       </c>
-      <c r="H48" s="50" t="s">
+      <c r="H48" s="46" t="s">
         <v>446</v>
       </c>
-      <c r="I48" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J48" s="50" t="s">
+      <c r="I48" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J48" s="46" t="s">
         <v>506</v>
       </c>
-      <c r="K48" s="50" t="s">
+      <c r="K48" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L48" s="50">
+      <c r="L48" s="46">
         <v>1</v>
       </c>
-      <c r="M48" s="45">
+      <c r="M48" s="42">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N48" s="50" t="s">
+      <c r="N48" s="46" t="s">
         <v>788</v>
       </c>
-      <c r="O48" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P48" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q48" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R48" s="53" t="s">
+      <c r="O48" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P48" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q48" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R48" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -5978,7 +5990,7 @@
       <c r="N49" s="20">
         <v>15</v>
       </c>
-      <c r="O49" s="54" t="s">
+      <c r="O49" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P49" s="21" t="s">
@@ -6033,7 +6045,7 @@
       <c r="N50" s="20">
         <v>11</v>
       </c>
-      <c r="O50" s="54" t="s">
+      <c r="O50" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P50" s="21" t="s">
@@ -6088,7 +6100,7 @@
       <c r="N51" s="14">
         <v>40</v>
       </c>
-      <c r="O51" s="54" t="s">
+      <c r="O51" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P51" s="15" t="s">
@@ -6143,7 +6155,7 @@
       <c r="N52" s="20">
         <v>15</v>
       </c>
-      <c r="O52" s="54" t="s">
+      <c r="O52" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P52" s="21" t="s">
@@ -6198,7 +6210,7 @@
       <c r="N53" s="14">
         <v>20</v>
       </c>
-      <c r="O53" s="54" t="s">
+      <c r="O53" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P53" s="15" t="s">
@@ -6219,50 +6231,50 @@
       <c r="C54" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D54" s="50" t="s">
+      <c r="D54" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="E54" s="50" t="s">
+      <c r="E54" s="46" t="s">
         <v>201</v>
       </c>
-      <c r="F54" s="50" t="s">
+      <c r="F54" s="46" t="s">
         <v>289</v>
       </c>
-      <c r="G54" s="50" t="s">
+      <c r="G54" s="46" t="s">
         <v>362</v>
       </c>
-      <c r="H54" s="50" t="s">
+      <c r="H54" s="46" t="s">
         <v>435</v>
       </c>
-      <c r="I54" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J54" s="50" t="s">
+      <c r="I54" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J54" s="46" t="s">
         <v>512</v>
       </c>
-      <c r="K54" s="50" t="s">
+      <c r="K54" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L54" s="50">
+      <c r="L54" s="46">
         <v>1</v>
       </c>
-      <c r="M54" s="45">
+      <c r="M54" s="42">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N54" s="50" t="s">
+      <c r="N54" s="46" t="s">
         <v>788</v>
       </c>
-      <c r="O54" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P54" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q54" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R54" s="53" t="s">
+      <c r="O54" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P54" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q54" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R54" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -6309,7 +6321,7 @@
       <c r="N55" s="14">
         <v>20</v>
       </c>
-      <c r="O55" s="54" t="s">
+      <c r="O55" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P55" s="15" t="s">
@@ -6364,7 +6376,7 @@
       <c r="N56" s="20" t="s">
         <v>790</v>
       </c>
-      <c r="O56" s="54" t="s">
+      <c r="O56" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P56" s="21" t="s">
@@ -6419,7 +6431,7 @@
       <c r="N57" s="14">
         <v>40</v>
       </c>
-      <c r="O57" s="54" t="s">
+      <c r="O57" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P57" s="15" t="s">
@@ -6474,7 +6486,7 @@
       <c r="N58" s="20" t="s">
         <v>787</v>
       </c>
-      <c r="O58" s="54" t="s">
+      <c r="O58" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P58" s="21" t="s">
@@ -6529,7 +6541,7 @@
       <c r="N59" s="14" t="s">
         <v>787</v>
       </c>
-      <c r="O59" s="54" t="s">
+      <c r="O59" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P59" s="15" t="s">
@@ -6584,7 +6596,7 @@
       <c r="N60" s="20">
         <v>11</v>
       </c>
-      <c r="O60" s="54" t="s">
+      <c r="O60" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P60" s="21" t="s">
@@ -6639,7 +6651,7 @@
       <c r="N61" s="14" t="s">
         <v>787</v>
       </c>
-      <c r="O61" s="54" t="s">
+      <c r="O61" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P61" s="15" t="s">
@@ -6694,7 +6706,7 @@
       <c r="N62" s="20">
         <v>80</v>
       </c>
-      <c r="O62" s="54" t="s">
+      <c r="O62" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P62" s="21" t="s">
@@ -6749,7 +6761,7 @@
       <c r="N63" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O63" s="54" t="s">
+      <c r="O63" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P63" s="15" t="s">
@@ -6804,7 +6816,7 @@
       <c r="N64" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O64" s="54" t="s">
+      <c r="O64" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P64" s="21" t="s">
@@ -6859,7 +6871,7 @@
       <c r="N65" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O65" s="54" t="s">
+      <c r="O65" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P65" s="15" t="s">
@@ -6914,7 +6926,7 @@
       <c r="N66" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O66" s="54" t="s">
+      <c r="O66" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P66" s="21" t="s">
@@ -6969,7 +6981,7 @@
       <c r="N67" s="14" t="s">
         <v>787</v>
       </c>
-      <c r="O67" s="54" t="s">
+      <c r="O67" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P67" s="15" t="s">
@@ -7024,7 +7036,7 @@
       <c r="N68" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O68" s="54" t="s">
+      <c r="O68" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P68" s="21" t="s">
@@ -7079,7 +7091,7 @@
       <c r="N69" s="14" t="s">
         <v>787</v>
       </c>
-      <c r="O69" s="54" t="s">
+      <c r="O69" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P69" s="15" t="s">
@@ -7134,7 +7146,7 @@
       <c r="N70" s="20" t="s">
         <v>787</v>
       </c>
-      <c r="O70" s="54" t="s">
+      <c r="O70" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P70" s="21" t="s">
@@ -7189,7 +7201,7 @@
       <c r="N71" s="14" t="s">
         <v>786</v>
       </c>
-      <c r="O71" s="54" t="s">
+      <c r="O71" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P71" s="15" t="s">
@@ -7244,7 +7256,7 @@
       <c r="N72" s="20" t="s">
         <v>786</v>
       </c>
-      <c r="O72" s="54" t="s">
+      <c r="O72" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P72" s="21" t="s">
@@ -7299,7 +7311,7 @@
       <c r="N73" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O73" s="54" t="s">
+      <c r="O73" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P73" s="15" t="s">
@@ -7354,7 +7366,7 @@
       <c r="N74" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O74" s="54" t="s">
+      <c r="O74" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P74" s="21" t="s">
@@ -7409,7 +7421,7 @@
       <c r="N75" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O75" s="54" t="s">
+      <c r="O75" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P75" s="15" t="s">
@@ -7464,7 +7476,7 @@
       <c r="N76" s="20" t="s">
         <v>791</v>
       </c>
-      <c r="O76" s="54" t="s">
+      <c r="O76" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P76" s="21" t="s">
@@ -7519,7 +7531,7 @@
       <c r="N77" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O77" s="54" t="s">
+      <c r="O77" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P77" s="15" t="s">
@@ -7574,7 +7586,7 @@
       <c r="N78" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O78" s="54" t="s">
+      <c r="O78" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P78" s="21" t="s">
@@ -7629,7 +7641,7 @@
       <c r="N79" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O79" s="54" t="s">
+      <c r="O79" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P79" s="15" t="s">
@@ -7684,7 +7696,7 @@
       <c r="N80" s="20">
         <v>200</v>
       </c>
-      <c r="O80" s="54" t="s">
+      <c r="O80" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P80" s="21" t="s">
@@ -7739,7 +7751,7 @@
       <c r="N81" s="14" t="s">
         <v>787</v>
       </c>
-      <c r="O81" s="54" t="s">
+      <c r="O81" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P81" s="15" t="s">
@@ -7794,7 +7806,7 @@
       <c r="N82" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O82" s="54" t="s">
+      <c r="O82" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P82" s="21" t="s">
@@ -7849,7 +7861,7 @@
       <c r="N83" s="14" t="s">
         <v>787</v>
       </c>
-      <c r="O83" s="54" t="s">
+      <c r="O83" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P83" s="15" t="s">
@@ -7904,7 +7916,7 @@
       <c r="N84" s="20" t="s">
         <v>787</v>
       </c>
-      <c r="O84" s="54" t="s">
+      <c r="O84" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P84" s="21" t="s">
@@ -7959,7 +7971,7 @@
       <c r="N85" s="14" t="s">
         <v>787</v>
       </c>
-      <c r="O85" s="54" t="s">
+      <c r="O85" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P85" s="15" t="s">
@@ -8014,7 +8026,7 @@
       <c r="N86" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O86" s="54" t="s">
+      <c r="O86" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P86" s="21" t="s">
@@ -8069,7 +8081,7 @@
       <c r="N87" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O87" s="54" t="s">
+      <c r="O87" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P87" s="15" t="s">
@@ -8124,7 +8136,7 @@
       <c r="N88" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O88" s="54" t="s">
+      <c r="O88" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P88" s="21" t="s">
@@ -8179,7 +8191,7 @@
       <c r="N89" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O89" s="54" t="s">
+      <c r="O89" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P89" s="15" t="s">
@@ -8209,7 +8221,9 @@
       <c r="F90" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="G90" s="20"/>
+      <c r="G90" s="20" t="s">
+        <v>879</v>
+      </c>
       <c r="H90" s="20"/>
       <c r="I90" s="14" t="s">
         <v>672</v>
@@ -8230,7 +8244,7 @@
       <c r="N90" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O90" s="54" t="s">
+      <c r="O90" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P90" s="21" t="s">
@@ -8285,7 +8299,7 @@
       <c r="N91" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O91" s="54" t="s">
+      <c r="O91" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P91" s="15" t="s">
@@ -8340,7 +8354,7 @@
       <c r="N92" s="20" t="s">
         <v>787</v>
       </c>
-      <c r="O92" s="54" t="s">
+      <c r="O92" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P92" s="21" t="s">
@@ -8395,7 +8409,7 @@
       <c r="N93" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O93" s="54" t="s">
+      <c r="O93" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P93" s="15" t="s">
@@ -8450,7 +8464,7 @@
       <c r="N94" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O94" s="54" t="s">
+      <c r="O94" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P94" s="21" t="s">
@@ -8505,7 +8519,7 @@
       <c r="N95" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O95" s="54" t="s">
+      <c r="O95" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P95" s="15" t="s">
@@ -8560,7 +8574,7 @@
       <c r="N96" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O96" s="54" t="s">
+      <c r="O96" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P96" s="21" t="s">
@@ -8615,7 +8629,7 @@
       <c r="N97" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O97" s="54" t="s">
+      <c r="O97" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P97" s="15" t="s">
@@ -8670,7 +8684,7 @@
       <c r="N98" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O98" s="54" t="s">
+      <c r="O98" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P98" s="21" t="s">
@@ -8725,7 +8739,7 @@
       <c r="N99" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O99" s="54" t="s">
+      <c r="O99" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P99" s="15" t="s">
@@ -8780,7 +8794,7 @@
       <c r="N100" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O100" s="54" t="s">
+      <c r="O100" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P100" s="21" t="s">
@@ -8835,7 +8849,7 @@
       <c r="N101" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O101" s="54" t="s">
+      <c r="O101" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P101" s="15" t="s">
@@ -8890,7 +8904,7 @@
       <c r="N102" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O102" s="54" t="s">
+      <c r="O102" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P102" s="21" t="s">
@@ -8911,50 +8925,50 @@
       <c r="C103" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D103" s="50" t="s">
+      <c r="D103" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="E103" s="50" t="s">
+      <c r="E103" s="46" t="s">
         <v>227</v>
       </c>
-      <c r="F103" s="50" t="s">
+      <c r="F103" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="G103" s="50" t="s">
+      <c r="G103" s="46" t="s">
         <v>387</v>
       </c>
-      <c r="H103" s="50" t="s">
+      <c r="H103" s="46" t="s">
         <v>438</v>
       </c>
-      <c r="I103" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J103" s="50" t="s">
+      <c r="I103" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J103" s="46" t="s">
         <v>537</v>
       </c>
-      <c r="K103" s="50" t="s">
+      <c r="K103" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L103" s="50">
+      <c r="L103" s="46">
         <v>2</v>
       </c>
-      <c r="M103" s="45">
+      <c r="M103" s="42">
         <f t="shared" si="30"/>
         <v>20</v>
       </c>
-      <c r="N103" s="50" t="s">
+      <c r="N103" s="46" t="s">
         <v>784</v>
       </c>
-      <c r="O103" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P103" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q103" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R103" s="53" t="s">
+      <c r="O103" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P103" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q103" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R103" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -9001,7 +9015,7 @@
       <c r="N104" s="20" t="s">
         <v>787</v>
       </c>
-      <c r="O104" s="54" t="s">
+      <c r="O104" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P104" s="21" t="s">
@@ -9056,7 +9070,7 @@
       <c r="N105" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O105" s="54" t="s">
+      <c r="O105" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P105" s="15" t="s">
@@ -9111,7 +9125,7 @@
       <c r="N106" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O106" s="54" t="s">
+      <c r="O106" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P106" s="21" t="s">
@@ -9166,7 +9180,7 @@
       <c r="N107" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O107" s="54" t="s">
+      <c r="O107" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P107" s="15" t="s">
@@ -9187,50 +9201,50 @@
       <c r="C108" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D108" s="50" t="s">
+      <c r="D108" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="E108" s="50" t="s">
+      <c r="E108" s="46" t="s">
         <v>245</v>
       </c>
-      <c r="F108" s="50" t="s">
+      <c r="F108" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="G108" s="50" t="s">
+      <c r="G108" s="46" t="s">
         <v>404</v>
       </c>
-      <c r="H108" s="50" t="s">
+      <c r="H108" s="46" t="s">
         <v>438</v>
       </c>
-      <c r="I108" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J108" s="50" t="s">
+      <c r="I108" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J108" s="46" t="s">
         <v>555</v>
       </c>
-      <c r="K108" s="50" t="s">
+      <c r="K108" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L108" s="50">
+      <c r="L108" s="46">
         <v>1</v>
       </c>
-      <c r="M108" s="45">
+      <c r="M108" s="42">
         <f t="shared" si="30"/>
         <v>10</v>
       </c>
-      <c r="N108" s="50" t="s">
+      <c r="N108" s="46" t="s">
         <v>784</v>
       </c>
-      <c r="O108" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P108" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q108" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R108" s="53" t="s">
+      <c r="O108" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P108" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q108" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R108" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -9277,7 +9291,7 @@
       <c r="N109" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O109" s="54" t="s">
+      <c r="O109" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P109" s="15" t="s">
@@ -9298,50 +9312,50 @@
       <c r="C110" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D110" s="50" t="s">
+      <c r="D110" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="E110" s="50" t="s">
+      <c r="E110" s="46" t="s">
         <v>253</v>
       </c>
-      <c r="F110" s="50" t="s">
+      <c r="F110" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="G110" s="50" t="s">
+      <c r="G110" s="46" t="s">
         <v>412</v>
       </c>
-      <c r="H110" s="50" t="s">
+      <c r="H110" s="46" t="s">
         <v>438</v>
       </c>
-      <c r="I110" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J110" s="50" t="s">
+      <c r="I110" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J110" s="46" t="s">
         <v>563</v>
       </c>
-      <c r="K110" s="50" t="s">
+      <c r="K110" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L110" s="50">
+      <c r="L110" s="46">
         <v>1</v>
       </c>
-      <c r="M110" s="45">
+      <c r="M110" s="42">
         <f t="shared" si="30"/>
         <v>10</v>
       </c>
-      <c r="N110" s="50" t="s">
+      <c r="N110" s="46" t="s">
         <v>784</v>
       </c>
-      <c r="O110" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P110" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q110" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R110" s="53" t="s">
+      <c r="O110" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P110" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q110" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R110" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -9388,7 +9402,7 @@
       <c r="N111" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="O111" s="54" t="s">
+      <c r="O111" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P111" s="15" t="s">
@@ -9443,7 +9457,7 @@
       <c r="N112" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O112" s="54" t="s">
+      <c r="O112" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P112" s="21" t="s">
@@ -9464,50 +9478,50 @@
       <c r="C113" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D113" s="50" t="s">
+      <c r="D113" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="E113" s="50" t="s">
+      <c r="E113" s="46" t="s">
         <v>249</v>
       </c>
-      <c r="F113" s="50" t="s">
+      <c r="F113" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="G113" s="50" t="s">
+      <c r="G113" s="46" t="s">
         <v>408</v>
       </c>
-      <c r="H113" s="50" t="s">
+      <c r="H113" s="46" t="s">
         <v>438</v>
       </c>
-      <c r="I113" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J113" s="50" t="s">
+      <c r="I113" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J113" s="46" t="s">
         <v>559</v>
       </c>
-      <c r="K113" s="50" t="s">
+      <c r="K113" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L113" s="50">
+      <c r="L113" s="46">
         <v>1</v>
       </c>
-      <c r="M113" s="45">
+      <c r="M113" s="42">
         <f t="shared" si="30"/>
         <v>10</v>
       </c>
-      <c r="N113" s="50" t="s">
+      <c r="N113" s="46" t="s">
         <v>784</v>
       </c>
-      <c r="O113" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P113" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q113" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R113" s="53" t="s">
+      <c r="O113" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P113" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q113" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R113" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -9520,50 +9534,50 @@
       <c r="C114" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D114" s="50" t="s">
+      <c r="D114" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="E114" s="50" t="s">
+      <c r="E114" s="46" t="s">
         <v>223</v>
       </c>
-      <c r="F114" s="50" t="s">
+      <c r="F114" s="46" t="s">
         <v>305</v>
       </c>
-      <c r="G114" s="50" t="s">
+      <c r="G114" s="46" t="s">
         <v>383</v>
       </c>
-      <c r="H114" s="50" t="s">
+      <c r="H114" s="46" t="s">
         <v>438</v>
       </c>
-      <c r="I114" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J114" s="50" t="s">
+      <c r="I114" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J114" s="46" t="s">
         <v>533</v>
       </c>
-      <c r="K114" s="50" t="s">
+      <c r="K114" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L114" s="50">
+      <c r="L114" s="46">
         <v>2</v>
       </c>
-      <c r="M114" s="45">
+      <c r="M114" s="42">
         <f t="shared" si="30"/>
         <v>20</v>
       </c>
-      <c r="N114" s="50" t="s">
+      <c r="N114" s="46" t="s">
         <v>784</v>
       </c>
-      <c r="O114" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P114" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q114" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R114" s="53" t="s">
+      <c r="O114" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P114" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q114" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R114" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -9579,19 +9593,19 @@
       <c r="D115" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E115" s="47" t="s">
+      <c r="E115" s="43" t="s">
         <v>257</v>
       </c>
       <c r="F115" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="G115" s="47" t="s">
+      <c r="G115" s="43" t="s">
         <v>416</v>
       </c>
       <c r="H115" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="I115" s="47" t="s">
+      <c r="I115" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J115" s="14" t="s">
@@ -9610,7 +9624,7 @@
       <c r="N115" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="O115" s="54" t="s">
+      <c r="O115" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P115" s="21" t="s">
@@ -9646,7 +9660,7 @@
       <c r="H116" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="I116" s="47" t="s">
+      <c r="I116" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J116" s="14" t="s">
@@ -9665,7 +9679,7 @@
       <c r="N116" s="14">
         <v>11</v>
       </c>
-      <c r="O116" s="54" t="s">
+      <c r="O116" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P116" s="15" t="s">
@@ -9701,7 +9715,7 @@
       <c r="H117" s="20" t="s">
         <v>458</v>
       </c>
-      <c r="I117" s="47" t="s">
+      <c r="I117" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J117" s="20" t="s">
@@ -9720,7 +9734,7 @@
       <c r="N117" s="20">
         <v>20</v>
       </c>
-      <c r="O117" s="54" t="s">
+      <c r="O117" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P117" s="21" t="s">
@@ -9756,7 +9770,7 @@
       <c r="H118" s="14" t="s">
         <v>458</v>
       </c>
-      <c r="I118" s="47" t="s">
+      <c r="I118" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J118" s="14" t="s">
@@ -9775,7 +9789,7 @@
       <c r="N118" s="14">
         <v>50</v>
       </c>
-      <c r="O118" s="54" t="s">
+      <c r="O118" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P118" s="15" t="s">
@@ -9811,7 +9825,7 @@
       <c r="H119" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="I119" s="47" t="s">
+      <c r="I119" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J119" s="20" t="s">
@@ -9830,7 +9844,7 @@
       <c r="N119" s="20">
         <v>11</v>
       </c>
-      <c r="O119" s="54" t="s">
+      <c r="O119" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P119" s="21" t="s">
@@ -9866,7 +9880,7 @@
       <c r="H120" s="14" t="s">
         <v>460</v>
       </c>
-      <c r="I120" s="47" t="s">
+      <c r="I120" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J120" s="14" t="s">
@@ -9885,7 +9899,7 @@
       <c r="N120" s="14">
         <v>11</v>
       </c>
-      <c r="O120" s="54" t="s">
+      <c r="O120" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P120" s="15" t="s">
@@ -9921,7 +9935,7 @@
       <c r="H121" s="20" t="s">
         <v>461</v>
       </c>
-      <c r="I121" s="47" t="s">
+      <c r="I121" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J121" s="20" t="s">
@@ -9940,7 +9954,7 @@
       <c r="N121" s="20">
         <v>11</v>
       </c>
-      <c r="O121" s="54" t="s">
+      <c r="O121" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P121" s="21" t="s">
@@ -9976,7 +9990,7 @@
       <c r="H122" s="14" t="s">
         <v>462</v>
       </c>
-      <c r="I122" s="47" t="s">
+      <c r="I122" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J122" s="14" t="s">
@@ -9995,7 +10009,7 @@
       <c r="N122" s="14">
         <v>11</v>
       </c>
-      <c r="O122" s="54" t="s">
+      <c r="O122" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P122" s="15" t="s">
@@ -10031,7 +10045,7 @@
       <c r="H123" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="I123" s="47" t="s">
+      <c r="I123" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J123" s="20" t="s">
@@ -10050,7 +10064,7 @@
       <c r="N123" s="20">
         <v>11</v>
       </c>
-      <c r="O123" s="54" t="s">
+      <c r="O123" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P123" s="21" t="s">
@@ -10086,7 +10100,7 @@
       <c r="H124" s="14" t="s">
         <v>463</v>
       </c>
-      <c r="I124" s="47" t="s">
+      <c r="I124" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J124" s="14" t="s">
@@ -10105,7 +10119,7 @@
       <c r="N124" s="14">
         <v>11</v>
       </c>
-      <c r="O124" s="54" t="s">
+      <c r="O124" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P124" s="15" t="s">
@@ -10141,7 +10155,7 @@
       <c r="H125" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="I125" s="47" t="s">
+      <c r="I125" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J125" s="20" t="s">
@@ -10160,7 +10174,7 @@
       <c r="N125" s="20">
         <v>15</v>
       </c>
-      <c r="O125" s="54" t="s">
+      <c r="O125" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P125" s="21" t="s">
@@ -10196,7 +10210,7 @@
       <c r="H126" s="14" t="s">
         <v>463</v>
       </c>
-      <c r="I126" s="47" t="s">
+      <c r="I126" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J126" s="14" t="s">
@@ -10215,7 +10229,7 @@
       <c r="N126" s="14">
         <v>11</v>
       </c>
-      <c r="O126" s="54" t="s">
+      <c r="O126" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P126" s="15" t="s">
@@ -10251,7 +10265,7 @@
       <c r="H127" s="20" t="s">
         <v>464</v>
       </c>
-      <c r="I127" s="47" t="s">
+      <c r="I127" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J127" s="20" t="s">
@@ -10270,7 +10284,7 @@
       <c r="N127" s="20">
         <v>15</v>
       </c>
-      <c r="O127" s="54" t="s">
+      <c r="O127" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P127" s="21" t="s">
@@ -10306,7 +10320,7 @@
       <c r="H128" s="14" t="s">
         <v>463</v>
       </c>
-      <c r="I128" s="47" t="s">
+      <c r="I128" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J128" s="14" t="s">
@@ -10325,7 +10339,7 @@
       <c r="N128" s="14">
         <v>11</v>
       </c>
-      <c r="O128" s="54" t="s">
+      <c r="O128" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P128" s="15" t="s">
@@ -10361,7 +10375,7 @@
       <c r="H129" s="20" t="s">
         <v>465</v>
       </c>
-      <c r="I129" s="47" t="s">
+      <c r="I129" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J129" s="20" t="s">
@@ -10380,7 +10394,7 @@
       <c r="N129" s="20">
         <v>11</v>
       </c>
-      <c r="O129" s="54" t="s">
+      <c r="O129" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P129" s="21" t="s">
@@ -10416,7 +10430,7 @@
       <c r="H130" s="14" t="s">
         <v>463</v>
       </c>
-      <c r="I130" s="47" t="s">
+      <c r="I130" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J130" s="14" t="s">
@@ -10435,7 +10449,7 @@
       <c r="N130" s="14">
         <v>11</v>
       </c>
-      <c r="O130" s="54" t="s">
+      <c r="O130" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P130" s="15" t="s">
@@ -10471,7 +10485,7 @@
       <c r="H131" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="I131" s="47" t="s">
+      <c r="I131" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J131" s="20" t="s">
@@ -10490,7 +10504,7 @@
       <c r="N131" s="20">
         <v>11</v>
       </c>
-      <c r="O131" s="54" t="s">
+      <c r="O131" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P131" s="21" t="s">
@@ -10526,7 +10540,7 @@
       <c r="H132" s="14" t="s">
         <v>466</v>
       </c>
-      <c r="I132" s="47" t="s">
+      <c r="I132" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J132" s="14" t="s">
@@ -10545,7 +10559,7 @@
       <c r="N132" s="14">
         <v>11</v>
       </c>
-      <c r="O132" s="54" t="s">
+      <c r="O132" s="50" t="s">
         <v>792</v>
       </c>
       <c r="P132" s="15">
@@ -10581,7 +10595,7 @@
       <c r="H133" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="I133" s="47" t="s">
+      <c r="I133" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J133" s="20" t="s">
@@ -10594,13 +10608,13 @@
         <v>1</v>
       </c>
       <c r="M133" s="14">
-        <f t="shared" ref="M133:M140" si="60">L133*10</f>
+        <f t="shared" ref="M133:M141" si="60">L133*10</f>
         <v>10</v>
       </c>
       <c r="N133" s="20">
         <v>15</v>
       </c>
-      <c r="O133" s="54" t="s">
+      <c r="O133" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P133" s="21" t="s">
@@ -10636,7 +10650,7 @@
       <c r="H134" s="20" t="s">
         <v>467</v>
       </c>
-      <c r="I134" s="47" t="s">
+      <c r="I134" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J134" s="20" t="s">
@@ -10655,7 +10669,7 @@
       <c r="N134" s="20">
         <v>15</v>
       </c>
-      <c r="O134" s="54" t="s">
+      <c r="O134" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P134" s="21" t="s">
@@ -10691,7 +10705,7 @@
       <c r="H135" s="14" t="s">
         <v>468</v>
       </c>
-      <c r="I135" s="47" t="s">
+      <c r="I135" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J135" s="14" t="s">
@@ -10710,7 +10724,7 @@
       <c r="N135" s="14">
         <v>25</v>
       </c>
-      <c r="O135" s="54" t="s">
+      <c r="O135" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P135" s="15" t="s">
@@ -10722,7 +10736,7 @@
       </c>
       <c r="R135" s="14"/>
     </row>
-    <row r="136" spans="1:18" ht="36.75" thickBot="1">
+    <row r="136" spans="1:18" ht="36">
       <c r="A136" s="1"/>
       <c r="B136" s="17">
         <f t="shared" si="0"/>
@@ -10746,7 +10760,7 @@
       <c r="H136" s="20" t="s">
         <v>469</v>
       </c>
-      <c r="I136" s="47" t="s">
+      <c r="I136" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J136" s="20" t="s">
@@ -10765,23 +10779,23 @@
       <c r="N136" s="20">
         <v>15</v>
       </c>
-      <c r="O136" s="54" t="s">
+      <c r="O136" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P136" s="21" t="s">
         <v>778</v>
       </c>
       <c r="Q136" s="21">
-        <f t="shared" ref="Q136:Q140" si="63">P136*N136</f>
+        <f t="shared" ref="Q136:Q141" si="63">P136*N136</f>
         <v>4.3424999999999994</v>
       </c>
       <c r="R136" s="20"/>
     </row>
-    <row r="137" spans="1:18" ht="24.75" thickBot="1">
+    <row r="137" spans="1:18" ht="24">
       <c r="A137" s="1"/>
-      <c r="B137" s="46">
-        <f>ROW(B137) - ROW($B$2)</f>
-        <v>135</v>
+      <c r="B137" s="17">
+        <f t="shared" si="0"/>
+        <v>130</v>
       </c>
       <c r="C137" s="22" t="s">
         <v>671</v>
@@ -10789,25 +10803,25 @@
       <c r="D137" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="E137" s="47" t="s">
+      <c r="E137" s="43" t="s">
         <v>673</v>
       </c>
       <c r="F137" s="14" t="s">
         <v>674</v>
       </c>
-      <c r="G137" s="47" t="s">
+      <c r="G137" s="43" t="s">
         <v>675</v>
       </c>
       <c r="H137" s="14" t="s">
         <v>676</v>
       </c>
-      <c r="I137" s="47" t="s">
+      <c r="I137" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J137" s="20" t="s">
         <v>693</v>
       </c>
-      <c r="K137" s="47" t="s">
+      <c r="K137" s="43" t="s">
         <v>672</v>
       </c>
       <c r="L137" s="14">
@@ -10820,7 +10834,7 @@
       <c r="N137" s="20">
         <v>21</v>
       </c>
-      <c r="O137" s="54" t="s">
+      <c r="O137" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P137" s="21" t="s">
@@ -10832,11 +10846,11 @@
       </c>
       <c r="R137" s="20"/>
     </row>
-    <row r="138" spans="1:18" ht="51.75" thickBot="1">
+    <row r="138" spans="1:18" ht="51">
       <c r="A138" s="1"/>
-      <c r="B138" s="46">
-        <f>ROW(B138) - ROW($B$2)</f>
-        <v>136</v>
+      <c r="B138" s="17">
+        <f t="shared" ref="B138:B141" si="64">ROW(B138) - ROW($B$7)</f>
+        <v>131</v>
       </c>
       <c r="C138" s="22" t="s">
         <v>671</v>
@@ -10844,25 +10858,25 @@
       <c r="D138" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="E138" s="47" t="s">
+      <c r="E138" s="43" t="s">
         <v>677</v>
       </c>
       <c r="F138" s="20" t="s">
         <v>674</v>
       </c>
-      <c r="G138" s="47" t="s">
+      <c r="G138" s="43" t="s">
         <v>678</v>
       </c>
       <c r="H138" s="14" t="s">
         <v>679</v>
       </c>
-      <c r="I138" s="47" t="s">
+      <c r="I138" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J138" s="20" t="s">
         <v>694</v>
       </c>
-      <c r="K138" s="47"/>
+      <c r="K138" s="43"/>
       <c r="L138" s="14">
         <v>1</v>
       </c>
@@ -10873,7 +10887,7 @@
       <c r="N138" s="20">
         <v>11</v>
       </c>
-      <c r="O138" s="54" t="s">
+      <c r="O138" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P138" s="21" t="s">
@@ -10883,15 +10897,15 @@
         <f t="shared" si="63"/>
         <v>61.974000000000004</v>
       </c>
-      <c r="R138" s="49" t="s">
+      <c r="R138" s="45" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="36.75" thickBot="1">
+    <row r="139" spans="1:18" ht="36">
       <c r="A139" s="1"/>
-      <c r="B139" s="46">
-        <f t="shared" ref="B139:B140" si="64">ROW(B139) - ROW($B$2)</f>
-        <v>137</v>
+      <c r="B139" s="17">
+        <f t="shared" si="64"/>
+        <v>132</v>
       </c>
       <c r="C139" s="22" t="s">
         <v>671</v>
@@ -10899,25 +10913,25 @@
       <c r="D139" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="E139" s="48" t="s">
+      <c r="E139" s="44" t="s">
         <v>680</v>
       </c>
       <c r="F139" s="20" t="s">
         <v>674</v>
       </c>
-      <c r="G139" s="48" t="s">
+      <c r="G139" s="44" t="s">
         <v>681</v>
       </c>
       <c r="H139" s="20" t="s">
         <v>682</v>
       </c>
-      <c r="I139" s="47" t="s">
+      <c r="I139" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J139" s="20" t="s">
         <v>695</v>
       </c>
-      <c r="K139" s="48"/>
+      <c r="K139" s="44"/>
       <c r="L139" s="20">
         <v>1</v>
       </c>
@@ -10928,7 +10942,7 @@
       <c r="N139" s="20">
         <v>15</v>
       </c>
-      <c r="O139" s="54" t="s">
+      <c r="O139" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P139" s="21" t="s">
@@ -10940,11 +10954,11 @@
       </c>
       <c r="R139" s="20"/>
     </row>
-    <row r="140" spans="1:18" ht="24.75" thickBot="1">
+    <row r="140" spans="1:18" ht="24">
       <c r="A140" s="1"/>
-      <c r="B140" s="46">
+      <c r="B140" s="17">
         <f t="shared" si="64"/>
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C140" s="22" t="s">
         <v>671</v>
@@ -10952,25 +10966,25 @@
       <c r="D140" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="E140" s="48" t="s">
+      <c r="E140" s="44" t="s">
         <v>683</v>
       </c>
       <c r="F140" s="20" t="s">
         <v>674</v>
       </c>
-      <c r="G140" s="48" t="s">
+      <c r="G140" s="44" t="s">
         <v>684</v>
       </c>
       <c r="H140" s="20" t="s">
         <v>685</v>
       </c>
-      <c r="I140" s="47" t="s">
+      <c r="I140" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J140" s="20" t="s">
         <v>696</v>
       </c>
-      <c r="K140" s="48"/>
+      <c r="K140" s="44"/>
       <c r="L140" s="20">
         <v>2</v>
       </c>
@@ -10981,7 +10995,7 @@
       <c r="N140" s="20">
         <v>21</v>
       </c>
-      <c r="O140" s="54" t="s">
+      <c r="O140" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P140" s="21" t="s">
@@ -10993,41 +11007,96 @@
       </c>
       <c r="R140" s="20"/>
     </row>
-    <row r="141" spans="1:18" ht="19.5" thickBot="1">
+    <row r="141" spans="1:18" ht="36.75" thickBot="1">
       <c r="A141" s="1"/>
-      <c r="N141" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="O141" s="44"/>
-      <c r="P141" s="44"/>
-      <c r="Q141" s="18">
-        <f>SUM(Q8:Q140)</f>
-        <v>880.00659999999993</v>
-      </c>
+      <c r="B141" s="17">
+        <f t="shared" si="64"/>
+        <v>134</v>
+      </c>
+      <c r="C141" s="22" t="s">
+        <v>671</v>
+      </c>
+      <c r="D141" s="14" t="s">
+        <v>672</v>
+      </c>
+      <c r="E141" s="44" t="s">
+        <v>880</v>
+      </c>
+      <c r="F141" s="20" t="s">
+        <v>674</v>
+      </c>
+      <c r="G141" s="44" t="s">
+        <v>881</v>
+      </c>
+      <c r="H141" s="20" t="s">
+        <v>882</v>
+      </c>
+      <c r="I141" s="43" t="s">
+        <v>672</v>
+      </c>
+      <c r="J141" s="20" t="s">
+        <v>672</v>
+      </c>
+      <c r="K141" s="44" t="s">
+        <v>672</v>
+      </c>
+      <c r="L141" s="20">
+        <v>1</v>
+      </c>
+      <c r="M141" s="14">
+        <f t="shared" si="60"/>
+        <v>10</v>
+      </c>
+      <c r="N141" s="20">
+        <v>6</v>
+      </c>
+      <c r="O141" s="50" t="s">
+        <v>883</v>
+      </c>
+      <c r="P141" s="21">
+        <v>2.4</v>
+      </c>
+      <c r="Q141" s="21">
+        <f t="shared" si="63"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="R141" s="20"/>
     </row>
     <row r="142" spans="1:18" ht="19.5" thickBot="1">
       <c r="A142" s="1"/>
-      <c r="N142" s="43" t="s">
+      <c r="N142" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="O142" s="54"/>
+      <c r="P142" s="54"/>
+      <c r="Q142" s="18">
+        <f>SUM(Q8:Q141)</f>
+        <v>894.40659999999991</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" ht="19.5" thickBot="1">
+      <c r="A143" s="1"/>
+      <c r="N143" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="O142" s="44"/>
-      <c r="P142" s="44"/>
-      <c r="Q142" s="19">
-        <f>Q141/10</f>
-        <v>88.000659999999996</v>
-      </c>
-    </row>
-    <row r="143" spans="1:18">
-      <c r="A143" s="1"/>
-    </row>
-    <row r="150" spans="13:13">
-      <c r="M150" s="38"/>
+      <c r="O143" s="54"/>
+      <c r="P143" s="54"/>
+      <c r="Q143" s="19">
+        <f>Q142/10</f>
+        <v>89.440659999999994</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18">
+      <c r="A144" s="1"/>
+    </row>
+    <row r="151" spans="13:13">
+      <c r="M151" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N141:P141"/>
     <mergeCell ref="N142:P142"/>
+    <mergeCell ref="N143:P143"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O8" r:id="rId1"/>
@@ -11162,21 +11231,22 @@
     <hyperlink ref="O132" r:id="rId130"/>
     <hyperlink ref="O39" r:id="rId131"/>
     <hyperlink ref="O115" r:id="rId132"/>
+    <hyperlink ref="O141" r:id="rId133" location="nav-specification"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId133"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId134"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R142"/>
+  <dimension ref="A1:R143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.7109375" customWidth="1"/>
     <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.42578125" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" customWidth="1"/>
     <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -11201,14 +11271,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1">
       <c r="A2" s="1"/>
@@ -11415,7 +11485,7 @@
       <c r="N8" s="14">
         <v>4020</v>
       </c>
-      <c r="O8" s="54" t="s">
+      <c r="O8" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P8" s="15" t="s">
@@ -11430,7 +11500,7 @@
     <row r="9" spans="1:18" ht="24">
       <c r="A9" s="1"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B136" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B137" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
@@ -11470,7 +11540,7 @@
       <c r="N9" s="20">
         <v>10002</v>
       </c>
-      <c r="O9" s="54" t="s">
+      <c r="O9" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P9" s="21" t="s">
@@ -11525,7 +11595,7 @@
       <c r="N10" s="14">
         <v>12010</v>
       </c>
-      <c r="O10" s="54" t="s">
+      <c r="O10" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P10" s="15" t="s">
@@ -11580,7 +11650,7 @@
       <c r="N11" s="20">
         <v>30100</v>
       </c>
-      <c r="O11" s="54" t="s">
+      <c r="O11" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P11" s="21" t="s">
@@ -11635,7 +11705,7 @@
       <c r="N12" s="14">
         <v>1002</v>
       </c>
-      <c r="O12" s="54" t="s">
+      <c r="O12" s="50" t="s">
         <v>793</v>
       </c>
       <c r="P12" s="15">
@@ -11690,7 +11760,7 @@
       <c r="N13" s="20">
         <v>12050</v>
       </c>
-      <c r="O13" s="54" t="s">
+      <c r="O13" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P13" s="21" t="s">
@@ -11745,7 +11815,7 @@
       <c r="N14" s="14">
         <v>1050</v>
       </c>
-      <c r="O14" s="54" t="s">
+      <c r="O14" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P14" s="15" t="s">
@@ -11800,7 +11870,7 @@
       <c r="N15" s="20">
         <v>2050</v>
       </c>
-      <c r="O15" s="54" t="s">
+      <c r="O15" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P15" s="21" t="s">
@@ -11812,7 +11882,7 @@
       </c>
       <c r="R15" s="20"/>
     </row>
-    <row r="16" spans="1:18" ht="24">
+    <row r="16" spans="1:18">
       <c r="A16" s="1"/>
       <c r="B16" s="16">
         <f>ROW(B16) - ROW($B$7)</f>
@@ -11855,7 +11925,7 @@
       <c r="N16" s="14">
         <v>1100</v>
       </c>
-      <c r="O16" s="54" t="s">
+      <c r="O16" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P16" s="15" t="s">
@@ -11910,7 +11980,7 @@
       <c r="N17" s="20">
         <v>9050</v>
       </c>
-      <c r="O17" s="54" t="s">
+      <c r="O17" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P17" s="21" t="s">
@@ -11965,7 +12035,7 @@
       <c r="N18" s="14">
         <v>9005</v>
       </c>
-      <c r="O18" s="54" t="s">
+      <c r="O18" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P18" s="15" t="s">
@@ -12020,7 +12090,7 @@
       <c r="N19" s="20">
         <v>2005</v>
       </c>
-      <c r="O19" s="54" t="s">
+      <c r="O19" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P19" s="21" t="s">
@@ -12075,7 +12145,7 @@
       <c r="N20" s="14">
         <v>3010</v>
       </c>
-      <c r="O20" s="54" t="s">
+      <c r="O20" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P20" s="15" t="s">
@@ -12130,7 +12200,7 @@
       <c r="N21" s="20">
         <v>1100</v>
       </c>
-      <c r="O21" s="54" t="s">
+      <c r="O21" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P21" s="21" t="s">
@@ -12185,7 +12255,7 @@
       <c r="N22" s="14">
         <v>1010</v>
       </c>
-      <c r="O22" s="54" t="s">
+      <c r="O22" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P22" s="15" t="s">
@@ -12240,7 +12310,7 @@
       <c r="N23" s="20">
         <v>8005</v>
       </c>
-      <c r="O23" s="54" t="s">
+      <c r="O23" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P23" s="21" t="s">
@@ -12295,7 +12365,7 @@
       <c r="N24" s="14">
         <v>5050</v>
       </c>
-      <c r="O24" s="54" t="s">
+      <c r="O24" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P24" s="15" t="s">
@@ -12307,7 +12377,7 @@
       </c>
       <c r="R24" s="14"/>
     </row>
-    <row r="25" spans="1:18" ht="24">
+    <row r="25" spans="1:18">
       <c r="A25" s="1"/>
       <c r="B25" s="17">
         <f t="shared" si="0"/>
@@ -12350,7 +12420,7 @@
       <c r="N25" s="20">
         <v>1010</v>
       </c>
-      <c r="O25" s="54" t="s">
+      <c r="O25" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P25" s="21" t="s">
@@ -12405,7 +12475,7 @@
       <c r="N26" s="14">
         <v>3020</v>
       </c>
-      <c r="O26" s="54" t="s">
+      <c r="O26" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P26" s="15" t="s">
@@ -12417,7 +12487,7 @@
       </c>
       <c r="R26" s="14"/>
     </row>
-    <row r="27" spans="1:18" ht="24">
+    <row r="27" spans="1:18">
       <c r="A27" s="1"/>
       <c r="B27" s="17">
         <f t="shared" si="0"/>
@@ -12460,7 +12530,7 @@
       <c r="N27" s="20">
         <v>2050</v>
       </c>
-      <c r="O27" s="54" t="s">
+      <c r="O27" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P27" s="21" t="s">
@@ -12472,7 +12542,7 @@
       </c>
       <c r="R27" s="20"/>
     </row>
-    <row r="28" spans="1:18" ht="24">
+    <row r="28" spans="1:18">
       <c r="A28" s="1"/>
       <c r="B28" s="16">
         <f>ROW(B28) - ROW($B$7)</f>
@@ -12515,7 +12585,7 @@
       <c r="N28" s="14">
         <v>3020</v>
       </c>
-      <c r="O28" s="54" t="s">
+      <c r="O28" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P28" s="15" t="s">
@@ -12570,7 +12640,7 @@
       <c r="N29" s="20">
         <v>1020</v>
       </c>
-      <c r="O29" s="54" t="s">
+      <c r="O29" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P29" s="21" t="s">
@@ -12625,7 +12695,7 @@
       <c r="N30" s="14">
         <v>2005</v>
       </c>
-      <c r="O30" s="54" t="s">
+      <c r="O30" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P30" s="15" t="s">
@@ -12680,7 +12750,7 @@
       <c r="N31" s="20">
         <v>2050</v>
       </c>
-      <c r="O31" s="54" t="s">
+      <c r="O31" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P31" s="21" t="s">
@@ -12735,7 +12805,7 @@
       <c r="N32" s="14">
         <v>2100</v>
       </c>
-      <c r="O32" s="54" t="s">
+      <c r="O32" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P32" s="15" t="s">
@@ -12747,7 +12817,7 @@
       </c>
       <c r="R32" s="14"/>
     </row>
-    <row r="33" spans="1:18" ht="24">
+    <row r="33" spans="1:18">
       <c r="A33" s="1"/>
       <c r="B33" s="17">
         <f t="shared" si="0"/>
@@ -12790,7 +12860,7 @@
       <c r="N33" s="20">
         <v>2100</v>
       </c>
-      <c r="O33" s="54" t="s">
+      <c r="O33" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P33" s="21" t="s">
@@ -12845,7 +12915,7 @@
       <c r="N34" s="14">
         <v>8100</v>
       </c>
-      <c r="O34" s="54" t="s">
+      <c r="O34" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P34" s="15" t="s">
@@ -12900,7 +12970,7 @@
       <c r="N35" s="20">
         <v>1100</v>
       </c>
-      <c r="O35" s="54" t="s">
+      <c r="O35" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P35" s="21" t="s">
@@ -12955,7 +13025,7 @@
       <c r="N36" s="14">
         <v>1020</v>
       </c>
-      <c r="O36" s="54" t="s">
+      <c r="O36" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P36" s="15" t="s">
@@ -12976,50 +13046,50 @@
       <c r="C37" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D37" s="50" t="s">
+      <c r="D37" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="50" t="s">
+      <c r="E37" s="46" t="s">
         <v>186</v>
       </c>
-      <c r="F37" s="50" t="s">
+      <c r="F37" s="46" t="s">
         <v>280</v>
       </c>
-      <c r="G37" s="50" t="s">
+      <c r="G37" s="46" t="s">
         <v>356</v>
       </c>
-      <c r="H37" s="50" t="s">
+      <c r="H37" s="46" t="s">
         <v>435</v>
       </c>
-      <c r="I37" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J37" s="50" t="s">
+      <c r="I37" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J37" s="46" t="s">
         <v>498</v>
       </c>
-      <c r="K37" s="50" t="s">
+      <c r="K37" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L37" s="50">
+      <c r="L37" s="46">
         <v>7</v>
       </c>
       <c r="M37" s="14">
         <f t="shared" si="1"/>
         <v>7000</v>
       </c>
-      <c r="N37" s="50" t="s">
+      <c r="N37" s="46" t="s">
         <v>871</v>
       </c>
-      <c r="O37" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P37" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q37" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R37" s="53" t="s">
+      <c r="O37" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P37" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q37" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R37" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -13032,50 +13102,50 @@
       <c r="C38" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="45" t="s">
+      <c r="D38" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="45" t="s">
+      <c r="E38" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="F38" s="45" t="s">
+      <c r="F38" s="42" t="s">
         <v>281</v>
       </c>
-      <c r="G38" s="45" t="s">
+      <c r="G38" s="42" t="s">
         <v>332</v>
       </c>
-      <c r="H38" s="45" t="s">
+      <c r="H38" s="42" t="s">
         <v>435</v>
       </c>
-      <c r="I38" s="45" t="s">
-        <v>672</v>
-      </c>
-      <c r="J38" s="45" t="s">
+      <c r="I38" s="42" t="s">
+        <v>672</v>
+      </c>
+      <c r="J38" s="42" t="s">
         <v>476</v>
       </c>
-      <c r="K38" s="45" t="s">
+      <c r="K38" s="42" t="s">
         <v>609</v>
       </c>
-      <c r="L38" s="45">
+      <c r="L38" s="42">
         <v>1</v>
       </c>
       <c r="M38" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N38" s="45" t="s">
+      <c r="N38" s="42" t="s">
         <v>869</v>
       </c>
-      <c r="O38" s="55" t="s">
-        <v>672</v>
-      </c>
-      <c r="P38" s="52" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q38" s="52" t="s">
-        <v>672</v>
-      </c>
-      <c r="R38" s="53" t="s">
+      <c r="O38" s="51" t="s">
+        <v>672</v>
+      </c>
+      <c r="P38" s="48" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q38" s="48" t="s">
+        <v>672</v>
+      </c>
+      <c r="R38" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -13122,7 +13192,7 @@
       <c r="N39" s="20">
         <v>9020</v>
       </c>
-      <c r="O39" s="54" t="s">
+      <c r="O39" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P39" s="21" t="s">
@@ -13177,7 +13247,7 @@
       <c r="N40" s="14">
         <v>1020</v>
       </c>
-      <c r="O40" s="54" t="s">
+      <c r="O40" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P40" s="15" t="s">
@@ -13198,50 +13268,50 @@
       <c r="C41" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="50" t="s">
+      <c r="D41" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="E41" s="50" t="s">
+      <c r="E41" s="46" t="s">
         <v>189</v>
       </c>
-      <c r="F41" s="50" t="s">
+      <c r="F41" s="46" t="s">
         <v>288</v>
       </c>
-      <c r="G41" s="50" t="s">
+      <c r="G41" s="46" t="s">
         <v>359</v>
       </c>
-      <c r="H41" s="50" t="s">
+      <c r="H41" s="46" t="s">
         <v>442</v>
       </c>
-      <c r="I41" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J41" s="50" t="s">
+      <c r="I41" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J41" s="46" t="s">
         <v>501</v>
       </c>
-      <c r="K41" s="50" t="s">
+      <c r="K41" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L41" s="50">
+      <c r="L41" s="46">
         <v>1</v>
       </c>
       <c r="M41" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N41" s="50" t="s">
+      <c r="N41" s="46" t="s">
         <v>869</v>
       </c>
-      <c r="O41" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P41" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q41" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R41" s="53" t="s">
+      <c r="O41" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P41" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q41" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R41" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -13288,7 +13358,7 @@
       <c r="N42" s="14">
         <v>2100</v>
       </c>
-      <c r="O42" s="54" t="s">
+      <c r="O42" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P42" s="15" t="s">
@@ -13343,7 +13413,7 @@
       <c r="N43" s="20">
         <v>1002</v>
       </c>
-      <c r="O43" s="54" t="s">
+      <c r="O43" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P43" s="21" t="s">
@@ -13355,7 +13425,7 @@
       </c>
       <c r="R43" s="20"/>
     </row>
-    <row r="44" spans="1:18" ht="60">
+    <row r="44" spans="1:18" ht="48">
       <c r="A44" s="1"/>
       <c r="B44" s="16">
         <f>ROW(B44) - ROW($B$7)</f>
@@ -13398,7 +13468,7 @@
       <c r="N44" s="14">
         <v>1005</v>
       </c>
-      <c r="O44" s="54" t="s">
+      <c r="O44" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P44" s="15" t="s">
@@ -13410,7 +13480,7 @@
       </c>
       <c r="R44" s="14"/>
     </row>
-    <row r="45" spans="1:18" ht="36">
+    <row r="45" spans="1:18" ht="24">
       <c r="A45" s="1"/>
       <c r="B45" s="17">
         <f t="shared" si="0"/>
@@ -13453,7 +13523,7 @@
       <c r="N45" s="20">
         <v>1005</v>
       </c>
-      <c r="O45" s="54" t="s">
+      <c r="O45" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P45" s="21" t="s">
@@ -13508,7 +13578,7 @@
       <c r="N46" s="14">
         <v>1002</v>
       </c>
-      <c r="O46" s="54" t="s">
+      <c r="O46" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P46" s="15" t="s">
@@ -13563,7 +13633,7 @@
       <c r="N47" s="20">
         <v>2005</v>
       </c>
-      <c r="O47" s="54" t="s">
+      <c r="O47" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P47" s="21" t="s">
@@ -13584,50 +13654,50 @@
       <c r="C48" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D48" s="50" t="s">
+      <c r="D48" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="E48" s="50" t="s">
+      <c r="E48" s="46" t="s">
         <v>195</v>
       </c>
       <c r="F48" s="20" t="s">
         <v>674</v>
       </c>
-      <c r="G48" s="50" t="s">
+      <c r="G48" s="46" t="s">
         <v>293</v>
       </c>
-      <c r="H48" s="50" t="s">
+      <c r="H48" s="46" t="s">
         <v>446</v>
       </c>
-      <c r="I48" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J48" s="50" t="s">
+      <c r="I48" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J48" s="46" t="s">
         <v>506</v>
       </c>
-      <c r="K48" s="50" t="s">
+      <c r="K48" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L48" s="50">
+      <c r="L48" s="46">
         <v>1</v>
       </c>
       <c r="M48" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N48" s="50" t="s">
+      <c r="N48" s="46" t="s">
         <v>869</v>
       </c>
-      <c r="O48" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P48" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q48" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R48" s="53" t="s">
+      <c r="O48" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P48" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q48" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R48" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -13674,7 +13744,7 @@
       <c r="N49" s="20">
         <v>1005</v>
       </c>
-      <c r="O49" s="54" t="s">
+      <c r="O49" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P49" s="21" t="s">
@@ -13686,7 +13756,7 @@
       </c>
       <c r="R49" s="20"/>
     </row>
-    <row r="50" spans="1:18" ht="24">
+    <row r="50" spans="1:18">
       <c r="A50" s="1"/>
       <c r="B50" s="17">
         <f t="shared" si="0"/>
@@ -13729,7 +13799,7 @@
       <c r="N50" s="20">
         <v>1002</v>
       </c>
-      <c r="O50" s="54" t="s">
+      <c r="O50" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P50" s="21" t="s">
@@ -13741,7 +13811,7 @@
       </c>
       <c r="R50" s="20"/>
     </row>
-    <row r="51" spans="1:18" ht="36">
+    <row r="51" spans="1:18" ht="24">
       <c r="A51" s="1"/>
       <c r="B51" s="16">
         <f>ROW(B51) - ROW($B$7)</f>
@@ -13784,7 +13854,7 @@
       <c r="N51" s="14">
         <v>3010</v>
       </c>
-      <c r="O51" s="54" t="s">
+      <c r="O51" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P51" s="15" t="s">
@@ -13796,7 +13866,7 @@
       </c>
       <c r="R51" s="14"/>
     </row>
-    <row r="52" spans="1:18" ht="24">
+    <row r="52" spans="1:18">
       <c r="A52" s="1"/>
       <c r="B52" s="17">
         <f t="shared" si="0"/>
@@ -13839,7 +13909,7 @@
       <c r="N52" s="20">
         <v>1005</v>
       </c>
-      <c r="O52" s="54" t="s">
+      <c r="O52" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P52" s="21" t="s">
@@ -13851,7 +13921,7 @@
       </c>
       <c r="R52" s="20"/>
     </row>
-    <row r="53" spans="1:18" ht="36">
+    <row r="53" spans="1:18" ht="24">
       <c r="A53" s="1"/>
       <c r="B53" s="16">
         <f>ROW(B53) - ROW($B$7)</f>
@@ -13894,7 +13964,7 @@
       <c r="N53" s="14">
         <v>1010</v>
       </c>
-      <c r="O53" s="54" t="s">
+      <c r="O53" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P53" s="15" t="s">
@@ -13915,50 +13985,50 @@
       <c r="C54" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D54" s="50" t="s">
+      <c r="D54" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="E54" s="50" t="s">
+      <c r="E54" s="46" t="s">
         <v>201</v>
       </c>
-      <c r="F54" s="50" t="s">
+      <c r="F54" s="46" t="s">
         <v>289</v>
       </c>
-      <c r="G54" s="50" t="s">
+      <c r="G54" s="46" t="s">
         <v>362</v>
       </c>
-      <c r="H54" s="50" t="s">
+      <c r="H54" s="46" t="s">
         <v>435</v>
       </c>
-      <c r="I54" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J54" s="50" t="s">
+      <c r="I54" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J54" s="46" t="s">
         <v>512</v>
       </c>
-      <c r="K54" s="50" t="s">
+      <c r="K54" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L54" s="50">
+      <c r="L54" s="46">
         <v>1</v>
       </c>
       <c r="M54" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N54" s="50" t="s">
+      <c r="N54" s="46" t="s">
         <v>869</v>
       </c>
-      <c r="O54" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P54" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q54" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R54" s="53" t="s">
+      <c r="O54" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P54" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q54" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R54" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -14005,7 +14075,7 @@
       <c r="N55" s="14">
         <v>1010</v>
       </c>
-      <c r="O55" s="54" t="s">
+      <c r="O55" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P55" s="15" t="s">
@@ -14060,7 +14130,7 @@
       <c r="N56" s="20">
         <v>5020</v>
       </c>
-      <c r="O56" s="54" t="s">
+      <c r="O56" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P56" s="21" t="s">
@@ -14072,7 +14142,7 @@
       </c>
       <c r="R56" s="20"/>
     </row>
-    <row r="57" spans="1:18" ht="36">
+    <row r="57" spans="1:18" ht="24">
       <c r="A57" s="1"/>
       <c r="B57" s="16">
         <f>ROW(B57) - ROW($B$7)</f>
@@ -14115,7 +14185,7 @@
       <c r="N57" s="14">
         <v>2020</v>
       </c>
-      <c r="O57" s="54" t="s">
+      <c r="O57" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P57" s="15" t="s">
@@ -14170,7 +14240,7 @@
       <c r="N58" s="20">
         <v>1020</v>
       </c>
-      <c r="O58" s="54" t="s">
+      <c r="O58" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P58" s="21" t="s">
@@ -14225,7 +14295,7 @@
       <c r="N59" s="14">
         <v>1020</v>
       </c>
-      <c r="O59" s="54" t="s">
+      <c r="O59" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P59" s="15" t="s">
@@ -14280,7 +14350,7 @@
       <c r="N60" s="20">
         <v>1002</v>
       </c>
-      <c r="O60" s="54" t="s">
+      <c r="O60" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P60" s="21" t="s">
@@ -14292,7 +14362,7 @@
       </c>
       <c r="R60" s="20"/>
     </row>
-    <row r="61" spans="1:18" ht="24">
+    <row r="61" spans="1:18">
       <c r="A61" s="1"/>
       <c r="B61" s="16">
         <f>ROW(B61) - ROW($B$7)</f>
@@ -14335,7 +14405,7 @@
       <c r="N61" s="14">
         <v>1020</v>
       </c>
-      <c r="O61" s="54" t="s">
+      <c r="O61" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P61" s="15" t="s">
@@ -14347,7 +14417,7 @@
       </c>
       <c r="R61" s="14"/>
     </row>
-    <row r="62" spans="1:18" ht="24">
+    <row r="62" spans="1:18">
       <c r="A62" s="1"/>
       <c r="B62" s="17">
         <f t="shared" si="0"/>
@@ -14390,7 +14460,7 @@
       <c r="N62" s="20">
         <v>6020</v>
       </c>
-      <c r="O62" s="54" t="s">
+      <c r="O62" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P62" s="21" t="s">
@@ -14445,7 +14515,7 @@
       <c r="N63" s="14">
         <v>7100</v>
       </c>
-      <c r="O63" s="54" t="s">
+      <c r="O63" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P63" s="15" t="s">
@@ -14500,7 +14570,7 @@
       <c r="N64" s="20">
         <v>1100</v>
       </c>
-      <c r="O64" s="54" t="s">
+      <c r="O64" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P64" s="21" t="s">
@@ -14555,7 +14625,7 @@
       <c r="N65" s="14">
         <v>1100</v>
       </c>
-      <c r="O65" s="54" t="s">
+      <c r="O65" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P65" s="15" t="s">
@@ -14610,7 +14680,7 @@
       <c r="N66" s="20">
         <v>1100</v>
       </c>
-      <c r="O66" s="54" t="s">
+      <c r="O66" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P66" s="21" t="s">
@@ -14622,7 +14692,7 @@
       </c>
       <c r="R66" s="20"/>
     </row>
-    <row r="67" spans="1:18" ht="24">
+    <row r="67" spans="1:18">
       <c r="A67" s="1"/>
       <c r="B67" s="16">
         <f>ROW(B67) - ROW($B$7)</f>
@@ -14665,7 +14735,7 @@
       <c r="N67" s="14">
         <v>1020</v>
       </c>
-      <c r="O67" s="54" t="s">
+      <c r="O67" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P67" s="15" t="s">
@@ -14720,7 +14790,7 @@
       <c r="N68" s="20">
         <v>1100</v>
       </c>
-      <c r="O68" s="54" t="s">
+      <c r="O68" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P68" s="21" t="s">
@@ -14732,7 +14802,7 @@
       </c>
       <c r="R68" s="20"/>
     </row>
-    <row r="69" spans="1:18" ht="24">
+    <row r="69" spans="1:18">
       <c r="A69" s="1"/>
       <c r="B69" s="16">
         <f>ROW(B69) - ROW($B$7)</f>
@@ -14775,7 +14845,7 @@
       <c r="N69" s="14">
         <v>1020</v>
       </c>
-      <c r="O69" s="54" t="s">
+      <c r="O69" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P69" s="15" t="s">
@@ -14787,7 +14857,7 @@
       </c>
       <c r="R69" s="14"/>
     </row>
-    <row r="70" spans="1:18" ht="24">
+    <row r="70" spans="1:18">
       <c r="A70" s="1"/>
       <c r="B70" s="17">
         <f t="shared" si="0"/>
@@ -14830,7 +14900,7 @@
       <c r="N70" s="20">
         <v>1020</v>
       </c>
-      <c r="O70" s="54" t="s">
+      <c r="O70" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P70" s="21" t="s">
@@ -14842,7 +14912,7 @@
       </c>
       <c r="R70" s="20"/>
     </row>
-    <row r="71" spans="1:18" ht="24">
+    <row r="71" spans="1:18">
       <c r="A71" s="1"/>
       <c r="B71" s="16">
         <f>ROW(B71) - ROW($B$7)</f>
@@ -14885,7 +14955,7 @@
       <c r="N71" s="14">
         <v>1050</v>
       </c>
-      <c r="O71" s="54" t="s">
+      <c r="O71" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P71" s="15" t="s">
@@ -14897,7 +14967,7 @@
       </c>
       <c r="R71" s="14"/>
     </row>
-    <row r="72" spans="1:18" ht="24">
+    <row r="72" spans="1:18">
       <c r="A72" s="1"/>
       <c r="B72" s="17">
         <f t="shared" si="0"/>
@@ -14940,7 +15010,7 @@
       <c r="N72" s="20">
         <v>1050</v>
       </c>
-      <c r="O72" s="54" t="s">
+      <c r="O72" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P72" s="21" t="s">
@@ -14995,7 +15065,7 @@
       <c r="N73" s="14">
         <v>1100</v>
       </c>
-      <c r="O73" s="54" t="s">
+      <c r="O73" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P73" s="15" t="s">
@@ -15050,7 +15120,7 @@
       <c r="N74" s="20">
         <v>6100</v>
       </c>
-      <c r="O74" s="54" t="s">
+      <c r="O74" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P74" s="21" t="s">
@@ -15105,7 +15175,7 @@
       <c r="N75" s="14">
         <v>1100</v>
       </c>
-      <c r="O75" s="54" t="s">
+      <c r="O75" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P75" s="15" t="s">
@@ -15160,7 +15230,7 @@
       <c r="N76" s="20">
         <v>19100</v>
       </c>
-      <c r="O76" s="54" t="s">
+      <c r="O76" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P76" s="21" t="s">
@@ -15215,7 +15285,7 @@
       <c r="N77" s="14">
         <v>2100</v>
       </c>
-      <c r="O77" s="54" t="s">
+      <c r="O77" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P77" s="15" t="s">
@@ -15270,7 +15340,7 @@
       <c r="N78" s="20">
         <v>1100</v>
       </c>
-      <c r="O78" s="54" t="s">
+      <c r="O78" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P78" s="21" t="s">
@@ -15325,7 +15395,7 @@
       <c r="N79" s="14">
         <v>1100</v>
       </c>
-      <c r="O79" s="54" t="s">
+      <c r="O79" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P79" s="15" t="s">
@@ -15380,7 +15450,7 @@
       <c r="N80" s="20">
         <v>10100</v>
       </c>
-      <c r="O80" s="54" t="s">
+      <c r="O80" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P80" s="21" t="s">
@@ -15392,7 +15462,7 @@
       </c>
       <c r="R80" s="20"/>
     </row>
-    <row r="81" spans="1:18" ht="24">
+    <row r="81" spans="1:18">
       <c r="A81" s="1"/>
       <c r="B81" s="16">
         <f>ROW(B81) - ROW($B$7)</f>
@@ -15435,7 +15505,7 @@
       <c r="N81" s="14">
         <v>1020</v>
       </c>
-      <c r="O81" s="54" t="s">
+      <c r="O81" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P81" s="15" t="s">
@@ -15490,7 +15560,7 @@
       <c r="N82" s="20">
         <v>1100</v>
       </c>
-      <c r="O82" s="54" t="s">
+      <c r="O82" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P82" s="21" t="s">
@@ -15502,7 +15572,7 @@
       </c>
       <c r="R82" s="20"/>
     </row>
-    <row r="83" spans="1:18" ht="24">
+    <row r="83" spans="1:18">
       <c r="A83" s="1"/>
       <c r="B83" s="16">
         <f>ROW(B83) - ROW($B$7)</f>
@@ -15545,7 +15615,7 @@
       <c r="N83" s="14">
         <v>1020</v>
       </c>
-      <c r="O83" s="54" t="s">
+      <c r="O83" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P83" s="15" t="s">
@@ -15557,7 +15627,7 @@
       </c>
       <c r="R83" s="14"/>
     </row>
-    <row r="84" spans="1:18" ht="24">
+    <row r="84" spans="1:18">
       <c r="A84" s="1"/>
       <c r="B84" s="17">
         <f t="shared" si="0"/>
@@ -15600,7 +15670,7 @@
       <c r="N84" s="20">
         <v>1020</v>
       </c>
-      <c r="O84" s="54" t="s">
+      <c r="O84" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P84" s="21" t="s">
@@ -15612,7 +15682,7 @@
       </c>
       <c r="R84" s="20"/>
     </row>
-    <row r="85" spans="1:18" ht="24">
+    <row r="85" spans="1:18">
       <c r="A85" s="1"/>
       <c r="B85" s="16">
         <f>ROW(B85) - ROW($B$7)</f>
@@ -15655,7 +15725,7 @@
       <c r="N85" s="14">
         <v>1020</v>
       </c>
-      <c r="O85" s="54" t="s">
+      <c r="O85" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P85" s="15" t="s">
@@ -15667,7 +15737,7 @@
       </c>
       <c r="R85" s="14"/>
     </row>
-    <row r="86" spans="1:18" ht="24">
+    <row r="86" spans="1:18">
       <c r="A86" s="1"/>
       <c r="B86" s="17">
         <f t="shared" si="0"/>
@@ -15710,7 +15780,7 @@
       <c r="N86" s="20">
         <v>8100</v>
       </c>
-      <c r="O86" s="54" t="s">
+      <c r="O86" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P86" s="21" t="s">
@@ -15765,7 +15835,7 @@
       <c r="N87" s="14">
         <v>4100</v>
       </c>
-      <c r="O87" s="54" t="s">
+      <c r="O87" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P87" s="15" t="s">
@@ -15820,7 +15890,7 @@
       <c r="N88" s="20">
         <v>5100</v>
       </c>
-      <c r="O88" s="54" t="s">
+      <c r="O88" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P88" s="21" t="s">
@@ -15875,7 +15945,7 @@
       <c r="N89" s="14">
         <v>1100</v>
       </c>
-      <c r="O89" s="54" t="s">
+      <c r="O89" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P89" s="15" t="s">
@@ -15905,7 +15975,9 @@
       <c r="F90" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="G90" s="20"/>
+      <c r="G90" s="20" t="s">
+        <v>879</v>
+      </c>
       <c r="H90" s="20"/>
       <c r="I90" s="14" t="s">
         <v>672</v>
@@ -15926,7 +15998,7 @@
       <c r="N90" s="20">
         <v>2100</v>
       </c>
-      <c r="O90" s="54" t="s">
+      <c r="O90" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P90" s="21" t="s">
@@ -15981,7 +16053,7 @@
       <c r="N91" s="14">
         <v>1100</v>
       </c>
-      <c r="O91" s="54" t="s">
+      <c r="O91" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P91" s="15" t="s">
@@ -15993,7 +16065,7 @@
       </c>
       <c r="R91" s="14"/>
     </row>
-    <row r="92" spans="1:18" ht="24">
+    <row r="92" spans="1:18">
       <c r="A92" s="1"/>
       <c r="B92" s="17">
         <f t="shared" si="0"/>
@@ -16036,7 +16108,7 @@
       <c r="N92" s="20">
         <v>1020</v>
       </c>
-      <c r="O92" s="54" t="s">
+      <c r="O92" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P92" s="21" t="s">
@@ -16091,7 +16163,7 @@
       <c r="N93" s="14">
         <v>1100</v>
       </c>
-      <c r="O93" s="54" t="s">
+      <c r="O93" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P93" s="15" t="s">
@@ -16146,7 +16218,7 @@
       <c r="N94" s="20">
         <v>1100</v>
       </c>
-      <c r="O94" s="54" t="s">
+      <c r="O94" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P94" s="21" t="s">
@@ -16201,7 +16273,7 @@
       <c r="N95" s="14">
         <v>1100</v>
       </c>
-      <c r="O95" s="54" t="s">
+      <c r="O95" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P95" s="15" t="s">
@@ -16256,7 +16328,7 @@
       <c r="N96" s="20">
         <v>1100</v>
       </c>
-      <c r="O96" s="54" t="s">
+      <c r="O96" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P96" s="21" t="s">
@@ -16311,7 +16383,7 @@
       <c r="N97" s="14">
         <v>3100</v>
       </c>
-      <c r="O97" s="54" t="s">
+      <c r="O97" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P97" s="15" t="s">
@@ -16323,7 +16395,7 @@
       </c>
       <c r="R97" s="14"/>
     </row>
-    <row r="98" spans="1:18" ht="24">
+    <row r="98" spans="1:18">
       <c r="A98" s="1"/>
       <c r="B98" s="17">
         <f t="shared" si="0"/>
@@ -16366,7 +16438,7 @@
       <c r="N98" s="20">
         <v>6100</v>
       </c>
-      <c r="O98" s="54" t="s">
+      <c r="O98" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P98" s="21" t="s">
@@ -16421,7 +16493,7 @@
       <c r="N99" s="14">
         <v>1100</v>
       </c>
-      <c r="O99" s="54" t="s">
+      <c r="O99" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P99" s="15" t="s">
@@ -16476,7 +16548,7 @@
       <c r="N100" s="20">
         <v>1100</v>
       </c>
-      <c r="O100" s="54" t="s">
+      <c r="O100" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P100" s="21" t="s">
@@ -16488,7 +16560,7 @@
       </c>
       <c r="R100" s="20"/>
     </row>
-    <row r="101" spans="1:18" ht="24">
+    <row r="101" spans="1:18">
       <c r="A101" s="1"/>
       <c r="B101" s="16">
         <f>ROW(B101) - ROW($B$7)</f>
@@ -16531,7 +16603,7 @@
       <c r="N101" s="14">
         <v>1100</v>
       </c>
-      <c r="O101" s="54" t="s">
+      <c r="O101" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P101" s="15" t="s">
@@ -16586,7 +16658,7 @@
       <c r="N102" s="20">
         <v>2100</v>
       </c>
-      <c r="O102" s="54" t="s">
+      <c r="O102" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P102" s="21" t="s">
@@ -16607,54 +16679,54 @@
       <c r="C103" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D103" s="50" t="s">
+      <c r="D103" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="E103" s="50" t="s">
+      <c r="E103" s="46" t="s">
         <v>227</v>
       </c>
-      <c r="F103" s="50" t="s">
+      <c r="F103" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="G103" s="50" t="s">
+      <c r="G103" s="46" t="s">
         <v>387</v>
       </c>
-      <c r="H103" s="50" t="s">
+      <c r="H103" s="46" t="s">
         <v>438</v>
       </c>
-      <c r="I103" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J103" s="50" t="s">
+      <c r="I103" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J103" s="46" t="s">
         <v>537</v>
       </c>
-      <c r="K103" s="50" t="s">
+      <c r="K103" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L103" s="50">
+      <c r="L103" s="46">
         <v>2</v>
       </c>
       <c r="M103" s="14">
         <f t="shared" si="31"/>
         <v>2000</v>
       </c>
-      <c r="N103" s="50" t="s">
+      <c r="N103" s="46" t="s">
         <v>870</v>
       </c>
-      <c r="O103" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P103" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q103" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R103" s="53" t="s">
+      <c r="O103" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P103" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q103" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R103" s="49" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="48">
+    <row r="104" spans="1:18" ht="36">
       <c r="A104" s="1"/>
       <c r="B104" s="17">
         <f t="shared" si="0"/>
@@ -16697,7 +16769,7 @@
       <c r="N104" s="20">
         <v>1020</v>
       </c>
-      <c r="O104" s="54" t="s">
+      <c r="O104" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P104" s="21" t="s">
@@ -16752,7 +16824,7 @@
       <c r="N105" s="14">
         <v>1100</v>
       </c>
-      <c r="O105" s="54" t="s">
+      <c r="O105" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P105" s="15" t="s">
@@ -16764,7 +16836,7 @@
       </c>
       <c r="R105" s="14"/>
     </row>
-    <row r="106" spans="1:18" ht="24">
+    <row r="106" spans="1:18">
       <c r="A106" s="1"/>
       <c r="B106" s="17">
         <f t="shared" si="0"/>
@@ -16807,7 +16879,7 @@
       <c r="N106" s="20">
         <v>1100</v>
       </c>
-      <c r="O106" s="54" t="s">
+      <c r="O106" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P106" s="21" t="s">
@@ -16862,7 +16934,7 @@
       <c r="N107" s="14">
         <v>1100</v>
       </c>
-      <c r="O107" s="54" t="s">
+      <c r="O107" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P107" s="15" t="s">
@@ -16883,50 +16955,50 @@
       <c r="C108" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D108" s="50" t="s">
+      <c r="D108" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="E108" s="50" t="s">
+      <c r="E108" s="46" t="s">
         <v>245</v>
       </c>
-      <c r="F108" s="50" t="s">
+      <c r="F108" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="G108" s="50" t="s">
+      <c r="G108" s="46" t="s">
         <v>404</v>
       </c>
-      <c r="H108" s="50" t="s">
+      <c r="H108" s="46" t="s">
         <v>438</v>
       </c>
-      <c r="I108" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J108" s="50" t="s">
+      <c r="I108" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J108" s="46" t="s">
         <v>555</v>
       </c>
-      <c r="K108" s="50" t="s">
+      <c r="K108" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L108" s="50">
+      <c r="L108" s="46">
         <v>1</v>
       </c>
       <c r="M108" s="14">
         <f t="shared" si="31"/>
         <v>1000</v>
       </c>
-      <c r="N108" s="50" t="s">
+      <c r="N108" s="46" t="s">
         <v>869</v>
       </c>
-      <c r="O108" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P108" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q108" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R108" s="53" t="s">
+      <c r="O108" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P108" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q108" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R108" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -16973,7 +17045,7 @@
       <c r="N109" s="14">
         <v>1100</v>
       </c>
-      <c r="O109" s="54" t="s">
+      <c r="O109" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P109" s="15" t="s">
@@ -16994,50 +17066,50 @@
       <c r="C110" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D110" s="50" t="s">
+      <c r="D110" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="E110" s="50" t="s">
+      <c r="E110" s="46" t="s">
         <v>253</v>
       </c>
-      <c r="F110" s="50" t="s">
+      <c r="F110" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="G110" s="50" t="s">
+      <c r="G110" s="46" t="s">
         <v>412</v>
       </c>
-      <c r="H110" s="50" t="s">
+      <c r="H110" s="46" t="s">
         <v>438</v>
       </c>
-      <c r="I110" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J110" s="50" t="s">
+      <c r="I110" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J110" s="46" t="s">
         <v>563</v>
       </c>
-      <c r="K110" s="50" t="s">
+      <c r="K110" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L110" s="50">
+      <c r="L110" s="46">
         <v>1</v>
       </c>
       <c r="M110" s="14">
         <f t="shared" si="31"/>
         <v>1000</v>
       </c>
-      <c r="N110" s="50" t="s">
+      <c r="N110" s="46" t="s">
         <v>869</v>
       </c>
-      <c r="O110" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P110" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q110" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R110" s="53" t="s">
+      <c r="O110" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P110" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q110" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R110" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -17084,7 +17156,7 @@
       <c r="N111" s="14">
         <v>4100</v>
       </c>
-      <c r="O111" s="54" t="s">
+      <c r="O111" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P111" s="15" t="s">
@@ -17096,7 +17168,7 @@
       </c>
       <c r="R111" s="14"/>
     </row>
-    <row r="112" spans="1:18" ht="24">
+    <row r="112" spans="1:18">
       <c r="A112" s="1"/>
       <c r="B112" s="17">
         <f t="shared" si="0"/>
@@ -17139,7 +17211,7 @@
       <c r="N112" s="20">
         <v>1100</v>
       </c>
-      <c r="O112" s="54" t="s">
+      <c r="O112" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P112" s="21" t="s">
@@ -17160,50 +17232,50 @@
       <c r="C113" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D113" s="50" t="s">
+      <c r="D113" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="E113" s="50" t="s">
+      <c r="E113" s="46" t="s">
         <v>249</v>
       </c>
-      <c r="F113" s="50" t="s">
+      <c r="F113" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="G113" s="50" t="s">
+      <c r="G113" s="46" t="s">
         <v>408</v>
       </c>
-      <c r="H113" s="50" t="s">
+      <c r="H113" s="46" t="s">
         <v>438</v>
       </c>
-      <c r="I113" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J113" s="50" t="s">
+      <c r="I113" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J113" s="46" t="s">
         <v>559</v>
       </c>
-      <c r="K113" s="50" t="s">
+      <c r="K113" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L113" s="50">
+      <c r="L113" s="46">
         <v>1</v>
       </c>
       <c r="M113" s="14">
         <f t="shared" si="31"/>
         <v>1000</v>
       </c>
-      <c r="N113" s="50" t="s">
+      <c r="N113" s="46" t="s">
         <v>869</v>
       </c>
-      <c r="O113" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P113" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q113" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R113" s="53" t="s">
+      <c r="O113" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P113" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q113" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R113" s="49" t="s">
         <v>688</v>
       </c>
     </row>
@@ -17216,54 +17288,54 @@
       <c r="C114" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D114" s="50" t="s">
+      <c r="D114" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="E114" s="50" t="s">
+      <c r="E114" s="46" t="s">
         <v>223</v>
       </c>
-      <c r="F114" s="50" t="s">
+      <c r="F114" s="46" t="s">
         <v>305</v>
       </c>
-      <c r="G114" s="50" t="s">
+      <c r="G114" s="46" t="s">
         <v>383</v>
       </c>
-      <c r="H114" s="50" t="s">
+      <c r="H114" s="46" t="s">
         <v>438</v>
       </c>
-      <c r="I114" s="50" t="s">
-        <v>672</v>
-      </c>
-      <c r="J114" s="50" t="s">
+      <c r="I114" s="46" t="s">
+        <v>672</v>
+      </c>
+      <c r="J114" s="46" t="s">
         <v>533</v>
       </c>
-      <c r="K114" s="50" t="s">
+      <c r="K114" s="46" t="s">
         <v>609</v>
       </c>
-      <c r="L114" s="50">
+      <c r="L114" s="46">
         <v>2</v>
       </c>
       <c r="M114" s="14">
         <f t="shared" si="31"/>
         <v>2000</v>
       </c>
-      <c r="N114" s="50" t="s">
+      <c r="N114" s="46" t="s">
         <v>870</v>
       </c>
-      <c r="O114" s="54" t="s">
-        <v>672</v>
-      </c>
-      <c r="P114" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q114" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="R114" s="53" t="s">
+      <c r="O114" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="P114" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q114" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="R114" s="49" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="24">
+    <row r="115" spans="1:18">
       <c r="A115" s="1"/>
       <c r="B115" s="17">
         <f t="shared" si="0"/>
@@ -17275,19 +17347,19 @@
       <c r="D115" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E115" s="47" t="s">
+      <c r="E115" s="43" t="s">
         <v>257</v>
       </c>
       <c r="F115" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="G115" s="47" t="s">
+      <c r="G115" s="43" t="s">
         <v>416</v>
       </c>
       <c r="H115" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="I115" s="47" t="s">
+      <c r="I115" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J115" s="14" t="s">
@@ -17306,7 +17378,7 @@
       <c r="N115" s="20">
         <v>1100</v>
       </c>
-      <c r="O115" s="54" t="s">
+      <c r="O115" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P115" s="21" t="s">
@@ -17342,7 +17414,7 @@
       <c r="H116" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="I116" s="47" t="s">
+      <c r="I116" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J116" s="14" t="s">
@@ -17361,7 +17433,7 @@
       <c r="N116" s="14">
         <v>1002</v>
       </c>
-      <c r="O116" s="54" t="s">
+      <c r="O116" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P116" s="15" t="s">
@@ -17373,7 +17445,7 @@
       </c>
       <c r="R116" s="14"/>
     </row>
-    <row r="117" spans="1:18" ht="60">
+    <row r="117" spans="1:18" ht="48">
       <c r="A117" s="1"/>
       <c r="B117" s="17">
         <f t="shared" si="0"/>
@@ -17397,7 +17469,7 @@
       <c r="H117" s="20" t="s">
         <v>458</v>
       </c>
-      <c r="I117" s="47" t="s">
+      <c r="I117" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J117" s="20" t="s">
@@ -17416,7 +17488,7 @@
       <c r="N117" s="20">
         <v>1010</v>
       </c>
-      <c r="O117" s="54" t="s">
+      <c r="O117" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P117" s="21" t="s">
@@ -17428,7 +17500,7 @@
       </c>
       <c r="R117" s="20"/>
     </row>
-    <row r="118" spans="1:18" ht="48">
+    <row r="118" spans="1:18" ht="36">
       <c r="A118" s="1"/>
       <c r="B118" s="16">
         <f>ROW(B118) - ROW($B$7)</f>
@@ -17452,7 +17524,7 @@
       <c r="H118" s="14" t="s">
         <v>458</v>
       </c>
-      <c r="I118" s="47" t="s">
+      <c r="I118" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J118" s="14" t="s">
@@ -17471,7 +17543,7 @@
       <c r="N118" s="14">
         <v>4010</v>
       </c>
-      <c r="O118" s="54" t="s">
+      <c r="O118" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P118" s="15" t="s">
@@ -17483,7 +17555,7 @@
       </c>
       <c r="R118" s="14"/>
     </row>
-    <row r="119" spans="1:18" ht="36">
+    <row r="119" spans="1:18" ht="24">
       <c r="A119" s="1"/>
       <c r="B119" s="17">
         <f t="shared" si="0"/>
@@ -17507,7 +17579,7 @@
       <c r="H119" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="I119" s="47" t="s">
+      <c r="I119" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J119" s="20" t="s">
@@ -17526,7 +17598,7 @@
       <c r="N119" s="20">
         <v>1002</v>
       </c>
-      <c r="O119" s="54" t="s">
+      <c r="O119" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P119" s="21" t="s">
@@ -17562,7 +17634,7 @@
       <c r="H120" s="14" t="s">
         <v>460</v>
       </c>
-      <c r="I120" s="47" t="s">
+      <c r="I120" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J120" s="14" t="s">
@@ -17581,7 +17653,7 @@
       <c r="N120" s="14">
         <v>1002</v>
       </c>
-      <c r="O120" s="54" t="s">
+      <c r="O120" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P120" s="15" t="s">
@@ -17617,7 +17689,7 @@
       <c r="H121" s="20" t="s">
         <v>461</v>
       </c>
-      <c r="I121" s="47" t="s">
+      <c r="I121" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J121" s="20" t="s">
@@ -17636,7 +17708,7 @@
       <c r="N121" s="20">
         <v>1002</v>
       </c>
-      <c r="O121" s="54" t="s">
+      <c r="O121" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P121" s="21" t="s">
@@ -17672,7 +17744,7 @@
       <c r="H122" s="14" t="s">
         <v>462</v>
       </c>
-      <c r="I122" s="47" t="s">
+      <c r="I122" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J122" s="14" t="s">
@@ -17691,7 +17763,7 @@
       <c r="N122" s="14">
         <v>1002</v>
       </c>
-      <c r="O122" s="54" t="s">
+      <c r="O122" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P122" s="15" t="s">
@@ -17727,7 +17799,7 @@
       <c r="H123" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="I123" s="47" t="s">
+      <c r="I123" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J123" s="20" t="s">
@@ -17746,7 +17818,7 @@
       <c r="N123" s="20">
         <v>1002</v>
       </c>
-      <c r="O123" s="54" t="s">
+      <c r="O123" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P123" s="21" t="s">
@@ -17782,7 +17854,7 @@
       <c r="H124" s="14" t="s">
         <v>463</v>
       </c>
-      <c r="I124" s="47" t="s">
+      <c r="I124" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J124" s="14" t="s">
@@ -17801,7 +17873,7 @@
       <c r="N124" s="14">
         <v>1002</v>
       </c>
-      <c r="O124" s="54" t="s">
+      <c r="O124" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P124" s="15" t="s">
@@ -17837,7 +17909,7 @@
       <c r="H125" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="I125" s="47" t="s">
+      <c r="I125" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J125" s="20" t="s">
@@ -17856,7 +17928,7 @@
       <c r="N125" s="20">
         <v>1005</v>
       </c>
-      <c r="O125" s="54" t="s">
+      <c r="O125" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P125" s="21" t="s">
@@ -17892,7 +17964,7 @@
       <c r="H126" s="14" t="s">
         <v>463</v>
       </c>
-      <c r="I126" s="47" t="s">
+      <c r="I126" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J126" s="14" t="s">
@@ -17911,7 +17983,7 @@
       <c r="N126" s="14">
         <v>1002</v>
       </c>
-      <c r="O126" s="54" t="s">
+      <c r="O126" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P126" s="15" t="s">
@@ -17947,7 +18019,7 @@
       <c r="H127" s="20" t="s">
         <v>464</v>
       </c>
-      <c r="I127" s="47" t="s">
+      <c r="I127" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J127" s="20" t="s">
@@ -17966,7 +18038,7 @@
       <c r="N127" s="20">
         <v>1005</v>
       </c>
-      <c r="O127" s="54" t="s">
+      <c r="O127" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P127" s="21" t="s">
@@ -18002,7 +18074,7 @@
       <c r="H128" s="14" t="s">
         <v>463</v>
       </c>
-      <c r="I128" s="47" t="s">
+      <c r="I128" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J128" s="14" t="s">
@@ -18021,7 +18093,7 @@
       <c r="N128" s="14">
         <v>1002</v>
       </c>
-      <c r="O128" s="54" t="s">
+      <c r="O128" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P128" s="15" t="s">
@@ -18057,7 +18129,7 @@
       <c r="H129" s="20" t="s">
         <v>465</v>
       </c>
-      <c r="I129" s="47" t="s">
+      <c r="I129" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J129" s="20" t="s">
@@ -18076,7 +18148,7 @@
       <c r="N129" s="20">
         <v>1002</v>
       </c>
-      <c r="O129" s="54" t="s">
+      <c r="O129" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P129" s="21" t="s">
@@ -18112,7 +18184,7 @@
       <c r="H130" s="14" t="s">
         <v>463</v>
       </c>
-      <c r="I130" s="47" t="s">
+      <c r="I130" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J130" s="14" t="s">
@@ -18131,7 +18203,7 @@
       <c r="N130" s="14">
         <v>1002</v>
       </c>
-      <c r="O130" s="54" t="s">
+      <c r="O130" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P130" s="15" t="s">
@@ -18167,7 +18239,7 @@
       <c r="H131" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="I131" s="47" t="s">
+      <c r="I131" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J131" s="20" t="s">
@@ -18186,7 +18258,7 @@
       <c r="N131" s="20">
         <v>1002</v>
       </c>
-      <c r="O131" s="54" t="s">
+      <c r="O131" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P131" s="21" t="s">
@@ -18222,7 +18294,7 @@
       <c r="H132" s="14" t="s">
         <v>466</v>
       </c>
-      <c r="I132" s="47" t="s">
+      <c r="I132" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J132" s="14" t="s">
@@ -18241,7 +18313,7 @@
       <c r="N132" s="14">
         <v>1001</v>
       </c>
-      <c r="O132" s="54" t="s">
+      <c r="O132" s="50" t="s">
         <v>792</v>
       </c>
       <c r="P132" s="15">
@@ -18277,7 +18349,7 @@
       <c r="H133" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="I133" s="47" t="s">
+      <c r="I133" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J133" s="20" t="s">
@@ -18296,7 +18368,7 @@
       <c r="N133" s="20">
         <v>1005</v>
       </c>
-      <c r="O133" s="54" t="s">
+      <c r="O133" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P133" s="21" t="s">
@@ -18332,7 +18404,7 @@
       <c r="H134" s="20" t="s">
         <v>467</v>
       </c>
-      <c r="I134" s="47" t="s">
+      <c r="I134" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J134" s="20" t="s">
@@ -18351,7 +18423,7 @@
       <c r="N134" s="20">
         <v>1005</v>
       </c>
-      <c r="O134" s="54" t="s">
+      <c r="O134" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P134" s="21" t="s">
@@ -18387,7 +18459,7 @@
       <c r="H135" s="14" t="s">
         <v>468</v>
       </c>
-      <c r="I135" s="47" t="s">
+      <c r="I135" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J135" s="14" t="s">
@@ -18406,7 +18478,7 @@
       <c r="N135" s="14">
         <v>2005</v>
       </c>
-      <c r="O135" s="54" t="s">
+      <c r="O135" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P135" s="15" t="s">
@@ -18418,7 +18490,7 @@
       </c>
       <c r="R135" s="14"/>
     </row>
-    <row r="136" spans="1:18" ht="36.75" thickBot="1">
+    <row r="136" spans="1:18" ht="36">
       <c r="A136" s="1"/>
       <c r="B136" s="17">
         <f t="shared" si="0"/>
@@ -18442,7 +18514,7 @@
       <c r="H136" s="20" t="s">
         <v>469</v>
       </c>
-      <c r="I136" s="47" t="s">
+      <c r="I136" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J136" s="20" t="s">
@@ -18461,23 +18533,23 @@
       <c r="N136" s="20">
         <v>1005</v>
       </c>
-      <c r="O136" s="54" t="s">
+      <c r="O136" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P136" s="21" t="s">
         <v>875</v>
       </c>
       <c r="Q136" s="21">
-        <f t="shared" ref="Q136:Q140" si="60">P136*N136</f>
+        <f t="shared" ref="Q136:Q141" si="60">P136*N136</f>
         <v>155.67450000000002</v>
       </c>
       <c r="R136" s="20"/>
     </row>
-    <row r="137" spans="1:18" ht="24.75" thickBot="1">
+    <row r="137" spans="1:18" ht="24">
       <c r="A137" s="1"/>
-      <c r="B137" s="46">
-        <f>ROW(B137) - ROW($B$2)</f>
-        <v>135</v>
+      <c r="B137" s="17">
+        <f t="shared" si="0"/>
+        <v>130</v>
       </c>
       <c r="C137" s="22" t="s">
         <v>671</v>
@@ -18485,38 +18557,38 @@
       <c r="D137" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="E137" s="47" t="s">
+      <c r="E137" s="43" t="s">
         <v>673</v>
       </c>
       <c r="F137" s="14" t="s">
         <v>674</v>
       </c>
-      <c r="G137" s="47" t="s">
+      <c r="G137" s="43" t="s">
         <v>675</v>
       </c>
       <c r="H137" s="14" t="s">
         <v>676</v>
       </c>
-      <c r="I137" s="47" t="s">
+      <c r="I137" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J137" s="20" t="s">
         <v>693</v>
       </c>
-      <c r="K137" s="47" t="s">
+      <c r="K137" s="43" t="s">
         <v>672</v>
       </c>
       <c r="L137" s="14">
         <v>2</v>
       </c>
       <c r="M137" s="14">
-        <f t="shared" ref="M137:M140" si="61">L137*1000</f>
+        <f t="shared" ref="M137:M141" si="61">L137*1000</f>
         <v>2000</v>
       </c>
       <c r="N137" s="20">
         <v>2002</v>
       </c>
-      <c r="O137" s="54" t="s">
+      <c r="O137" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P137" s="21" t="s">
@@ -18528,11 +18600,11 @@
       </c>
       <c r="R137" s="20"/>
     </row>
-    <row r="138" spans="1:18" ht="90" thickBot="1">
+    <row r="138" spans="1:18" ht="89.25">
       <c r="A138" s="1"/>
-      <c r="B138" s="46">
-        <f>ROW(B138) - ROW($B$2)</f>
-        <v>136</v>
+      <c r="B138" s="17">
+        <f t="shared" ref="B138:B141" si="62">ROW(B138) - ROW($B$7)</f>
+        <v>131</v>
       </c>
       <c r="C138" s="22" t="s">
         <v>671</v>
@@ -18540,25 +18612,27 @@
       <c r="D138" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="E138" s="47" t="s">
+      <c r="E138" s="43" t="s">
         <v>677</v>
       </c>
       <c r="F138" s="20" t="s">
         <v>674</v>
       </c>
-      <c r="G138" s="47" t="s">
+      <c r="G138" s="43" t="s">
         <v>678</v>
       </c>
       <c r="H138" s="14" t="s">
         <v>679</v>
       </c>
-      <c r="I138" s="47" t="s">
+      <c r="I138" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J138" s="20" t="s">
         <v>694</v>
       </c>
-      <c r="K138" s="47"/>
+      <c r="K138" s="43" t="s">
+        <v>672</v>
+      </c>
       <c r="L138" s="14">
         <v>1</v>
       </c>
@@ -18569,7 +18643,7 @@
       <c r="N138" s="20">
         <v>1001</v>
       </c>
-      <c r="O138" s="54" t="s">
+      <c r="O138" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P138" s="21" t="s">
@@ -18579,15 +18653,15 @@
         <f t="shared" si="60"/>
         <v>5639.634</v>
       </c>
-      <c r="R138" s="49" t="s">
+      <c r="R138" s="45" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="36.75" thickBot="1">
+    <row r="139" spans="1:18" ht="36">
       <c r="A139" s="1"/>
-      <c r="B139" s="46">
-        <f t="shared" ref="B139:B140" si="62">ROW(B139) - ROW($B$2)</f>
-        <v>137</v>
+      <c r="B139" s="17">
+        <f t="shared" si="62"/>
+        <v>132</v>
       </c>
       <c r="C139" s="22" t="s">
         <v>671</v>
@@ -18595,25 +18669,27 @@
       <c r="D139" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="E139" s="48" t="s">
+      <c r="E139" s="44" t="s">
         <v>680</v>
       </c>
       <c r="F139" s="20" t="s">
         <v>674</v>
       </c>
-      <c r="G139" s="48" t="s">
+      <c r="G139" s="44" t="s">
         <v>681</v>
       </c>
       <c r="H139" s="20" t="s">
         <v>682</v>
       </c>
-      <c r="I139" s="47" t="s">
+      <c r="I139" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J139" s="20" t="s">
         <v>695</v>
       </c>
-      <c r="K139" s="48"/>
+      <c r="K139" s="43" t="s">
+        <v>672</v>
+      </c>
       <c r="L139" s="20">
         <v>1</v>
       </c>
@@ -18624,7 +18700,7 @@
       <c r="N139" s="20">
         <v>1005</v>
       </c>
-      <c r="O139" s="54" t="s">
+      <c r="O139" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P139" s="21" t="s">
@@ -18636,11 +18712,11 @@
       </c>
       <c r="R139" s="20"/>
     </row>
-    <row r="140" spans="1:18" ht="24.75" thickBot="1">
+    <row r="140" spans="1:18" ht="24">
       <c r="A140" s="1"/>
-      <c r="B140" s="46">
+      <c r="B140" s="17">
         <f t="shared" si="62"/>
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C140" s="22" t="s">
         <v>671</v>
@@ -18648,25 +18724,27 @@
       <c r="D140" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="E140" s="48" t="s">
+      <c r="E140" s="44" t="s">
         <v>683</v>
       </c>
       <c r="F140" s="20" t="s">
         <v>674</v>
       </c>
-      <c r="G140" s="48" t="s">
+      <c r="G140" s="44" t="s">
         <v>684</v>
       </c>
       <c r="H140" s="20" t="s">
         <v>685</v>
       </c>
-      <c r="I140" s="47" t="s">
+      <c r="I140" s="43" t="s">
         <v>672</v>
       </c>
       <c r="J140" s="20" t="s">
         <v>696</v>
       </c>
-      <c r="K140" s="48"/>
+      <c r="K140" s="43" t="s">
+        <v>672</v>
+      </c>
       <c r="L140" s="20">
         <v>2</v>
       </c>
@@ -18677,7 +18755,7 @@
       <c r="N140" s="20">
         <v>2002</v>
       </c>
-      <c r="O140" s="54" t="s">
+      <c r="O140" s="50" t="s">
         <v>701</v>
       </c>
       <c r="P140" s="21" t="s">
@@ -18689,39 +18767,94 @@
       </c>
       <c r="R140" s="20"/>
     </row>
-    <row r="141" spans="1:18" ht="19.5" thickBot="1">
+    <row r="141" spans="1:18" ht="36.75" thickBot="1">
       <c r="A141" s="1"/>
-      <c r="B141" s="10"/>
-      <c r="C141" s="10"/>
-      <c r="N141" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="O141" s="44"/>
-      <c r="P141" s="44"/>
-      <c r="Q141" s="18">
-        <f>SUM(Q8:Q140)</f>
-        <v>53965.850099999996</v>
-      </c>
+      <c r="B141" s="17">
+        <f t="shared" si="62"/>
+        <v>134</v>
+      </c>
+      <c r="C141" s="22" t="s">
+        <v>671</v>
+      </c>
+      <c r="D141" s="14" t="s">
+        <v>672</v>
+      </c>
+      <c r="E141" s="44" t="s">
+        <v>880</v>
+      </c>
+      <c r="F141" s="20" t="s">
+        <v>674</v>
+      </c>
+      <c r="G141" s="44" t="s">
+        <v>881</v>
+      </c>
+      <c r="H141" s="20" t="s">
+        <v>882</v>
+      </c>
+      <c r="I141" s="43" t="s">
+        <v>672</v>
+      </c>
+      <c r="J141" s="20" t="s">
+        <v>672</v>
+      </c>
+      <c r="K141" s="44" t="s">
+        <v>672</v>
+      </c>
+      <c r="L141" s="20">
+        <v>1</v>
+      </c>
+      <c r="M141" s="14">
+        <f t="shared" si="61"/>
+        <v>1000</v>
+      </c>
+      <c r="N141" s="20">
+        <v>501</v>
+      </c>
+      <c r="O141" s="50" t="s">
+        <v>883</v>
+      </c>
+      <c r="P141" s="21">
+        <v>2.4</v>
+      </c>
+      <c r="Q141" s="21">
+        <f t="shared" si="60"/>
+        <v>1202.3999999999999</v>
+      </c>
+      <c r="R141" s="20"/>
     </row>
     <row r="142" spans="1:18" ht="19.5" thickBot="1">
       <c r="A142" s="1"/>
       <c r="B142" s="10"/>
       <c r="C142" s="10"/>
-      <c r="N142" s="43" t="s">
+      <c r="N142" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="O142" s="54"/>
+      <c r="P142" s="54"/>
+      <c r="Q142" s="18">
+        <f>SUM(Q8:Q141)</f>
+        <v>55168.250099999997</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" ht="19.5" thickBot="1">
+      <c r="A143" s="1"/>
+      <c r="B143" s="10"/>
+      <c r="C143" s="10"/>
+      <c r="N143" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="O142" s="44"/>
-      <c r="P142" s="44"/>
-      <c r="Q142" s="19">
-        <f>Q141/1000</f>
-        <v>53.965850099999997</v>
+      <c r="O143" s="54"/>
+      <c r="P143" s="54"/>
+      <c r="Q143" s="19">
+        <f>Q142/1000</f>
+        <v>55.168250099999995</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N141:P141"/>
     <mergeCell ref="N142:P142"/>
+    <mergeCell ref="N143:P143"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O8" r:id="rId1"/>
@@ -18856,6 +18989,7 @@
     <hyperlink ref="O132" r:id="rId130"/>
     <hyperlink ref="O39" r:id="rId131"/>
     <hyperlink ref="O115" r:id="rId132"/>
+    <hyperlink ref="O141" r:id="rId133" location="nav-specification"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Design-Files/OFP_MCM_v1.5/BOM/eSpark-BOM-OFP_MCM_v1.5.xlsx
+++ b/Design-Files/OFP_MCM_v1.5/BOM/eSpark-BOM-OFP_MCM_v1.5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3139" uniqueCount="885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3159" uniqueCount="888">
   <si>
     <t>Component list</t>
   </si>
@@ -2675,6 +2675,15 @@
   </si>
   <si>
     <t>R85</t>
+  </si>
+  <si>
+    <t>5 inch TFT LCD Display 800*480 RGB Interface LCD Touch Screen Panel</t>
+  </si>
+  <si>
+    <t>RGB5001</t>
+  </si>
+  <si>
+    <t>QDTFT</t>
   </si>
 </sst>
 </file>
@@ -3187,6 +3196,9 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3197,9 +3209,6 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3489,7 +3498,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R152"/>
+  <dimension ref="A1:R153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4" style="10" bestFit="1" customWidth="1"/>
@@ -3523,14 +3532,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1">
       <c r="A2" s="1"/>
@@ -8990,13 +8999,13 @@
       <c r="D104" s="42" t="s">
         <v>884</v>
       </c>
-      <c r="E104" s="55" t="s">
+      <c r="E104" s="52" t="s">
         <v>231</v>
       </c>
       <c r="F104" s="42" t="s">
         <v>304</v>
       </c>
-      <c r="G104" s="55" t="s">
+      <c r="G104" s="52" t="s">
         <v>391</v>
       </c>
       <c r="H104" s="42" t="s">
@@ -10670,7 +10679,7 @@
         <v>1</v>
       </c>
       <c r="M134" s="14">
-        <f t="shared" ref="M134:M142" si="60">L134*10</f>
+        <f t="shared" ref="M134:M143" si="60">L134*10</f>
         <v>10</v>
       </c>
       <c r="N134" s="20">
@@ -10848,7 +10857,7 @@
         <v>776</v>
       </c>
       <c r="Q137" s="21">
-        <f t="shared" ref="Q137:Q142" si="63">P137*N137</f>
+        <f t="shared" ref="Q137:Q143" si="63">P137*N137</f>
         <v>4.3424999999999994</v>
       </c>
       <c r="R137" s="20"/>
@@ -10911,7 +10920,7 @@
     <row r="139" spans="1:18" ht="51">
       <c r="A139" s="1"/>
       <c r="B139" s="17">
-        <f t="shared" ref="B139:B142" si="64">ROW(B139) - ROW($B$7)</f>
+        <f t="shared" ref="B139:B143" si="64">ROW(B139) - ROW($B$7)</f>
         <v>132</v>
       </c>
       <c r="C139" s="22" t="s">
@@ -11069,7 +11078,7 @@
       </c>
       <c r="R141" s="20"/>
     </row>
-    <row r="142" spans="1:18" ht="36.75" thickBot="1">
+    <row r="142" spans="1:18" ht="36">
       <c r="A142" s="1"/>
       <c r="B142" s="17">
         <f t="shared" si="64"/>
@@ -11110,7 +11119,7 @@
         <v>10</v>
       </c>
       <c r="N142" s="20">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O142" s="50" t="s">
         <v>881</v>
@@ -11120,45 +11129,97 @@
       </c>
       <c r="Q142" s="21">
         <f t="shared" si="63"/>
-        <v>14.399999999999999</v>
+        <v>26.4</v>
       </c>
       <c r="R142" s="20"/>
     </row>
-    <row r="143" spans="1:18" ht="19.5" thickBot="1">
+    <row r="143" spans="1:18" ht="30.75" thickBot="1">
       <c r="A143" s="1"/>
-      <c r="N143" s="53" t="s">
-        <v>3</v>
-      </c>
-      <c r="O143" s="54"/>
-      <c r="P143" s="54"/>
-      <c r="Q143" s="18">
-        <f>SUM(Q8:Q142)</f>
-        <v>894.40659999999991</v>
-      </c>
+      <c r="B143" s="17">
+        <f t="shared" si="64"/>
+        <v>136</v>
+      </c>
+      <c r="C143" s="22" t="s">
+        <v>669</v>
+      </c>
+      <c r="D143" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="E143" s="44" t="s">
+        <v>885</v>
+      </c>
+      <c r="F143" s="20" t="s">
+        <v>672</v>
+      </c>
+      <c r="G143" s="44" t="s">
+        <v>886</v>
+      </c>
+      <c r="H143" s="20" t="s">
+        <v>887</v>
+      </c>
+      <c r="I143" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J143" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="K143" s="44" t="s">
+        <v>670</v>
+      </c>
+      <c r="L143" s="20">
+        <v>1</v>
+      </c>
+      <c r="M143" s="14">
+        <f t="shared" si="60"/>
+        <v>10</v>
+      </c>
+      <c r="N143" s="20">
+        <v>11</v>
+      </c>
+      <c r="O143" s="50" t="s">
+        <v>881</v>
+      </c>
+      <c r="P143" s="21">
+        <v>9.82</v>
+      </c>
+      <c r="Q143" s="21">
+        <f t="shared" si="63"/>
+        <v>108.02000000000001</v>
+      </c>
+      <c r="R143" s="20"/>
     </row>
     <row r="144" spans="1:18" ht="19.5" thickBot="1">
       <c r="A144" s="1"/>
-      <c r="N144" s="53" t="s">
+      <c r="N144" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="O144" s="55"/>
+      <c r="P144" s="55"/>
+      <c r="Q144" s="18">
+        <f>SUM(Q8:Q143)</f>
+        <v>1014.4265999999999</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" ht="19.5" thickBot="1">
+      <c r="A145" s="1"/>
+      <c r="N145" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="O144" s="54"/>
-      <c r="P144" s="54"/>
-      <c r="Q144" s="19">
-        <f>Q143/10</f>
-        <v>89.440659999999994</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13">
-      <c r="A145" s="1"/>
-    </row>
-    <row r="152" spans="1:13">
-      <c r="M152" s="38"/>
+      <c r="O145" s="55"/>
+      <c r="P145" s="55"/>
+      <c r="Q145" s="19">
+        <f>Q144/10</f>
+        <v>101.44265999999999</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17">
+      <c r="M153" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N143:P143"/>
     <mergeCell ref="N144:P144"/>
+    <mergeCell ref="N145:P145"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O8" r:id="rId1"/>
@@ -11294,15 +11355,16 @@
     <hyperlink ref="O39" r:id="rId131"/>
     <hyperlink ref="O116" r:id="rId132"/>
     <hyperlink ref="O142" r:id="rId133" location="nav-specification"/>
+    <hyperlink ref="O143" r:id="rId134" location="nav-specification"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId134"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId135"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R144"/>
+  <dimension ref="A1:R145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
@@ -11333,14 +11395,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1">
       <c r="A2" s="1"/>
@@ -16800,13 +16862,13 @@
       <c r="D104" s="42" t="s">
         <v>884</v>
       </c>
-      <c r="E104" s="55" t="s">
+      <c r="E104" s="52" t="s">
         <v>231</v>
       </c>
       <c r="F104" s="42" t="s">
         <v>304</v>
       </c>
-      <c r="G104" s="55" t="s">
+      <c r="G104" s="52" t="s">
         <v>391</v>
       </c>
       <c r="H104" s="42" t="s">
@@ -18721,7 +18783,7 @@
     <row r="139" spans="1:18" ht="89.25">
       <c r="A139" s="1"/>
       <c r="B139" s="17">
-        <f t="shared" ref="B139:B142" si="62">ROW(B139) - ROW($B$7)</f>
+        <f t="shared" ref="B139:B143" si="62">ROW(B139) - ROW($B$7)</f>
         <v>132</v>
       </c>
       <c r="C139" s="22" t="s">
@@ -18885,7 +18947,7 @@
       </c>
       <c r="R141" s="20"/>
     </row>
-    <row r="142" spans="1:18" ht="36.75" thickBot="1">
+    <row r="142" spans="1:18" ht="36">
       <c r="A142" s="1"/>
       <c r="B142" s="17">
         <f t="shared" si="62"/>
@@ -18926,7 +18988,7 @@
         <v>1000</v>
       </c>
       <c r="N142" s="20">
-        <v>501</v>
+        <v>1001</v>
       </c>
       <c r="O142" s="50" t="s">
         <v>881</v>
@@ -18936,43 +18998,98 @@
       </c>
       <c r="Q142" s="21">
         <f t="shared" si="60"/>
-        <v>1202.3999999999999</v>
+        <v>2402.4</v>
       </c>
       <c r="R142" s="20"/>
     </row>
-    <row r="143" spans="1:18" ht="19.5" thickBot="1">
+    <row r="143" spans="1:18" ht="30.75" thickBot="1">
       <c r="A143" s="1"/>
-      <c r="B143" s="10"/>
-      <c r="C143" s="10"/>
-      <c r="N143" s="53" t="s">
-        <v>3</v>
-      </c>
-      <c r="O143" s="54"/>
-      <c r="P143" s="54"/>
-      <c r="Q143" s="18">
-        <f>SUM(Q8:Q142)</f>
-        <v>55168.250099999997</v>
-      </c>
+      <c r="B143" s="17">
+        <f t="shared" si="62"/>
+        <v>136</v>
+      </c>
+      <c r="C143" s="22" t="s">
+        <v>669</v>
+      </c>
+      <c r="D143" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="E143" s="44" t="s">
+        <v>885</v>
+      </c>
+      <c r="F143" s="20" t="s">
+        <v>672</v>
+      </c>
+      <c r="G143" s="44" t="s">
+        <v>886</v>
+      </c>
+      <c r="H143" s="20" t="s">
+        <v>887</v>
+      </c>
+      <c r="I143" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J143" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="K143" s="44" t="s">
+        <v>670</v>
+      </c>
+      <c r="L143" s="20">
+        <v>1</v>
+      </c>
+      <c r="M143" s="14">
+        <f t="shared" ref="M143" si="63">L143*1000</f>
+        <v>1000</v>
+      </c>
+      <c r="N143" s="20">
+        <v>1001</v>
+      </c>
+      <c r="O143" s="50" t="s">
+        <v>881</v>
+      </c>
+      <c r="P143" s="21">
+        <v>8.8699999999999992</v>
+      </c>
+      <c r="Q143" s="21">
+        <f t="shared" ref="Q143" si="64">P143*N143</f>
+        <v>8878.869999999999</v>
+      </c>
+      <c r="R143" s="20"/>
     </row>
     <row r="144" spans="1:18" ht="19.5" thickBot="1">
       <c r="A144" s="1"/>
       <c r="B144" s="10"/>
       <c r="C144" s="10"/>
-      <c r="N144" s="53" t="s">
+      <c r="N144" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="O144" s="55"/>
+      <c r="P144" s="55"/>
+      <c r="Q144" s="18">
+        <f>SUM(Q8:Q143)</f>
+        <v>65247.1201</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" ht="19.5" thickBot="1">
+      <c r="A145" s="1"/>
+      <c r="B145" s="10"/>
+      <c r="C145" s="10"/>
+      <c r="N145" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="O144" s="54"/>
-      <c r="P144" s="54"/>
-      <c r="Q144" s="19">
-        <f>Q143/1000</f>
-        <v>55.168250099999995</v>
+      <c r="O145" s="55"/>
+      <c r="P145" s="55"/>
+      <c r="Q145" s="19">
+        <f>Q144/1000</f>
+        <v>65.247120100000004</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N143:P143"/>
     <mergeCell ref="N144:P144"/>
+    <mergeCell ref="N145:P145"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O8" r:id="rId1"/>
@@ -19108,6 +19225,7 @@
     <hyperlink ref="O39" r:id="rId131"/>
     <hyperlink ref="O116" r:id="rId132"/>
     <hyperlink ref="O142" r:id="rId133" location="nav-specification"/>
+    <hyperlink ref="O143" r:id="rId134" location="nav-specification"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Design-Files/OFP_MCM_v1.5/BOM/eSpark-BOM-OFP_MCM_v1.5.xlsx
+++ b/Design-Files/OFP_MCM_v1.5/BOM/eSpark-BOM-OFP_MCM_v1.5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3159" uniqueCount="888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3169" uniqueCount="892">
   <si>
     <t>Component list</t>
   </si>
@@ -2684,6 +2684,18 @@
   </si>
   <si>
     <t>QDTFT</t>
+  </si>
+  <si>
+    <t>C149</t>
+  </si>
+  <si>
+    <t>CAP CER 10UF 25V X5R 0603</t>
+  </si>
+  <si>
+    <t>GRM188R61E106KA73D</t>
+  </si>
+  <si>
+    <t>C344022</t>
   </si>
 </sst>
 </file>
@@ -11364,7 +11376,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R145"/>
+  <dimension ref="A1:R146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
@@ -11624,7 +11636,7 @@
     <row r="9" spans="1:18" ht="24">
       <c r="A9" s="1"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B138" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B139" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
@@ -11658,7 +11670,7 @@
         <v>10</v>
       </c>
       <c r="M9" s="14">
-        <f t="shared" ref="M9:M72" si="1">L9*1000</f>
+        <f t="shared" ref="M9:M73" si="1">L9*1000</f>
         <v>10000</v>
       </c>
       <c r="N9" s="20">
@@ -13210,7 +13222,7 @@
       <c r="P37" s="47" t="s">
         <v>670</v>
       </c>
-      <c r="Q37" s="47" t="s">
+      <c r="Q37" s="15" t="s">
         <v>670</v>
       </c>
       <c r="R37" s="49" t="s">
@@ -13266,508 +13278,508 @@
       <c r="P38" s="48" t="s">
         <v>670</v>
       </c>
-      <c r="Q38" s="48" t="s">
+      <c r="Q38" s="15" t="s">
         <v>670</v>
       </c>
       <c r="R38" s="49" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="36">
+    <row r="39" spans="1:18">
       <c r="A39" s="1"/>
-      <c r="B39" s="17">
-        <f t="shared" si="0"/>
+      <c r="B39" s="16">
+        <f>ROW(B39) - ROW($B$7)</f>
         <v>32</v>
       </c>
-      <c r="C39" s="23" t="s">
-        <v>9</v>
+      <c r="C39" s="22" t="s">
+        <v>6</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>185</v>
+        <v>888</v>
+      </c>
+      <c r="E39" s="43" t="s">
+        <v>889</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>355</v>
+        <v>279</v>
+      </c>
+      <c r="G39" s="43" t="s">
+        <v>890</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>438</v>
-      </c>
-      <c r="I39" s="20" t="s">
+        <v>433</v>
+      </c>
+      <c r="I39" s="42" t="s">
         <v>670</v>
       </c>
       <c r="J39" s="20" t="s">
-        <v>497</v>
-      </c>
-      <c r="K39" s="20" t="s">
+        <v>891</v>
+      </c>
+      <c r="K39" s="42" t="s">
         <v>670</v>
       </c>
       <c r="L39" s="20">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M39" s="14">
         <f t="shared" si="1"/>
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="N39" s="20">
-        <v>9020</v>
+        <v>1020</v>
       </c>
       <c r="O39" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P39" s="21" t="s">
-        <v>820</v>
-      </c>
-      <c r="Q39" s="21">
-        <f t="shared" ref="Q39" si="16">P39*N39</f>
-        <v>92.004000000000005</v>
-      </c>
-      <c r="R39" s="20"/>
+      <c r="P39" s="21">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="Q39" s="15">
+        <f t="shared" ref="Q37:Q39" si="16">P39*N39</f>
+        <v>20.808</v>
+      </c>
+      <c r="R39" s="49"/>
     </row>
     <row r="40" spans="1:18" ht="36">
       <c r="A40" s="1"/>
-      <c r="B40" s="16">
-        <f>ROW(B40) - ROW($B$7)</f>
+      <c r="B40" s="17">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C40" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>439</v>
+      <c r="C40" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>438</v>
       </c>
       <c r="I40" s="20" t="s">
         <v>670</v>
       </c>
-      <c r="J40" s="14" t="s">
-        <v>498</v>
+      <c r="J40" s="20" t="s">
+        <v>497</v>
       </c>
       <c r="K40" s="20" t="s">
         <v>670</v>
       </c>
-      <c r="L40" s="14">
-        <v>1</v>
+      <c r="L40" s="20">
+        <v>9</v>
       </c>
       <c r="M40" s="14">
         <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N40" s="14">
-        <v>1020</v>
+        <v>9000</v>
+      </c>
+      <c r="N40" s="20">
+        <v>9020</v>
       </c>
       <c r="O40" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P40" s="15" t="s">
-        <v>821</v>
-      </c>
-      <c r="Q40" s="15">
-        <f>P40*N40</f>
-        <v>16.625999999999998</v>
-      </c>
-      <c r="R40" s="14"/>
-    </row>
-    <row r="41" spans="1:18" ht="25.5">
+      <c r="P40" s="21" t="s">
+        <v>820</v>
+      </c>
+      <c r="Q40" s="21">
+        <f t="shared" ref="Q40" si="17">P40*N40</f>
+        <v>92.004000000000005</v>
+      </c>
+      <c r="R40" s="20"/>
+    </row>
+    <row r="41" spans="1:18" ht="36">
       <c r="A41" s="1"/>
-      <c r="B41" s="17">
-        <f t="shared" si="0"/>
+      <c r="B41" s="16">
+        <f>ROW(B41) - ROW($B$7)</f>
         <v>34</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="E41" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="F41" s="46" t="s">
-        <v>286</v>
-      </c>
-      <c r="G41" s="46" t="s">
-        <v>357</v>
-      </c>
-      <c r="H41" s="46" t="s">
-        <v>440</v>
-      </c>
-      <c r="I41" s="46" t="s">
-        <v>670</v>
-      </c>
-      <c r="J41" s="46" t="s">
-        <v>499</v>
-      </c>
-      <c r="K41" s="46" t="s">
-        <v>607</v>
-      </c>
-      <c r="L41" s="46">
+      <c r="D41" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="I41" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>498</v>
+      </c>
+      <c r="K41" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="L41" s="14">
         <v>1</v>
       </c>
       <c r="M41" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N41" s="46" t="s">
-        <v>867</v>
+      <c r="N41" s="14">
+        <v>1020</v>
       </c>
       <c r="O41" s="50" t="s">
-        <v>670</v>
-      </c>
-      <c r="P41" s="47" t="s">
-        <v>670</v>
-      </c>
-      <c r="Q41" s="47" t="s">
-        <v>670</v>
-      </c>
-      <c r="R41" s="49" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="24">
+        <v>699</v>
+      </c>
+      <c r="P41" s="15" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q41" s="15">
+        <f>P41*N41</f>
+        <v>16.625999999999998</v>
+      </c>
+      <c r="R41" s="14"/>
+    </row>
+    <row r="42" spans="1:18" ht="25.5">
       <c r="A42" s="1"/>
-      <c r="B42" s="16">
-        <f>ROW(B42) - ROW($B$7)</f>
+      <c r="B42" s="17">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C42" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="F42" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="G42" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="I42" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="J42" s="14" t="s">
-        <v>500</v>
-      </c>
-      <c r="K42" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="L42" s="14">
-        <v>2</v>
+      <c r="C42" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="F42" s="46" t="s">
+        <v>286</v>
+      </c>
+      <c r="G42" s="46" t="s">
+        <v>357</v>
+      </c>
+      <c r="H42" s="46" t="s">
+        <v>440</v>
+      </c>
+      <c r="I42" s="46" t="s">
+        <v>670</v>
+      </c>
+      <c r="J42" s="46" t="s">
+        <v>499</v>
+      </c>
+      <c r="K42" s="46" t="s">
+        <v>607</v>
+      </c>
+      <c r="L42" s="46">
+        <v>1</v>
       </c>
       <c r="M42" s="14">
         <f t="shared" si="1"/>
-        <v>2000</v>
-      </c>
-      <c r="N42" s="14">
-        <v>2100</v>
+        <v>1000</v>
+      </c>
+      <c r="N42" s="46" t="s">
+        <v>867</v>
       </c>
       <c r="O42" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P42" s="15" t="s">
-        <v>822</v>
-      </c>
-      <c r="Q42" s="15">
-        <f>P42*N42</f>
-        <v>13.23</v>
-      </c>
-      <c r="R42" s="14"/>
-    </row>
-    <row r="43" spans="1:18" ht="36">
+        <v>670</v>
+      </c>
+      <c r="P42" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="Q42" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="R42" s="49" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="24">
       <c r="A43" s="1"/>
-      <c r="B43" s="17">
-        <f t="shared" si="0"/>
+      <c r="B43" s="16">
+        <f>ROW(B43) - ROW($B$7)</f>
         <v>36</v>
       </c>
-      <c r="C43" s="23" t="s">
-        <v>685</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>672</v>
-      </c>
-      <c r="G43" s="20">
-        <v>5027740891</v>
-      </c>
-      <c r="H43" s="20" t="s">
-        <v>441</v>
+      <c r="C43" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>433</v>
       </c>
       <c r="I43" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J43" s="20" t="s">
-        <v>689</v>
+      <c r="J43" s="14" t="s">
+        <v>500</v>
       </c>
       <c r="K43" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L43" s="20">
-        <v>1</v>
+      <c r="L43" s="14">
+        <v>2</v>
       </c>
       <c r="M43" s="14">
         <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N43" s="20">
-        <v>1002</v>
+        <v>2000</v>
+      </c>
+      <c r="N43" s="14">
+        <v>2100</v>
       </c>
       <c r="O43" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P43" s="21" t="s">
-        <v>823</v>
-      </c>
-      <c r="Q43" s="21">
-        <f t="shared" ref="Q43" si="17">P43*N43</f>
-        <v>813.32339999999999</v>
-      </c>
-      <c r="R43" s="20"/>
-    </row>
-    <row r="44" spans="1:18" ht="48">
+      <c r="P43" s="15" t="s">
+        <v>822</v>
+      </c>
+      <c r="Q43" s="15">
+        <f>P43*N43</f>
+        <v>13.23</v>
+      </c>
+      <c r="R43" s="14"/>
+    </row>
+    <row r="44" spans="1:18" ht="36">
       <c r="A44" s="1"/>
-      <c r="B44" s="16">
-        <f>ROW(B44) - ROW($B$7)</f>
+      <c r="B44" s="17">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C44" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>190</v>
+      <c r="C44" s="23" t="s">
+        <v>685</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>189</v>
       </c>
       <c r="F44" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="G44" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>442</v>
+      <c r="G44" s="20">
+        <v>5027740891</v>
+      </c>
+      <c r="H44" s="20" t="s">
+        <v>441</v>
       </c>
       <c r="I44" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J44" s="14" t="s">
-        <v>501</v>
+      <c r="J44" s="20" t="s">
+        <v>689</v>
       </c>
       <c r="K44" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="20">
         <v>1</v>
       </c>
       <c r="M44" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N44" s="14">
-        <v>1005</v>
+      <c r="N44" s="20">
+        <v>1002</v>
       </c>
       <c r="O44" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P44" s="15" t="s">
-        <v>824</v>
-      </c>
-      <c r="Q44" s="15">
-        <f>P44*N44</f>
-        <v>48.7425</v>
-      </c>
-      <c r="R44" s="14"/>
-    </row>
-    <row r="45" spans="1:18" ht="24">
+      <c r="P44" s="21" t="s">
+        <v>823</v>
+      </c>
+      <c r="Q44" s="21">
+        <f t="shared" ref="Q44" si="18">P44*N44</f>
+        <v>813.32339999999999</v>
+      </c>
+      <c r="R44" s="20"/>
+    </row>
+    <row r="45" spans="1:18" ht="48">
       <c r="A45" s="1"/>
-      <c r="B45" s="17">
-        <f t="shared" si="0"/>
+      <c r="B45" s="16">
+        <f>ROW(B45) - ROW($B$7)</f>
         <v>38</v>
       </c>
-      <c r="C45" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>191</v>
+      <c r="C45" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>190</v>
       </c>
       <c r="F45" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="G45" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="H45" s="20" t="s">
-        <v>443</v>
+      <c r="G45" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>442</v>
       </c>
       <c r="I45" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J45" s="20" t="s">
-        <v>502</v>
+      <c r="J45" s="14" t="s">
+        <v>501</v>
       </c>
       <c r="K45" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L45" s="20">
+      <c r="L45" s="14">
         <v>1</v>
       </c>
       <c r="M45" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N45" s="20">
+      <c r="N45" s="14">
         <v>1005</v>
       </c>
       <c r="O45" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P45" s="21" t="s">
-        <v>825</v>
-      </c>
-      <c r="Q45" s="21">
-        <f t="shared" ref="Q45" si="18">P45*N45</f>
-        <v>140.499</v>
-      </c>
-      <c r="R45" s="20"/>
-    </row>
-    <row r="46" spans="1:18" ht="25.5">
+      <c r="P45" s="15" t="s">
+        <v>824</v>
+      </c>
+      <c r="Q45" s="15">
+        <f>P45*N45</f>
+        <v>48.7425</v>
+      </c>
+      <c r="R45" s="14"/>
+    </row>
+    <row r="46" spans="1:18" ht="24">
       <c r="A46" s="1"/>
-      <c r="B46" s="16">
-        <f>ROW(B46) - ROW($B$7)</f>
+      <c r="B46" s="17">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C46" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>192</v>
+      <c r="C46" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>191</v>
       </c>
       <c r="F46" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="G46" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="H46" s="14" t="s">
-        <v>444</v>
+      <c r="G46" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="H46" s="20" t="s">
+        <v>443</v>
       </c>
       <c r="I46" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J46" s="14" t="s">
-        <v>503</v>
+      <c r="J46" s="20" t="s">
+        <v>502</v>
       </c>
       <c r="K46" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L46" s="14">
+      <c r="L46" s="20">
         <v>1</v>
       </c>
       <c r="M46" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N46" s="14">
-        <v>1002</v>
+      <c r="N46" s="20">
+        <v>1005</v>
       </c>
       <c r="O46" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P46" s="15" t="s">
-        <v>826</v>
-      </c>
-      <c r="Q46" s="15">
-        <f>P46*N46</f>
-        <v>177.95520000000002</v>
-      </c>
-      <c r="R46" s="14"/>
+      <c r="P46" s="21" t="s">
+        <v>825</v>
+      </c>
+      <c r="Q46" s="21">
+        <f t="shared" ref="Q46" si="19">P46*N46</f>
+        <v>140.499</v>
+      </c>
+      <c r="R46" s="20"/>
     </row>
     <row r="47" spans="1:18" ht="25.5">
       <c r="A47" s="1"/>
-      <c r="B47" s="17">
-        <f t="shared" si="0"/>
+      <c r="B47" s="16">
+        <f>ROW(B47) - ROW($B$7)</f>
         <v>40</v>
       </c>
-      <c r="C47" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>193</v>
+      <c r="C47" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>192</v>
       </c>
       <c r="F47" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="G47" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="H47" s="20" t="s">
+      <c r="G47" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="H47" s="14" t="s">
         <v>444</v>
       </c>
       <c r="I47" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J47" s="20" t="s">
-        <v>504</v>
+      <c r="J47" s="14" t="s">
+        <v>503</v>
       </c>
       <c r="K47" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L47" s="20">
-        <v>2</v>
+      <c r="L47" s="14">
+        <v>1</v>
       </c>
       <c r="M47" s="14">
         <f t="shared" si="1"/>
-        <v>2000</v>
-      </c>
-      <c r="N47" s="20">
-        <v>2005</v>
+        <v>1000</v>
+      </c>
+      <c r="N47" s="14">
+        <v>1002</v>
       </c>
       <c r="O47" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P47" s="21" t="s">
-        <v>827</v>
-      </c>
-      <c r="Q47" s="21">
-        <f t="shared" ref="Q47" si="19">P47*N47</f>
-        <v>373.13049999999998</v>
-      </c>
-      <c r="R47" s="20"/>
+      <c r="P47" s="15" t="s">
+        <v>826</v>
+      </c>
+      <c r="Q47" s="15">
+        <f>P47*N47</f>
+        <v>177.95520000000002</v>
+      </c>
+      <c r="R47" s="14"/>
     </row>
     <row r="48" spans="1:18" ht="25.5">
       <c r="A48" s="1"/>
@@ -13778,52 +13790,51 @@
       <c r="C48" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D48" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="E48" s="46" t="s">
+      <c r="D48" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" s="20" t="s">
         <v>193</v>
       </c>
       <c r="F48" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="G48" s="46" t="s">
+      <c r="G48" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="H48" s="46" t="s">
+      <c r="H48" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="I48" s="46" t="s">
-        <v>670</v>
-      </c>
-      <c r="J48" s="46" t="s">
+      <c r="I48" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="J48" s="20" t="s">
         <v>504</v>
       </c>
-      <c r="K48" s="46" t="s">
-        <v>607</v>
-      </c>
-      <c r="L48" s="46">
-        <v>1</v>
+      <c r="K48" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="L48" s="20">
+        <v>2</v>
       </c>
       <c r="M48" s="14">
         <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N48" s="46" t="s">
-        <v>867</v>
+        <v>2000</v>
+      </c>
+      <c r="N48" s="20">
+        <v>2005</v>
       </c>
       <c r="O48" s="50" t="s">
-        <v>670</v>
-      </c>
-      <c r="P48" s="47" t="s">
-        <v>670</v>
-      </c>
-      <c r="Q48" s="47" t="s">
-        <v>670</v>
-      </c>
-      <c r="R48" s="49" t="s">
-        <v>686</v>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="P48" s="21" t="s">
+        <v>827</v>
+      </c>
+      <c r="Q48" s="21">
+        <f t="shared" ref="Q48" si="20">P48*N48</f>
+        <v>373.13049999999998</v>
+      </c>
+      <c r="R48" s="20"/>
     </row>
     <row r="49" spans="1:18" ht="25.5">
       <c r="A49" s="1"/>
@@ -13832,86 +13843,87 @@
         <v>42</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D49" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E49" s="20" t="s">
-        <v>194</v>
+        <v>15</v>
+      </c>
+      <c r="D49" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" s="46" t="s">
+        <v>193</v>
       </c>
       <c r="F49" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="G49" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="H49" s="20" t="s">
-        <v>445</v>
-      </c>
-      <c r="I49" s="20" t="s">
-        <v>670</v>
-      </c>
-      <c r="J49" s="20" t="s">
-        <v>505</v>
-      </c>
-      <c r="K49" s="20" t="s">
-        <v>670</v>
-      </c>
-      <c r="L49" s="20">
+      <c r="G49" s="46" t="s">
+        <v>291</v>
+      </c>
+      <c r="H49" s="46" t="s">
+        <v>444</v>
+      </c>
+      <c r="I49" s="46" t="s">
+        <v>670</v>
+      </c>
+      <c r="J49" s="46" t="s">
+        <v>504</v>
+      </c>
+      <c r="K49" s="46" t="s">
+        <v>607</v>
+      </c>
+      <c r="L49" s="46">
         <v>1</v>
       </c>
       <c r="M49" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N49" s="20">
-        <v>1005</v>
+      <c r="N49" s="46" t="s">
+        <v>867</v>
       </c>
       <c r="O49" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P49" s="21" t="s">
-        <v>828</v>
-      </c>
-      <c r="Q49" s="21">
-        <f t="shared" ref="Q49:Q50" si="20">P49*N49</f>
-        <v>57.1845</v>
-      </c>
-      <c r="R49" s="20"/>
-    </row>
-    <row r="50" spans="1:18">
+        <v>670</v>
+      </c>
+      <c r="P49" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="Q49" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="R49" s="49" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="25.5">
       <c r="A50" s="1"/>
       <c r="B50" s="17">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F50" s="20" t="s">
         <v>672</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I50" s="20" t="s">
         <v>670</v>
       </c>
       <c r="J50" s="20" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K50" s="20" t="s">
-        <v>608</v>
+        <v>670</v>
       </c>
       <c r="L50" s="20">
         <v>1</v>
@@ -13921,2934 +13933,2933 @@
         <v>1000</v>
       </c>
       <c r="N50" s="20">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="O50" s="50" t="s">
         <v>699</v>
       </c>
       <c r="P50" s="21" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="Q50" s="21">
-        <f t="shared" si="20"/>
-        <v>343.98660000000001</v>
+        <f t="shared" ref="Q50:Q51" si="21">P50*N50</f>
+        <v>57.1845</v>
       </c>
       <c r="R50" s="20"/>
     </row>
-    <row r="51" spans="1:18" ht="24">
+    <row r="51" spans="1:18">
       <c r="A51" s="1"/>
-      <c r="B51" s="16">
-        <f>ROW(B51) - ROW($B$7)</f>
+      <c r="B51" s="17">
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C51" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E51" s="14" t="s">
-        <v>196</v>
+      <c r="C51" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>195</v>
       </c>
       <c r="F51" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="G51" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="H51" s="14" t="s">
-        <v>447</v>
+      <c r="G51" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="H51" s="20" t="s">
+        <v>446</v>
       </c>
       <c r="I51" s="20" t="s">
         <v>670</v>
       </c>
-      <c r="J51" s="14" t="s">
-        <v>507</v>
-      </c>
-      <c r="K51" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="L51" s="14">
-        <v>3</v>
+      <c r="J51" s="20" t="s">
+        <v>506</v>
+      </c>
+      <c r="K51" s="20" t="s">
+        <v>608</v>
+      </c>
+      <c r="L51" s="20">
+        <v>1</v>
       </c>
       <c r="M51" s="14">
         <f t="shared" si="1"/>
-        <v>3000</v>
-      </c>
-      <c r="N51" s="14">
-        <v>3010</v>
+        <v>1000</v>
+      </c>
+      <c r="N51" s="20">
+        <v>1002</v>
       </c>
       <c r="O51" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P51" s="15" t="s">
-        <v>736</v>
-      </c>
-      <c r="Q51" s="15">
-        <f>P51*N51</f>
-        <v>101.437</v>
-      </c>
-      <c r="R51" s="14"/>
-    </row>
-    <row r="52" spans="1:18">
+      <c r="P51" s="21" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q51" s="21">
+        <f t="shared" si="21"/>
+        <v>343.98660000000001</v>
+      </c>
+      <c r="R51" s="20"/>
+    </row>
+    <row r="52" spans="1:18" ht="24">
       <c r="A52" s="1"/>
-      <c r="B52" s="17">
-        <f t="shared" si="0"/>
+      <c r="B52" s="16">
+        <f>ROW(B52) - ROW($B$7)</f>
         <v>45</v>
       </c>
       <c r="C52" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E52" s="20" t="s">
-        <v>197</v>
+      <c r="D52" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>196</v>
       </c>
       <c r="F52" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="G52" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="H52" s="20" t="s">
-        <v>448</v>
+      <c r="G52" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="H52" s="14" t="s">
+        <v>447</v>
       </c>
       <c r="I52" s="20" t="s">
         <v>670</v>
       </c>
-      <c r="J52" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="K52" s="20" t="s">
+      <c r="J52" s="14" t="s">
+        <v>507</v>
+      </c>
+      <c r="K52" s="14" t="s">
         <v>609</v>
       </c>
-      <c r="L52" s="20">
-        <v>1</v>
+      <c r="L52" s="14">
+        <v>3</v>
       </c>
       <c r="M52" s="14">
         <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N52" s="20">
-        <v>1005</v>
+        <v>3000</v>
+      </c>
+      <c r="N52" s="14">
+        <v>3010</v>
       </c>
       <c r="O52" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P52" s="21" t="s">
-        <v>830</v>
-      </c>
-      <c r="Q52" s="21">
-        <f t="shared" ref="Q52" si="21">P52*N52</f>
-        <v>157.584</v>
-      </c>
-      <c r="R52" s="20"/>
-    </row>
-    <row r="53" spans="1:18" ht="24">
+      <c r="P52" s="15" t="s">
+        <v>736</v>
+      </c>
+      <c r="Q52" s="15">
+        <f>P52*N52</f>
+        <v>101.437</v>
+      </c>
+      <c r="R52" s="14"/>
+    </row>
+    <row r="53" spans="1:18">
       <c r="A53" s="1"/>
-      <c r="B53" s="16">
-        <f>ROW(B53) - ROW($B$7)</f>
+      <c r="B53" s="17">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="C53" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D53" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>198</v>
+      <c r="D53" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>197</v>
       </c>
       <c r="F53" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="G53" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="H53" s="14" t="s">
-        <v>449</v>
+      <c r="G53" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="H53" s="20" t="s">
+        <v>448</v>
       </c>
       <c r="I53" s="20" t="s">
         <v>670</v>
       </c>
-      <c r="J53" s="14" t="s">
-        <v>509</v>
-      </c>
-      <c r="K53" s="14" t="s">
-        <v>610</v>
-      </c>
-      <c r="L53" s="14">
+      <c r="J53" s="20" t="s">
+        <v>508</v>
+      </c>
+      <c r="K53" s="20" t="s">
+        <v>609</v>
+      </c>
+      <c r="L53" s="20">
         <v>1</v>
       </c>
       <c r="M53" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N53" s="14">
-        <v>1010</v>
+      <c r="N53" s="20">
+        <v>1005</v>
       </c>
       <c r="O53" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P53" s="15" t="s">
-        <v>831</v>
-      </c>
-      <c r="Q53" s="15">
-        <f>P53*N53</f>
-        <v>41.410000000000004</v>
-      </c>
-      <c r="R53" s="14"/>
-    </row>
-    <row r="54" spans="1:18" ht="25.5">
+      <c r="P53" s="21" t="s">
+        <v>830</v>
+      </c>
+      <c r="Q53" s="21">
+        <f t="shared" ref="Q53" si="22">P53*N53</f>
+        <v>157.584</v>
+      </c>
+      <c r="R53" s="20"/>
+    </row>
+    <row r="54" spans="1:18" ht="24">
       <c r="A54" s="1"/>
-      <c r="B54" s="17">
-        <f t="shared" si="0"/>
+      <c r="B54" s="16">
+        <f>ROW(B54) - ROW($B$7)</f>
         <v>47</v>
       </c>
-      <c r="C54" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D54" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="E54" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="F54" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="G54" s="46" t="s">
-        <v>360</v>
-      </c>
-      <c r="H54" s="46" t="s">
-        <v>433</v>
-      </c>
-      <c r="I54" s="46" t="s">
-        <v>670</v>
-      </c>
-      <c r="J54" s="46" t="s">
-        <v>510</v>
-      </c>
-      <c r="K54" s="46" t="s">
-        <v>607</v>
-      </c>
-      <c r="L54" s="46">
+      <c r="C54" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="F54" s="20" t="s">
+        <v>672</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="H54" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="I54" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="J54" s="14" t="s">
+        <v>509</v>
+      </c>
+      <c r="K54" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="L54" s="14">
         <v>1</v>
       </c>
       <c r="M54" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N54" s="46" t="s">
-        <v>867</v>
+      <c r="N54" s="14">
+        <v>1010</v>
       </c>
       <c r="O54" s="50" t="s">
-        <v>670</v>
-      </c>
-      <c r="P54" s="47" t="s">
-        <v>670</v>
-      </c>
-      <c r="Q54" s="47" t="s">
-        <v>670</v>
-      </c>
-      <c r="R54" s="49" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" ht="24">
+        <v>699</v>
+      </c>
+      <c r="P54" s="15" t="s">
+        <v>831</v>
+      </c>
+      <c r="Q54" s="15">
+        <f>P54*N54</f>
+        <v>41.410000000000004</v>
+      </c>
+      <c r="R54" s="14"/>
+    </row>
+    <row r="55" spans="1:18" ht="25.5">
       <c r="A55" s="1"/>
-      <c r="B55" s="16">
-        <f>ROW(B55) - ROW($B$7)</f>
+      <c r="B55" s="17">
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C55" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="F55" s="14" t="s">
-        <v>296</v>
-      </c>
-      <c r="G55" s="14" t="s">
-        <v>361</v>
-      </c>
-      <c r="H55" s="14" t="s">
-        <v>450</v>
-      </c>
-      <c r="I55" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="J55" s="14" t="s">
-        <v>511</v>
-      </c>
-      <c r="K55" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="L55" s="14">
+      <c r="C55" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="E55" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="F55" s="46" t="s">
+        <v>287</v>
+      </c>
+      <c r="G55" s="46" t="s">
+        <v>360</v>
+      </c>
+      <c r="H55" s="46" t="s">
+        <v>433</v>
+      </c>
+      <c r="I55" s="46" t="s">
+        <v>670</v>
+      </c>
+      <c r="J55" s="46" t="s">
+        <v>510</v>
+      </c>
+      <c r="K55" s="46" t="s">
+        <v>607</v>
+      </c>
+      <c r="L55" s="46">
         <v>1</v>
       </c>
       <c r="M55" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N55" s="14">
-        <v>1010</v>
+      <c r="N55" s="46" t="s">
+        <v>867</v>
       </c>
       <c r="O55" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P55" s="15" t="s">
-        <v>832</v>
-      </c>
-      <c r="Q55" s="15">
-        <f>P55*N55</f>
-        <v>21.917000000000002</v>
-      </c>
-      <c r="R55" s="14"/>
-    </row>
-    <row r="56" spans="1:18" ht="48">
+        <v>670</v>
+      </c>
+      <c r="P55" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="Q55" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="R55" s="49" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="24">
       <c r="A56" s="1"/>
-      <c r="B56" s="17">
-        <f t="shared" si="0"/>
+      <c r="B56" s="16">
+        <f>ROW(B56) - ROW($B$7)</f>
         <v>49</v>
       </c>
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D56" s="20" t="s">
-        <v>667</v>
-      </c>
-      <c r="E56" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="F56" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="G56" s="20" t="s">
-        <v>362</v>
-      </c>
-      <c r="H56" s="20" t="s">
-        <v>451</v>
+      <c r="D56" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="F56" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="G56" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="H56" s="14" t="s">
+        <v>450</v>
       </c>
       <c r="I56" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J56" s="20" t="s">
-        <v>512</v>
+      <c r="J56" s="14" t="s">
+        <v>511</v>
       </c>
       <c r="K56" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L56" s="20">
-        <v>5</v>
+      <c r="L56" s="14">
+        <v>1</v>
       </c>
       <c r="M56" s="14">
         <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="N56" s="20">
-        <v>5020</v>
+        <v>1000</v>
+      </c>
+      <c r="N56" s="14">
+        <v>1010</v>
       </c>
       <c r="O56" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P56" s="21" t="s">
-        <v>833</v>
-      </c>
-      <c r="Q56" s="21">
-        <f t="shared" ref="Q56" si="22">P56*N56</f>
-        <v>69.777999999999992</v>
-      </c>
-      <c r="R56" s="20"/>
-    </row>
-    <row r="57" spans="1:18" ht="24">
+      <c r="P56" s="15" t="s">
+        <v>832</v>
+      </c>
+      <c r="Q56" s="15">
+        <f>P56*N56</f>
+        <v>21.917000000000002</v>
+      </c>
+      <c r="R56" s="14"/>
+    </row>
+    <row r="57" spans="1:18" ht="48">
       <c r="A57" s="1"/>
-      <c r="B57" s="16">
-        <f>ROW(B57) - ROW($B$7)</f>
+      <c r="B57" s="17">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="D57" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E57" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="F57" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G57" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="H57" s="14" t="s">
-        <v>452</v>
+      <c r="D57" s="20" t="s">
+        <v>667</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="F57" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="G57" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="H57" s="20" t="s">
+        <v>451</v>
       </c>
       <c r="I57" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J57" s="14" t="s">
-        <v>513</v>
+      <c r="J57" s="20" t="s">
+        <v>512</v>
       </c>
       <c r="K57" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L57" s="14">
-        <v>2</v>
+      <c r="L57" s="20">
+        <v>5</v>
       </c>
       <c r="M57" s="14">
         <f t="shared" si="1"/>
-        <v>2000</v>
-      </c>
-      <c r="N57" s="14">
-        <v>2020</v>
+        <v>5000</v>
+      </c>
+      <c r="N57" s="20">
+        <v>5020</v>
       </c>
       <c r="O57" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P57" s="15" t="s">
-        <v>834</v>
-      </c>
-      <c r="Q57" s="15">
-        <f>P57*N57</f>
-        <v>38.380000000000003</v>
-      </c>
-      <c r="R57" s="14"/>
+      <c r="P57" s="21" t="s">
+        <v>833</v>
+      </c>
+      <c r="Q57" s="21">
+        <f t="shared" ref="Q57" si="23">P57*N57</f>
+        <v>69.777999999999992</v>
+      </c>
+      <c r="R57" s="20"/>
     </row>
     <row r="58" spans="1:18" ht="24">
       <c r="A58" s="1"/>
-      <c r="B58" s="17">
-        <f t="shared" si="0"/>
+      <c r="B58" s="16">
+        <f>ROW(B58) - ROW($B$7)</f>
         <v>51</v>
       </c>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D58" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="E58" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="F58" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="G58" s="20" t="s">
-        <v>364</v>
-      </c>
-      <c r="H58" s="20" t="s">
+      <c r="D58" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F58" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="H58" s="14" t="s">
         <v>452</v>
       </c>
       <c r="I58" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J58" s="20" t="s">
-        <v>514</v>
+      <c r="J58" s="14" t="s">
+        <v>513</v>
       </c>
       <c r="K58" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L58" s="20">
-        <v>1</v>
+      <c r="L58" s="14">
+        <v>2</v>
       </c>
       <c r="M58" s="14">
         <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N58" s="20">
-        <v>1020</v>
+        <v>2000</v>
+      </c>
+      <c r="N58" s="14">
+        <v>2020</v>
       </c>
       <c r="O58" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P58" s="21" t="s">
-        <v>835</v>
-      </c>
-      <c r="Q58" s="21">
-        <f t="shared" ref="Q58" si="23">P58*N58</f>
-        <v>23.868000000000002</v>
-      </c>
-      <c r="R58" s="20"/>
-    </row>
-    <row r="59" spans="1:18" ht="48">
+      <c r="P58" s="15" t="s">
+        <v>834</v>
+      </c>
+      <c r="Q58" s="15">
+        <f>P58*N58</f>
+        <v>38.380000000000003</v>
+      </c>
+      <c r="R58" s="14"/>
+    </row>
+    <row r="59" spans="1:18" ht="24">
       <c r="A59" s="1"/>
-      <c r="B59" s="16">
-        <f>ROW(B59) - ROW($B$7)</f>
+      <c r="B59" s="17">
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C59" s="22" t="s">
+      <c r="C59" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="D59" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="F59" s="14" t="s">
-        <v>297</v>
-      </c>
-      <c r="G59" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="H59" s="14" t="s">
-        <v>451</v>
+      <c r="D59" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="F59" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="G59" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="H59" s="20" t="s">
+        <v>452</v>
       </c>
       <c r="I59" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J59" s="14" t="s">
-        <v>515</v>
+      <c r="J59" s="20" t="s">
+        <v>514</v>
       </c>
       <c r="K59" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L59" s="14">
+      <c r="L59" s="20">
         <v>1</v>
       </c>
       <c r="M59" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N59" s="14">
+      <c r="N59" s="20">
         <v>1020</v>
       </c>
       <c r="O59" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P59" s="15" t="s">
-        <v>812</v>
-      </c>
-      <c r="Q59" s="15">
-        <f>P59*N59</f>
-        <v>17.033999999999999</v>
-      </c>
-      <c r="R59" s="14"/>
-    </row>
-    <row r="60" spans="1:18" ht="36">
+      <c r="P59" s="21" t="s">
+        <v>835</v>
+      </c>
+      <c r="Q59" s="21">
+        <f t="shared" ref="Q59" si="24">P59*N59</f>
+        <v>23.868000000000002</v>
+      </c>
+      <c r="R59" s="20"/>
+    </row>
+    <row r="60" spans="1:18" ht="48">
       <c r="A60" s="1"/>
-      <c r="B60" s="17">
-        <f t="shared" si="0"/>
+      <c r="B60" s="16">
+        <f>ROW(B60) - ROW($B$7)</f>
         <v>53</v>
       </c>
-      <c r="C60" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D60" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E60" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="F60" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="G60" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="H60" s="20" t="s">
-        <v>453</v>
+      <c r="C60" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F60" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="G60" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="H60" s="14" t="s">
+        <v>451</v>
       </c>
       <c r="I60" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J60" s="20" t="s">
-        <v>516</v>
+      <c r="J60" s="14" t="s">
+        <v>515</v>
       </c>
       <c r="K60" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L60" s="20">
+      <c r="L60" s="14">
         <v>1</v>
       </c>
       <c r="M60" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N60" s="20">
-        <v>1002</v>
+      <c r="N60" s="14">
+        <v>1020</v>
       </c>
       <c r="O60" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P60" s="21" t="s">
-        <v>836</v>
-      </c>
-      <c r="Q60" s="21">
-        <f t="shared" ref="Q60" si="24">P60*N60</f>
-        <v>223.1454</v>
-      </c>
-      <c r="R60" s="20"/>
-    </row>
-    <row r="61" spans="1:18">
+      <c r="P60" s="15" t="s">
+        <v>812</v>
+      </c>
+      <c r="Q60" s="15">
+        <f>P60*N60</f>
+        <v>17.033999999999999</v>
+      </c>
+      <c r="R60" s="14"/>
+    </row>
+    <row r="61" spans="1:18" ht="36">
       <c r="A61" s="1"/>
-      <c r="B61" s="16">
-        <f>ROW(B61) - ROW($B$7)</f>
+      <c r="B61" s="17">
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C61" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E61" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="F61" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="G61" s="14" t="s">
-        <v>366</v>
-      </c>
-      <c r="H61" s="14" t="s">
-        <v>440</v>
+      <c r="C61" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="G61" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>453</v>
       </c>
       <c r="I61" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J61" s="14" t="s">
-        <v>517</v>
+      <c r="J61" s="20" t="s">
+        <v>516</v>
       </c>
       <c r="K61" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L61" s="14">
+      <c r="L61" s="20">
         <v>1</v>
       </c>
       <c r="M61" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N61" s="14">
-        <v>1020</v>
+      <c r="N61" s="20">
+        <v>1002</v>
       </c>
       <c r="O61" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P61" s="15" t="s">
-        <v>837</v>
-      </c>
-      <c r="Q61" s="15">
-        <f>P61*N61</f>
-        <v>12.24</v>
-      </c>
-      <c r="R61" s="14"/>
+      <c r="P61" s="21" t="s">
+        <v>836</v>
+      </c>
+      <c r="Q61" s="21">
+        <f t="shared" ref="Q61" si="25">P61*N61</f>
+        <v>223.1454</v>
+      </c>
+      <c r="R61" s="20"/>
     </row>
     <row r="62" spans="1:18">
       <c r="A62" s="1"/>
-      <c r="B62" s="17">
-        <f t="shared" si="0"/>
+      <c r="B62" s="16">
+        <f>ROW(B62) - ROW($B$7)</f>
         <v>55</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D62" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E62" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="F62" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="G62" s="20" t="s">
-        <v>367</v>
-      </c>
-      <c r="H62" s="20" t="s">
-        <v>454</v>
+      <c r="D62" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E62" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="F62" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="G62" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>440</v>
       </c>
       <c r="I62" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J62" s="20" t="s">
-        <v>518</v>
+      <c r="J62" s="14" t="s">
+        <v>517</v>
       </c>
       <c r="K62" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L62" s="20">
-        <v>6</v>
+      <c r="L62" s="14">
+        <v>1</v>
       </c>
       <c r="M62" s="14">
         <f t="shared" si="1"/>
-        <v>6000</v>
-      </c>
-      <c r="N62" s="20">
-        <v>6020</v>
+        <v>1000</v>
+      </c>
+      <c r="N62" s="14">
+        <v>1020</v>
       </c>
       <c r="O62" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P62" s="21" t="s">
-        <v>838</v>
-      </c>
-      <c r="Q62" s="21">
-        <f t="shared" ref="Q62" si="25">P62*N62</f>
-        <v>71.638000000000005</v>
-      </c>
-      <c r="R62" s="20"/>
+      <c r="P62" s="15" t="s">
+        <v>837</v>
+      </c>
+      <c r="Q62" s="15">
+        <f>P62*N62</f>
+        <v>12.24</v>
+      </c>
+      <c r="R62" s="14"/>
     </row>
     <row r="63" spans="1:18">
       <c r="A63" s="1"/>
-      <c r="B63" s="16">
-        <f>ROW(B63) - ROW($B$7)</f>
+      <c r="B63" s="17">
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C63" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E63" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="F63" s="14" t="s">
-        <v>303</v>
-      </c>
-      <c r="G63" s="14" t="s">
-        <v>368</v>
-      </c>
-      <c r="H63" s="14" t="s">
-        <v>436</v>
+      <c r="C63" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="F63" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="G63" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="H63" s="20" t="s">
+        <v>454</v>
       </c>
       <c r="I63" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J63" s="14" t="s">
-        <v>519</v>
+      <c r="J63" s="20" t="s">
+        <v>518</v>
       </c>
       <c r="K63" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="L63" s="14">
-        <v>7</v>
+        <v>670</v>
+      </c>
+      <c r="L63" s="20">
+        <v>6</v>
       </c>
       <c r="M63" s="14">
         <f t="shared" si="1"/>
-        <v>7000</v>
-      </c>
-      <c r="N63" s="14">
-        <v>7100</v>
+        <v>6000</v>
+      </c>
+      <c r="N63" s="20">
+        <v>6020</v>
       </c>
       <c r="O63" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P63" s="15" t="s">
-        <v>839</v>
-      </c>
-      <c r="Q63" s="15">
-        <f>P63*N63</f>
-        <v>3.5500000000000003</v>
-      </c>
-      <c r="R63" s="14"/>
+      <c r="P63" s="21" t="s">
+        <v>838</v>
+      </c>
+      <c r="Q63" s="21">
+        <f t="shared" ref="Q63" si="26">P63*N63</f>
+        <v>71.638000000000005</v>
+      </c>
+      <c r="R63" s="20"/>
     </row>
     <row r="64" spans="1:18">
       <c r="A64" s="1"/>
-      <c r="B64" s="17">
-        <f t="shared" si="0"/>
+      <c r="B64" s="16">
+        <f>ROW(B64) - ROW($B$7)</f>
         <v>57</v>
       </c>
       <c r="C64" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D64" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E64" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="F64" s="20" t="s">
+      <c r="D64" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E64" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="F64" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="G64" s="20" t="s">
-        <v>369</v>
-      </c>
-      <c r="H64" s="20" t="s">
+      <c r="G64" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="H64" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I64" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J64" s="20" t="s">
-        <v>520</v>
-      </c>
-      <c r="K64" s="20" t="s">
-        <v>612</v>
-      </c>
-      <c r="L64" s="20">
-        <v>1</v>
+      <c r="J64" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="K64" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="L64" s="14">
+        <v>7</v>
       </c>
       <c r="M64" s="14">
         <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N64" s="20">
-        <v>1100</v>
+        <v>7000</v>
+      </c>
+      <c r="N64" s="14">
+        <v>7100</v>
       </c>
       <c r="O64" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P64" s="21" t="s">
-        <v>719</v>
-      </c>
-      <c r="Q64" s="21">
-        <f t="shared" ref="Q64" si="26">P64*N64</f>
-        <v>1.21</v>
-      </c>
-      <c r="R64" s="20"/>
+      <c r="P64" s="15" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q64" s="15">
+        <f>P64*N64</f>
+        <v>3.5500000000000003</v>
+      </c>
+      <c r="R64" s="14"/>
     </row>
     <row r="65" spans="1:18">
       <c r="A65" s="1"/>
-      <c r="B65" s="16">
-        <f>ROW(B65) - ROW($B$7)</f>
+      <c r="B65" s="17">
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D65" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="E65" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="F65" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D65" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="F65" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="G65" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="H65" s="14" t="s">
+      <c r="G65" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="H65" s="20" t="s">
         <v>436</v>
       </c>
       <c r="I65" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J65" s="14" t="s">
-        <v>521</v>
-      </c>
-      <c r="K65" s="14" t="s">
-        <v>613</v>
-      </c>
-      <c r="L65" s="14">
+      <c r="J65" s="20" t="s">
+        <v>520</v>
+      </c>
+      <c r="K65" s="20" t="s">
+        <v>612</v>
+      </c>
+      <c r="L65" s="20">
         <v>1</v>
       </c>
       <c r="M65" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N65" s="14">
+      <c r="N65" s="20">
         <v>1100</v>
       </c>
       <c r="O65" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P65" s="15" t="s">
-        <v>839</v>
-      </c>
-      <c r="Q65" s="15">
-        <f>P65*N65</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="R65" s="14"/>
+      <c r="P65" s="21" t="s">
+        <v>719</v>
+      </c>
+      <c r="Q65" s="21">
+        <f t="shared" ref="Q65" si="27">P65*N65</f>
+        <v>1.21</v>
+      </c>
+      <c r="R65" s="20"/>
     </row>
     <row r="66" spans="1:18">
       <c r="A66" s="1"/>
-      <c r="B66" s="17">
-        <f t="shared" si="0"/>
+      <c r="B66" s="16">
+        <f>ROW(B66) - ROW($B$7)</f>
         <v>59</v>
       </c>
-      <c r="C66" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D66" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="E66" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="F66" s="20" t="s">
+      <c r="C66" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E66" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="F66" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="G66" s="20" t="s">
-        <v>371</v>
-      </c>
-      <c r="H66" s="20" t="s">
+      <c r="G66" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="H66" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I66" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J66" s="20" t="s">
-        <v>522</v>
-      </c>
-      <c r="K66" s="20" t="s">
-        <v>614</v>
-      </c>
-      <c r="L66" s="20">
+      <c r="J66" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="K66" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="L66" s="14">
         <v>1</v>
       </c>
       <c r="M66" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N66" s="20">
+      <c r="N66" s="14">
         <v>1100</v>
       </c>
       <c r="O66" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P66" s="21" t="s">
-        <v>840</v>
-      </c>
-      <c r="Q66" s="21">
-        <f t="shared" ref="Q66" si="27">P66*N66</f>
-        <v>0.44</v>
-      </c>
-      <c r="R66" s="20"/>
+      <c r="P66" s="15" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q66" s="15">
+        <f>P66*N66</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="R66" s="14"/>
     </row>
     <row r="67" spans="1:18">
       <c r="A67" s="1"/>
-      <c r="B67" s="16">
-        <f>ROW(B67) - ROW($B$7)</f>
+      <c r="B67" s="17">
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C67" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="E67" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="F67" s="14" t="s">
+      <c r="C67" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D67" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="F67" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="G67" s="14" t="s">
-        <v>372</v>
-      </c>
-      <c r="H67" s="14" t="s">
+      <c r="G67" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="H67" s="20" t="s">
         <v>436</v>
       </c>
       <c r="I67" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J67" s="14" t="s">
-        <v>523</v>
-      </c>
-      <c r="K67" s="14" t="s">
-        <v>615</v>
-      </c>
-      <c r="L67" s="14">
+      <c r="J67" s="20" t="s">
+        <v>522</v>
+      </c>
+      <c r="K67" s="20" t="s">
+        <v>614</v>
+      </c>
+      <c r="L67" s="20">
         <v>1</v>
       </c>
       <c r="M67" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N67" s="14">
-        <v>1020</v>
+      <c r="N67" s="20">
+        <v>1100</v>
       </c>
       <c r="O67" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P67" s="15" t="s">
-        <v>821</v>
-      </c>
-      <c r="Q67" s="15">
-        <f>P67*N67</f>
-        <v>16.625999999999998</v>
-      </c>
-      <c r="R67" s="14"/>
+      <c r="P67" s="21" t="s">
+        <v>840</v>
+      </c>
+      <c r="Q67" s="21">
+        <f t="shared" ref="Q67" si="28">P67*N67</f>
+        <v>0.44</v>
+      </c>
+      <c r="R67" s="20"/>
     </row>
     <row r="68" spans="1:18">
       <c r="A68" s="1"/>
-      <c r="B68" s="17">
-        <f t="shared" si="0"/>
+      <c r="B68" s="16">
+        <f>ROW(B68) - ROW($B$7)</f>
         <v>61</v>
       </c>
-      <c r="C68" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D68" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E68" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="F68" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="G68" s="20" t="s">
-        <v>373</v>
-      </c>
-      <c r="H68" s="20" t="s">
+      <c r="C68" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E68" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="F68" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="G68" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="H68" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I68" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J68" s="20" t="s">
-        <v>524</v>
-      </c>
-      <c r="K68" s="20" t="s">
-        <v>616</v>
-      </c>
-      <c r="L68" s="20">
+      <c r="J68" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="K68" s="14" t="s">
+        <v>615</v>
+      </c>
+      <c r="L68" s="14">
         <v>1</v>
       </c>
       <c r="M68" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N68" s="20">
-        <v>1100</v>
+      <c r="N68" s="14">
+        <v>1020</v>
       </c>
       <c r="O68" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P68" s="21" t="s">
-        <v>841</v>
-      </c>
-      <c r="Q68" s="21">
-        <f t="shared" ref="Q68" si="28">P68*N68</f>
-        <v>0.99</v>
-      </c>
-      <c r="R68" s="20"/>
+      <c r="P68" s="15" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q68" s="15">
+        <f>P68*N68</f>
+        <v>16.625999999999998</v>
+      </c>
+      <c r="R68" s="14"/>
     </row>
     <row r="69" spans="1:18">
       <c r="A69" s="1"/>
-      <c r="B69" s="16">
-        <f>ROW(B69) - ROW($B$7)</f>
+      <c r="B69" s="17">
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C69" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E69" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="F69" s="14" t="s">
-        <v>303</v>
-      </c>
-      <c r="G69" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="H69" s="14" t="s">
+      <c r="C69" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D69" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="F69" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="G69" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="H69" s="20" t="s">
         <v>436</v>
       </c>
       <c r="I69" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J69" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="K69" s="14" t="s">
-        <v>617</v>
-      </c>
-      <c r="L69" s="14">
+      <c r="J69" s="20" t="s">
+        <v>524</v>
+      </c>
+      <c r="K69" s="20" t="s">
+        <v>616</v>
+      </c>
+      <c r="L69" s="20">
         <v>1</v>
       </c>
       <c r="M69" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N69" s="14">
-        <v>1020</v>
+      <c r="N69" s="20">
+        <v>1100</v>
       </c>
       <c r="O69" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P69" s="15" t="s">
-        <v>842</v>
-      </c>
-      <c r="Q69" s="15">
-        <f>P69*N69</f>
-        <v>15.504</v>
-      </c>
-      <c r="R69" s="14"/>
+      <c r="P69" s="21" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q69" s="21">
+        <f t="shared" ref="Q69" si="29">P69*N69</f>
+        <v>0.99</v>
+      </c>
+      <c r="R69" s="20"/>
     </row>
     <row r="70" spans="1:18">
       <c r="A70" s="1"/>
-      <c r="B70" s="17">
-        <f t="shared" si="0"/>
+      <c r="B70" s="16">
+        <f>ROW(B70) - ROW($B$7)</f>
         <v>63</v>
       </c>
-      <c r="C70" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D70" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="E70" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="F70" s="20" t="s">
+      <c r="C70" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E70" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="F70" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="G70" s="20" t="s">
-        <v>375</v>
-      </c>
-      <c r="H70" s="20" t="s">
+      <c r="G70" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="H70" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I70" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J70" s="20" t="s">
+      <c r="J70" s="14" t="s">
         <v>525</v>
       </c>
-      <c r="K70" s="20" t="s">
-        <v>618</v>
-      </c>
-      <c r="L70" s="20">
+      <c r="K70" s="14" t="s">
+        <v>617</v>
+      </c>
+      <c r="L70" s="14">
         <v>1</v>
       </c>
       <c r="M70" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N70" s="20">
+      <c r="N70" s="14">
         <v>1020</v>
       </c>
       <c r="O70" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P70" s="21" t="s">
+      <c r="P70" s="15" t="s">
         <v>842</v>
       </c>
-      <c r="Q70" s="21">
-        <f t="shared" ref="Q70" si="29">P70*N70</f>
+      <c r="Q70" s="15">
+        <f>P70*N70</f>
         <v>15.504</v>
       </c>
-      <c r="R70" s="20"/>
+      <c r="R70" s="14"/>
     </row>
     <row r="71" spans="1:18">
       <c r="A71" s="1"/>
-      <c r="B71" s="16">
-        <f>ROW(B71) - ROW($B$7)</f>
+      <c r="B71" s="17">
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C71" s="22" t="s">
+      <c r="C71" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D71" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E71" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="F71" s="14" t="s">
+      <c r="D71" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="F71" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="G71" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="H71" s="14" t="s">
+      <c r="G71" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="H71" s="20" t="s">
         <v>436</v>
       </c>
       <c r="I71" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J71" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="K71" s="14" t="s">
-        <v>614</v>
-      </c>
-      <c r="L71" s="14">
+      <c r="J71" s="20" t="s">
+        <v>525</v>
+      </c>
+      <c r="K71" s="20" t="s">
+        <v>618</v>
+      </c>
+      <c r="L71" s="20">
         <v>1</v>
       </c>
       <c r="M71" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N71" s="14">
-        <v>1050</v>
+      <c r="N71" s="20">
+        <v>1020</v>
       </c>
       <c r="O71" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P71" s="15" t="s">
-        <v>843</v>
-      </c>
-      <c r="Q71" s="15">
-        <f>P71*N71</f>
-        <v>13.755000000000001</v>
-      </c>
-      <c r="R71" s="14"/>
+      <c r="P71" s="21" t="s">
+        <v>842</v>
+      </c>
+      <c r="Q71" s="21">
+        <f t="shared" ref="Q71" si="30">P71*N71</f>
+        <v>15.504</v>
+      </c>
+      <c r="R71" s="20"/>
     </row>
     <row r="72" spans="1:18">
       <c r="A72" s="1"/>
-      <c r="B72" s="17">
-        <f t="shared" si="0"/>
+      <c r="B72" s="16">
+        <f>ROW(B72) - ROW($B$7)</f>
         <v>65</v>
       </c>
-      <c r="C72" s="23" t="s">
+      <c r="C72" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D72" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="E72" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="F72" s="20" t="s">
+      <c r="D72" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="F72" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="G72" s="20" t="s">
-        <v>377</v>
-      </c>
-      <c r="H72" s="20" t="s">
+      <c r="G72" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="H72" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I72" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J72" s="20" t="s">
-        <v>527</v>
-      </c>
-      <c r="K72" s="20" t="s">
-        <v>619</v>
-      </c>
-      <c r="L72" s="20">
+      <c r="J72" s="14" t="s">
+        <v>526</v>
+      </c>
+      <c r="K72" s="14" t="s">
+        <v>614</v>
+      </c>
+      <c r="L72" s="14">
         <v>1</v>
       </c>
       <c r="M72" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N72" s="20">
+      <c r="N72" s="14">
         <v>1050</v>
       </c>
       <c r="O72" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P72" s="21" t="s">
-        <v>844</v>
-      </c>
-      <c r="Q72" s="21">
-        <f t="shared" ref="Q72" si="30">P72*N72</f>
-        <v>14.91</v>
-      </c>
-      <c r="R72" s="20"/>
+      <c r="P72" s="15" t="s">
+        <v>843</v>
+      </c>
+      <c r="Q72" s="15">
+        <f>P72*N72</f>
+        <v>13.755000000000001</v>
+      </c>
+      <c r="R72" s="14"/>
     </row>
     <row r="73" spans="1:18">
       <c r="A73" s="1"/>
-      <c r="B73" s="16">
-        <f>ROW(B73) - ROW($B$7)</f>
+      <c r="B73" s="17">
+        <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C73" s="22" t="s">
+      <c r="C73" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="E73" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="F73" s="14" t="s">
+      <c r="D73" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="F73" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="G73" s="14" t="s">
-        <v>378</v>
-      </c>
-      <c r="H73" s="14" t="s">
+      <c r="G73" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="H73" s="20" t="s">
         <v>436</v>
       </c>
       <c r="I73" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J73" s="14" t="s">
-        <v>528</v>
-      </c>
-      <c r="K73" s="14" t="s">
-        <v>620</v>
-      </c>
-      <c r="L73" s="14">
+      <c r="J73" s="20" t="s">
+        <v>527</v>
+      </c>
+      <c r="K73" s="20" t="s">
+        <v>619</v>
+      </c>
+      <c r="L73" s="20">
         <v>1</v>
       </c>
       <c r="M73" s="14">
-        <f t="shared" ref="M73:M137" si="31">L73*1000</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N73" s="14">
-        <v>1100</v>
+      <c r="N73" s="20">
+        <v>1050</v>
       </c>
       <c r="O73" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P73" s="15" t="s">
-        <v>839</v>
-      </c>
-      <c r="Q73" s="15">
-        <f>P73*N73</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="R73" s="14"/>
+      <c r="P73" s="21" t="s">
+        <v>844</v>
+      </c>
+      <c r="Q73" s="21">
+        <f t="shared" ref="Q73" si="31">P73*N73</f>
+        <v>14.91</v>
+      </c>
+      <c r="R73" s="20"/>
     </row>
     <row r="74" spans="1:18">
       <c r="A74" s="1"/>
-      <c r="B74" s="17">
-        <f t="shared" si="0"/>
+      <c r="B74" s="16">
+        <f>ROW(B74) - ROW($B$7)</f>
         <v>67</v>
       </c>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D74" s="20" t="s">
-        <v>668</v>
-      </c>
-      <c r="E74" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="F74" s="20" t="s">
+      <c r="D74" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E74" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="F74" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="G74" s="20" t="s">
-        <v>379</v>
-      </c>
-      <c r="H74" s="20" t="s">
+      <c r="G74" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="H74" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I74" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J74" s="20" t="s">
-        <v>529</v>
-      </c>
-      <c r="K74" s="20" t="s">
-        <v>621</v>
-      </c>
-      <c r="L74" s="20">
-        <v>6</v>
+      <c r="J74" s="14" t="s">
+        <v>528</v>
+      </c>
+      <c r="K74" s="14" t="s">
+        <v>620</v>
+      </c>
+      <c r="L74" s="14">
+        <v>1</v>
       </c>
       <c r="M74" s="14">
-        <f t="shared" si="31"/>
-        <v>6000</v>
-      </c>
-      <c r="N74" s="20">
-        <v>6100</v>
+        <f t="shared" ref="M74:M138" si="32">L74*1000</f>
+        <v>1000</v>
+      </c>
+      <c r="N74" s="14">
+        <v>1100</v>
       </c>
       <c r="O74" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P74" s="21" t="s">
+      <c r="P74" s="15" t="s">
         <v>839</v>
       </c>
-      <c r="Q74" s="21">
-        <f t="shared" ref="Q74" si="32">P74*N74</f>
-        <v>3.0500000000000003</v>
-      </c>
-      <c r="R74" s="20"/>
+      <c r="Q74" s="15">
+        <f>P74*N74</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="R74" s="14"/>
     </row>
     <row r="75" spans="1:18">
       <c r="A75" s="1"/>
-      <c r="B75" s="16">
-        <f>ROW(B75) - ROW($B$7)</f>
+      <c r="B75" s="17">
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C75" s="22" t="s">
+      <c r="C75" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D75" s="14" t="s">
+      <c r="D75" s="20" t="s">
+        <v>668</v>
+      </c>
+      <c r="E75" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="F75" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="G75" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="H75" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="I75" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="J75" s="20" t="s">
+        <v>529</v>
+      </c>
+      <c r="K75" s="20" t="s">
+        <v>621</v>
+      </c>
+      <c r="L75" s="20">
+        <v>6</v>
+      </c>
+      <c r="M75" s="14">
+        <f t="shared" si="32"/>
+        <v>6000</v>
+      </c>
+      <c r="N75" s="20">
+        <v>6100</v>
+      </c>
+      <c r="O75" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P75" s="21" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q75" s="21">
+        <f t="shared" ref="Q75" si="33">P75*N75</f>
+        <v>3.0500000000000003</v>
+      </c>
+      <c r="R75" s="20"/>
+    </row>
+    <row r="76" spans="1:18">
+      <c r="A76" s="1"/>
+      <c r="B76" s="16">
+        <f>ROW(B76) - ROW($B$7)</f>
+        <v>69</v>
+      </c>
+      <c r="C76" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D76" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="E75" s="14" t="s">
+      <c r="E76" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="F75" s="14" t="s">
+      <c r="F76" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="G75" s="14" t="s">
+      <c r="G76" s="14" t="s">
         <v>380</v>
       </c>
-      <c r="H75" s="14" t="s">
+      <c r="H76" s="14" t="s">
         <v>436</v>
       </c>
-      <c r="I75" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="J75" s="14" t="s">
+      <c r="I76" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="J76" s="14" t="s">
         <v>530</v>
       </c>
-      <c r="K75" s="14" t="s">
+      <c r="K76" s="14" t="s">
         <v>622</v>
       </c>
-      <c r="L75" s="14">
+      <c r="L76" s="14">
         <v>1</v>
       </c>
-      <c r="M75" s="14">
-        <f t="shared" si="31"/>
+      <c r="M76" s="14">
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N75" s="14">
+      <c r="N76" s="14">
         <v>1100</v>
       </c>
-      <c r="O75" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P75" s="15" t="s">
+      <c r="O76" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P76" s="15" t="s">
         <v>845</v>
       </c>
-      <c r="Q75" s="15">
-        <f>P75*N75</f>
+      <c r="Q76" s="15">
+        <f>P76*N76</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="R75" s="14"/>
-    </row>
-    <row r="76" spans="1:18" ht="36">
-      <c r="A76" s="1"/>
-      <c r="B76" s="17">
+      <c r="R76" s="14"/>
+    </row>
+    <row r="77" spans="1:18" ht="36">
+      <c r="A77" s="1"/>
+      <c r="B77" s="17">
         <f t="shared" si="0"/>
-        <v>69</v>
-      </c>
-      <c r="C76" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C77" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D76" s="20" t="s">
+      <c r="D77" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="E76" s="20" t="s">
+      <c r="E77" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="F76" s="20" t="s">
+      <c r="F77" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="G76" s="20" t="s">
+      <c r="G77" s="20" t="s">
         <v>381</v>
       </c>
-      <c r="H76" s="20" t="s">
+      <c r="H77" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="I76" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="J76" s="20" t="s">
+      <c r="I77" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="J77" s="20" t="s">
         <v>531</v>
       </c>
-      <c r="K76" s="20" t="s">
+      <c r="K77" s="20" t="s">
         <v>623</v>
       </c>
-      <c r="L76" s="20">
+      <c r="L77" s="20">
         <v>19</v>
       </c>
-      <c r="M76" s="14">
-        <f t="shared" si="31"/>
+      <c r="M77" s="14">
+        <f t="shared" si="32"/>
         <v>19000</v>
       </c>
-      <c r="N76" s="20">
+      <c r="N77" s="20">
         <v>19100</v>
       </c>
-      <c r="O76" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P76" s="21" t="s">
+      <c r="O77" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P77" s="21" t="s">
         <v>840</v>
       </c>
-      <c r="Q76" s="21">
-        <f t="shared" ref="Q76" si="33">P76*N76</f>
+      <c r="Q77" s="21">
+        <f t="shared" ref="Q77" si="34">P77*N77</f>
         <v>7.6400000000000006</v>
       </c>
-      <c r="R76" s="20"/>
-    </row>
-    <row r="77" spans="1:18">
-      <c r="A77" s="1"/>
-      <c r="B77" s="16">
-        <f>ROW(B77) - ROW($B$7)</f>
-        <v>70</v>
-      </c>
-      <c r="C77" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D77" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="E77" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="F77" s="14" t="s">
-        <v>303</v>
-      </c>
-      <c r="G77" s="14" t="s">
-        <v>382</v>
-      </c>
-      <c r="H77" s="14" t="s">
-        <v>436</v>
-      </c>
-      <c r="I77" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="J77" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="K77" s="14" t="s">
-        <v>624</v>
-      </c>
-      <c r="L77" s="14">
-        <v>2</v>
-      </c>
-      <c r="M77" s="14">
-        <f t="shared" si="31"/>
-        <v>2000</v>
-      </c>
-      <c r="N77" s="14">
-        <v>2100</v>
-      </c>
-      <c r="O77" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P77" s="15" t="s">
-        <v>839</v>
-      </c>
-      <c r="Q77" s="15">
-        <f>P77*N77</f>
-        <v>1.05</v>
-      </c>
-      <c r="R77" s="14"/>
+      <c r="R77" s="20"/>
     </row>
     <row r="78" spans="1:18">
       <c r="A78" s="1"/>
-      <c r="B78" s="17">
-        <f t="shared" si="0"/>
+      <c r="B78" s="16">
+        <f>ROW(B78) - ROW($B$7)</f>
         <v>71</v>
       </c>
-      <c r="C78" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="D78" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="E78" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="F78" s="20" t="s">
+      <c r="C78" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E78" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F78" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="G78" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="H78" s="20" t="s">
+      <c r="G78" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="H78" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I78" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J78" s="20" t="s">
-        <v>533</v>
-      </c>
-      <c r="K78" s="20" t="s">
-        <v>625</v>
-      </c>
-      <c r="L78" s="20">
-        <v>1</v>
+      <c r="J78" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="K78" s="14" t="s">
+        <v>624</v>
+      </c>
+      <c r="L78" s="14">
+        <v>2</v>
       </c>
       <c r="M78" s="14">
-        <f t="shared" si="31"/>
-        <v>1000</v>
-      </c>
-      <c r="N78" s="20">
-        <v>1100</v>
+        <f t="shared" si="32"/>
+        <v>2000</v>
+      </c>
+      <c r="N78" s="14">
+        <v>2100</v>
       </c>
       <c r="O78" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P78" s="21" t="s">
+      <c r="P78" s="15" t="s">
         <v>839</v>
       </c>
-      <c r="Q78" s="21">
-        <f t="shared" ref="Q78" si="34">P78*N78</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="R78" s="20"/>
+      <c r="Q78" s="15">
+        <f>P78*N78</f>
+        <v>1.05</v>
+      </c>
+      <c r="R78" s="14"/>
     </row>
     <row r="79" spans="1:18">
       <c r="A79" s="1"/>
-      <c r="B79" s="16">
-        <f>ROW(B79) - ROW($B$7)</f>
+      <c r="B79" s="17">
+        <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C79" s="22" t="s">
+      <c r="C79" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D79" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="E79" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="F79" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="G79" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="H79" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="I79" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="J79" s="20" t="s">
+        <v>533</v>
+      </c>
+      <c r="K79" s="20" t="s">
+        <v>625</v>
+      </c>
+      <c r="L79" s="20">
+        <v>1</v>
+      </c>
+      <c r="M79" s="14">
+        <f t="shared" si="32"/>
+        <v>1000</v>
+      </c>
+      <c r="N79" s="20">
+        <v>1100</v>
+      </c>
+      <c r="O79" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P79" s="21" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q79" s="21">
+        <f t="shared" ref="Q79" si="35">P79*N79</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="R79" s="20"/>
+    </row>
+    <row r="80" spans="1:18">
+      <c r="A80" s="1"/>
+      <c r="B80" s="16">
+        <f>ROW(B80) - ROW($B$7)</f>
+        <v>73</v>
+      </c>
+      <c r="C80" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D79" s="14" t="s">
+      <c r="D80" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E79" s="14" t="s">
+      <c r="E80" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="F79" s="14" t="s">
+      <c r="F80" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="G79" s="14" t="s">
+      <c r="G80" s="14" t="s">
         <v>384</v>
       </c>
-      <c r="H79" s="14" t="s">
+      <c r="H80" s="14" t="s">
         <v>436</v>
       </c>
-      <c r="I79" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="J79" s="14" t="s">
+      <c r="I80" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="J80" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="K79" s="14" t="s">
+      <c r="K80" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="L79" s="14">
+      <c r="L80" s="14">
         <v>1</v>
       </c>
-      <c r="M79" s="14">
-        <f t="shared" si="31"/>
+      <c r="M80" s="14">
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N79" s="14">
+      <c r="N80" s="14">
         <v>1100</v>
       </c>
-      <c r="O79" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P79" s="15" t="s">
+      <c r="O80" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P80" s="15" t="s">
         <v>839</v>
       </c>
-      <c r="Q79" s="15">
-        <f>P79*N79</f>
+      <c r="Q80" s="15">
+        <f>P80*N80</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="R79" s="14"/>
-    </row>
-    <row r="80" spans="1:18" ht="24">
-      <c r="A80" s="1"/>
-      <c r="B80" s="17">
+      <c r="R80" s="14"/>
+    </row>
+    <row r="81" spans="1:18" ht="24">
+      <c r="A81" s="1"/>
+      <c r="B81" s="17">
         <f t="shared" si="0"/>
-        <v>73</v>
-      </c>
-      <c r="C80" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C81" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D80" s="20" t="s">
+      <c r="D81" s="20" t="s">
         <v>883</v>
       </c>
-      <c r="E80" s="20" t="s">
+      <c r="E81" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="F80" s="20" t="s">
+      <c r="F81" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="G80" s="20" t="s">
+      <c r="G81" s="20" t="s">
         <v>385</v>
       </c>
-      <c r="H80" s="20" t="s">
+      <c r="H81" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="I80" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="J80" s="20" t="s">
+      <c r="I81" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="J81" s="20" t="s">
         <v>535</v>
       </c>
-      <c r="K80" s="20" t="s">
+      <c r="K81" s="20" t="s">
         <v>623</v>
       </c>
-      <c r="L80" s="20">
+      <c r="L81" s="20">
         <v>10</v>
       </c>
-      <c r="M80" s="14">
-        <f t="shared" si="31"/>
+      <c r="M81" s="14">
+        <f t="shared" si="32"/>
         <v>10000</v>
       </c>
-      <c r="N80" s="20">
+      <c r="N81" s="20">
         <v>10100</v>
       </c>
-      <c r="O80" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P80" s="21" t="s">
+      <c r="O81" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P81" s="21" t="s">
         <v>744</v>
       </c>
-      <c r="Q80" s="21">
-        <f t="shared" ref="Q80" si="35">P80*N80</f>
+      <c r="Q81" s="21">
+        <f t="shared" ref="Q81" si="36">P81*N81</f>
         <v>6.06</v>
       </c>
-      <c r="R80" s="20"/>
-    </row>
-    <row r="81" spans="1:18">
-      <c r="A81" s="1"/>
-      <c r="B81" s="16">
-        <f>ROW(B81) - ROW($B$7)</f>
-        <v>74</v>
-      </c>
-      <c r="C81" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D81" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E81" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="F81" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="G81" s="14" t="s">
-        <v>386</v>
-      </c>
-      <c r="H81" s="14" t="s">
-        <v>436</v>
-      </c>
-      <c r="I81" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="J81" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="K81" s="14" t="s">
-        <v>627</v>
-      </c>
-      <c r="L81" s="14">
-        <v>1</v>
-      </c>
-      <c r="M81" s="14">
-        <f t="shared" si="31"/>
-        <v>1000</v>
-      </c>
-      <c r="N81" s="14">
-        <v>1020</v>
-      </c>
-      <c r="O81" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P81" s="15" t="s">
-        <v>846</v>
-      </c>
-      <c r="Q81" s="15">
-        <f>P81*N81</f>
-        <v>17.34</v>
-      </c>
-      <c r="R81" s="14"/>
+      <c r="R81" s="20"/>
     </row>
     <row r="82" spans="1:18">
       <c r="A82" s="1"/>
-      <c r="B82" s="17">
-        <f t="shared" si="0"/>
+      <c r="B82" s="16">
+        <f>ROW(B82) - ROW($B$7)</f>
         <v>75</v>
       </c>
-      <c r="C82" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D82" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="E82" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="F82" s="20" t="s">
+      <c r="C82" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E82" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="F82" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="G82" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="H82" s="20" t="s">
+      <c r="G82" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="H82" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I82" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J82" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="K82" s="20" t="s">
-        <v>628</v>
-      </c>
-      <c r="L82" s="20">
+      <c r="J82" s="14" t="s">
+        <v>536</v>
+      </c>
+      <c r="K82" s="14" t="s">
+        <v>627</v>
+      </c>
+      <c r="L82" s="14">
         <v>1</v>
       </c>
       <c r="M82" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N82" s="20">
-        <v>1100</v>
+      <c r="N82" s="14">
+        <v>1020</v>
       </c>
       <c r="O82" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P82" s="21" t="s">
-        <v>845</v>
-      </c>
-      <c r="Q82" s="21">
-        <f t="shared" ref="Q82" si="36">P82*N82</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="R82" s="20"/>
+      <c r="P82" s="15" t="s">
+        <v>846</v>
+      </c>
+      <c r="Q82" s="15">
+        <f>P82*N82</f>
+        <v>17.34</v>
+      </c>
+      <c r="R82" s="14"/>
     </row>
     <row r="83" spans="1:18">
       <c r="A83" s="1"/>
-      <c r="B83" s="16">
-        <f>ROW(B83) - ROW($B$7)</f>
+      <c r="B83" s="17">
+        <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C83" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D83" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E83" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="F83" s="14" t="s">
+      <c r="C83" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D83" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="E83" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="F83" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="G83" s="14" t="s">
-        <v>388</v>
-      </c>
-      <c r="H83" s="14" t="s">
+      <c r="G83" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="H83" s="20" t="s">
         <v>436</v>
       </c>
       <c r="I83" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J83" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="K83" s="14" t="s">
-        <v>629</v>
-      </c>
-      <c r="L83" s="14">
+      <c r="J83" s="20" t="s">
+        <v>537</v>
+      </c>
+      <c r="K83" s="20" t="s">
+        <v>628</v>
+      </c>
+      <c r="L83" s="20">
         <v>1</v>
       </c>
       <c r="M83" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N83" s="14">
-        <v>1020</v>
+      <c r="N83" s="20">
+        <v>1100</v>
       </c>
       <c r="O83" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P83" s="15" t="s">
-        <v>701</v>
-      </c>
-      <c r="Q83" s="15">
-        <f>P83*N83</f>
-        <v>17.544</v>
-      </c>
-      <c r="R83" s="14"/>
+      <c r="P83" s="21" t="s">
+        <v>845</v>
+      </c>
+      <c r="Q83" s="21">
+        <f t="shared" ref="Q83" si="37">P83*N83</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R83" s="20"/>
     </row>
     <row r="84" spans="1:18">
       <c r="A84" s="1"/>
-      <c r="B84" s="17">
-        <f t="shared" si="0"/>
+      <c r="B84" s="16">
+        <f>ROW(B84) - ROW($B$7)</f>
         <v>77</v>
       </c>
-      <c r="C84" s="23" t="s">
+      <c r="C84" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D84" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="E84" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="F84" s="20" t="s">
+      <c r="D84" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E84" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F84" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="G84" s="20" t="s">
-        <v>389</v>
-      </c>
-      <c r="H84" s="20" t="s">
+      <c r="G84" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="H84" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I84" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J84" s="20" t="s">
-        <v>539</v>
-      </c>
-      <c r="K84" s="20" t="s">
-        <v>630</v>
-      </c>
-      <c r="L84" s="20">
+      <c r="J84" s="14" t="s">
+        <v>538</v>
+      </c>
+      <c r="K84" s="14" t="s">
+        <v>629</v>
+      </c>
+      <c r="L84" s="14">
         <v>1</v>
       </c>
       <c r="M84" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N84" s="20">
+      <c r="N84" s="14">
         <v>1020</v>
       </c>
       <c r="O84" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P84" s="21" t="s">
-        <v>847</v>
-      </c>
-      <c r="Q84" s="21">
-        <f t="shared" ref="Q84" si="37">P84*N84</f>
-        <v>16.32</v>
-      </c>
-      <c r="R84" s="20"/>
+      <c r="P84" s="15" t="s">
+        <v>701</v>
+      </c>
+      <c r="Q84" s="15">
+        <f>P84*N84</f>
+        <v>17.544</v>
+      </c>
+      <c r="R84" s="14"/>
     </row>
     <row r="85" spans="1:18">
       <c r="A85" s="1"/>
-      <c r="B85" s="16">
-        <f>ROW(B85) - ROW($B$7)</f>
+      <c r="B85" s="17">
+        <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="C85" s="22" t="s">
+      <c r="C85" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D85" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E85" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="F85" s="14" t="s">
+      <c r="D85" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="E85" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="F85" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="G85" s="14" t="s">
-        <v>390</v>
-      </c>
-      <c r="H85" s="14" t="s">
+      <c r="G85" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="H85" s="20" t="s">
         <v>436</v>
       </c>
       <c r="I85" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J85" s="14" t="s">
-        <v>540</v>
-      </c>
-      <c r="K85" s="14" t="s">
-        <v>631</v>
-      </c>
-      <c r="L85" s="14">
+      <c r="J85" s="20" t="s">
+        <v>539</v>
+      </c>
+      <c r="K85" s="20" t="s">
+        <v>630</v>
+      </c>
+      <c r="L85" s="20">
         <v>1</v>
       </c>
       <c r="M85" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N85" s="14">
+      <c r="N85" s="20">
         <v>1020</v>
       </c>
       <c r="O85" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P85" s="15" t="s">
-        <v>848</v>
-      </c>
-      <c r="Q85" s="15">
-        <f>P85*N85</f>
-        <v>16.728000000000002</v>
-      </c>
-      <c r="R85" s="14"/>
+      <c r="P85" s="21" t="s">
+        <v>847</v>
+      </c>
+      <c r="Q85" s="21">
+        <f t="shared" ref="Q85" si="38">P85*N85</f>
+        <v>16.32</v>
+      </c>
+      <c r="R85" s="20"/>
     </row>
     <row r="86" spans="1:18">
       <c r="A86" s="1"/>
-      <c r="B86" s="17">
-        <f t="shared" si="0"/>
+      <c r="B86" s="16">
+        <f>ROW(B86) - ROW($B$7)</f>
         <v>79</v>
       </c>
-      <c r="C86" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D86" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E86" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="F86" s="20" t="s">
+      <c r="C86" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D86" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E86" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="F86" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="G86" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="H86" s="20" t="s">
+      <c r="G86" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="H86" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I86" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J86" s="20" t="s">
-        <v>541</v>
-      </c>
-      <c r="K86" s="20" t="s">
-        <v>614</v>
-      </c>
-      <c r="L86" s="20">
-        <v>8</v>
+      <c r="J86" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="K86" s="14" t="s">
+        <v>631</v>
+      </c>
+      <c r="L86" s="14">
+        <v>1</v>
       </c>
       <c r="M86" s="14">
-        <f t="shared" si="31"/>
-        <v>8000</v>
-      </c>
-      <c r="N86" s="20">
-        <v>8100</v>
+        <f t="shared" si="32"/>
+        <v>1000</v>
+      </c>
+      <c r="N86" s="14">
+        <v>1020</v>
       </c>
       <c r="O86" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P86" s="21" t="s">
-        <v>742</v>
-      </c>
-      <c r="Q86" s="21">
-        <f t="shared" ref="Q86" si="38">P86*N86</f>
-        <v>5.67</v>
-      </c>
-      <c r="R86" s="20"/>
+      <c r="P86" s="15" t="s">
+        <v>848</v>
+      </c>
+      <c r="Q86" s="15">
+        <f>P86*N86</f>
+        <v>16.728000000000002</v>
+      </c>
+      <c r="R86" s="14"/>
     </row>
     <row r="87" spans="1:18">
       <c r="A87" s="1"/>
-      <c r="B87" s="16">
-        <f>ROW(B87) - ROW($B$7)</f>
+      <c r="B87" s="17">
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="C87" s="22" t="s">
+      <c r="C87" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D87" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E87" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="F87" s="14" t="s">
+      <c r="D87" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="F87" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="G87" s="14" t="s">
-        <v>392</v>
-      </c>
-      <c r="H87" s="14" t="s">
+      <c r="G87" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="H87" s="20" t="s">
         <v>436</v>
       </c>
       <c r="I87" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J87" s="14" t="s">
-        <v>542</v>
-      </c>
-      <c r="K87" s="14" t="s">
-        <v>632</v>
-      </c>
-      <c r="L87" s="14">
-        <v>4</v>
+      <c r="J87" s="20" t="s">
+        <v>541</v>
+      </c>
+      <c r="K87" s="20" t="s">
+        <v>614</v>
+      </c>
+      <c r="L87" s="20">
+        <v>8</v>
       </c>
       <c r="M87" s="14">
-        <f t="shared" si="31"/>
-        <v>4000</v>
-      </c>
-      <c r="N87" s="14">
-        <v>4100</v>
+        <f t="shared" si="32"/>
+        <v>8000</v>
+      </c>
+      <c r="N87" s="20">
+        <v>8100</v>
       </c>
       <c r="O87" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P87" s="15" t="s">
-        <v>845</v>
-      </c>
-      <c r="Q87" s="15">
-        <f>P87*N87</f>
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="R87" s="14"/>
+      <c r="P87" s="21" t="s">
+        <v>742</v>
+      </c>
+      <c r="Q87" s="21">
+        <f t="shared" ref="Q87" si="39">P87*N87</f>
+        <v>5.67</v>
+      </c>
+      <c r="R87" s="20"/>
     </row>
     <row r="88" spans="1:18">
       <c r="A88" s="1"/>
-      <c r="B88" s="17">
-        <f t="shared" si="0"/>
+      <c r="B88" s="16">
+        <f>ROW(B88) - ROW($B$7)</f>
         <v>81</v>
       </c>
-      <c r="C88" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="D88" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E88" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="F88" s="20" t="s">
+      <c r="C88" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D88" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E88" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="F88" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="G88" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="H88" s="20" t="s">
+      <c r="G88" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="H88" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I88" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J88" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="K88" s="20" t="s">
-        <v>619</v>
-      </c>
-      <c r="L88" s="20">
-        <v>5</v>
+      <c r="J88" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="K88" s="14" t="s">
+        <v>632</v>
+      </c>
+      <c r="L88" s="14">
+        <v>4</v>
       </c>
       <c r="M88" s="14">
-        <f t="shared" si="31"/>
-        <v>5000</v>
-      </c>
-      <c r="N88" s="20">
-        <v>5100</v>
+        <f t="shared" si="32"/>
+        <v>4000</v>
+      </c>
+      <c r="N88" s="14">
+        <v>4100</v>
       </c>
       <c r="O88" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P88" s="21" t="s">
-        <v>744</v>
-      </c>
-      <c r="Q88" s="21">
-        <f t="shared" ref="Q88" si="39">P88*N88</f>
-        <v>3.0599999999999996</v>
-      </c>
-      <c r="R88" s="20"/>
+      <c r="P88" s="15" t="s">
+        <v>845</v>
+      </c>
+      <c r="Q88" s="15">
+        <f>P88*N88</f>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="R88" s="14"/>
     </row>
     <row r="89" spans="1:18">
       <c r="A89" s="1"/>
-      <c r="B89" s="16">
-        <f>ROW(B89) - ROW($B$7)</f>
+      <c r="B89" s="17">
+        <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="C89" s="22" t="s">
+      <c r="C89" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D89" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="E89" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="F89" s="14" t="s">
+      <c r="D89" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="E89" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="F89" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="G89" s="14" t="s">
-        <v>394</v>
-      </c>
-      <c r="H89" s="14" t="s">
+      <c r="G89" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="H89" s="20" t="s">
         <v>436</v>
       </c>
       <c r="I89" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J89" s="14" t="s">
-        <v>544</v>
-      </c>
-      <c r="K89" s="14" t="s">
-        <v>633</v>
-      </c>
-      <c r="L89" s="14">
-        <v>1</v>
+      <c r="J89" s="20" t="s">
+        <v>543</v>
+      </c>
+      <c r="K89" s="20" t="s">
+        <v>619</v>
+      </c>
+      <c r="L89" s="20">
+        <v>5</v>
       </c>
       <c r="M89" s="14">
-        <f t="shared" si="31"/>
-        <v>1000</v>
-      </c>
-      <c r="N89" s="14">
-        <v>1100</v>
+        <f t="shared" si="32"/>
+        <v>5000</v>
+      </c>
+      <c r="N89" s="20">
+        <v>5100</v>
       </c>
       <c r="O89" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P89" s="15" t="s">
-        <v>719</v>
-      </c>
-      <c r="Q89" s="15">
-        <f>P89*N89</f>
-        <v>1.21</v>
-      </c>
-      <c r="R89" s="14"/>
+      <c r="P89" s="21" t="s">
+        <v>744</v>
+      </c>
+      <c r="Q89" s="21">
+        <f t="shared" ref="Q89" si="40">P89*N89</f>
+        <v>3.0599999999999996</v>
+      </c>
+      <c r="R89" s="20"/>
     </row>
     <row r="90" spans="1:18">
       <c r="A90" s="1"/>
-      <c r="B90" s="17">
-        <f t="shared" si="0"/>
+      <c r="B90" s="16">
+        <f>ROW(B90) - ROW($B$7)</f>
         <v>83</v>
       </c>
       <c r="C90" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D90" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="E90" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="F90" s="20" t="s">
+      <c r="D90" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E90" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="F90" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="G90" s="20" t="s">
-        <v>877</v>
-      </c>
-      <c r="H90" s="20"/>
+      <c r="G90" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="H90" s="14" t="s">
+        <v>436</v>
+      </c>
       <c r="I90" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J90" s="20" t="s">
-        <v>545</v>
-      </c>
-      <c r="K90" s="20" t="s">
-        <v>634</v>
-      </c>
-      <c r="L90" s="20">
-        <v>2</v>
+      <c r="J90" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="K90" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="L90" s="14">
+        <v>1</v>
       </c>
       <c r="M90" s="14">
-        <f t="shared" si="31"/>
-        <v>2000</v>
-      </c>
-      <c r="N90" s="20">
-        <v>2100</v>
+        <f t="shared" si="32"/>
+        <v>1000</v>
+      </c>
+      <c r="N90" s="14">
+        <v>1100</v>
       </c>
       <c r="O90" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P90" s="21" t="s">
-        <v>841</v>
-      </c>
-      <c r="Q90" s="21">
-        <f t="shared" ref="Q90" si="40">P90*N90</f>
-        <v>1.89</v>
-      </c>
-      <c r="R90" s="20"/>
+      <c r="P90" s="15" t="s">
+        <v>719</v>
+      </c>
+      <c r="Q90" s="15">
+        <f>P90*N90</f>
+        <v>1.21</v>
+      </c>
+      <c r="R90" s="14"/>
     </row>
     <row r="91" spans="1:18">
       <c r="A91" s="1"/>
-      <c r="B91" s="16">
-        <f>ROW(B91) - ROW($B$7)</f>
+      <c r="B91" s="17">
+        <f t="shared" si="0"/>
         <v>84</v>
       </c>
       <c r="C91" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D91" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="E91" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="F91" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D91" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="E91" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="F91" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="G91" s="14" t="s">
-        <v>395</v>
-      </c>
-      <c r="H91" s="14" t="s">
-        <v>436</v>
-      </c>
+      <c r="G91" s="20" t="s">
+        <v>877</v>
+      </c>
+      <c r="H91" s="20"/>
       <c r="I91" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J91" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="K91" s="14" t="s">
-        <v>635</v>
-      </c>
-      <c r="L91" s="14">
-        <v>1</v>
+      <c r="J91" s="20" t="s">
+        <v>545</v>
+      </c>
+      <c r="K91" s="20" t="s">
+        <v>634</v>
+      </c>
+      <c r="L91" s="20">
+        <v>2</v>
       </c>
       <c r="M91" s="14">
-        <f t="shared" si="31"/>
-        <v>1000</v>
-      </c>
-      <c r="N91" s="14">
-        <v>1100</v>
+        <f t="shared" si="32"/>
+        <v>2000</v>
+      </c>
+      <c r="N91" s="20">
+        <v>2100</v>
       </c>
       <c r="O91" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P91" s="15" t="s">
+      <c r="P91" s="21" t="s">
         <v>841</v>
       </c>
-      <c r="Q91" s="15">
-        <f>P91*N91</f>
-        <v>0.99</v>
-      </c>
-      <c r="R91" s="14"/>
+      <c r="Q91" s="21">
+        <f t="shared" ref="Q91" si="41">P91*N91</f>
+        <v>1.89</v>
+      </c>
+      <c r="R91" s="20"/>
     </row>
     <row r="92" spans="1:18">
       <c r="A92" s="1"/>
-      <c r="B92" s="17">
-        <f t="shared" si="0"/>
+      <c r="B92" s="16">
+        <f>ROW(B92) - ROW($B$7)</f>
         <v>85</v>
       </c>
-      <c r="C92" s="23" t="s">
+      <c r="C92" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D92" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="E92" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="F92" s="20" t="s">
+      <c r="D92" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E92" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="F92" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="G92" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="H92" s="20" t="s">
+      <c r="G92" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="H92" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I92" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J92" s="20" t="s">
-        <v>547</v>
-      </c>
-      <c r="K92" s="20" t="s">
-        <v>636</v>
-      </c>
-      <c r="L92" s="20">
+      <c r="J92" s="14" t="s">
+        <v>546</v>
+      </c>
+      <c r="K92" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="L92" s="14">
         <v>1</v>
       </c>
       <c r="M92" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N92" s="20">
-        <v>1020</v>
+      <c r="N92" s="14">
+        <v>1100</v>
       </c>
       <c r="O92" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P92" s="21" t="s">
-        <v>849</v>
-      </c>
-      <c r="Q92" s="21">
-        <f t="shared" ref="Q92" si="41">P92*N92</f>
-        <v>17.135999999999999</v>
-      </c>
-      <c r="R92" s="20"/>
+      <c r="P92" s="15" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q92" s="15">
+        <f>P92*N92</f>
+        <v>0.99</v>
+      </c>
+      <c r="R92" s="14"/>
     </row>
     <row r="93" spans="1:18">
       <c r="A93" s="1"/>
-      <c r="B93" s="16">
-        <f>ROW(B93) - ROW($B$7)</f>
+      <c r="B93" s="17">
+        <f t="shared" si="0"/>
         <v>86</v>
       </c>
-      <c r="C93" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D93" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E93" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="F93" s="14" t="s">
+      <c r="C93" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D93" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="E93" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="F93" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="G93" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="H93" s="14" t="s">
+      <c r="G93" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="H93" s="20" t="s">
         <v>436</v>
       </c>
       <c r="I93" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J93" s="14" t="s">
-        <v>548</v>
-      </c>
-      <c r="K93" s="14" t="s">
-        <v>637</v>
-      </c>
-      <c r="L93" s="14">
+      <c r="J93" s="20" t="s">
+        <v>547</v>
+      </c>
+      <c r="K93" s="20" t="s">
+        <v>636</v>
+      </c>
+      <c r="L93" s="20">
         <v>1</v>
       </c>
       <c r="M93" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N93" s="14">
-        <v>1100</v>
+      <c r="N93" s="20">
+        <v>1020</v>
       </c>
       <c r="O93" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P93" s="15" t="s">
-        <v>845</v>
-      </c>
-      <c r="Q93" s="15">
-        <f>P93*N93</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="R93" s="14"/>
+      <c r="P93" s="21" t="s">
+        <v>849</v>
+      </c>
+      <c r="Q93" s="21">
+        <f t="shared" ref="Q93" si="42">P93*N93</f>
+        <v>17.135999999999999</v>
+      </c>
+      <c r="R93" s="20"/>
     </row>
     <row r="94" spans="1:18">
       <c r="A94" s="1"/>
-      <c r="B94" s="17">
-        <f t="shared" si="0"/>
+      <c r="B94" s="16">
+        <f>ROW(B94) - ROW($B$7)</f>
         <v>87</v>
       </c>
-      <c r="C94" s="23" t="s">
+      <c r="C94" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D94" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="E94" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="F94" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="G94" s="20" t="s">
-        <v>398</v>
-      </c>
-      <c r="H94" s="20" t="s">
+      <c r="D94" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E94" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="F94" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="G94" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="H94" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I94" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J94" s="20" t="s">
-        <v>549</v>
-      </c>
-      <c r="K94" s="20" t="s">
-        <v>638</v>
-      </c>
-      <c r="L94" s="20">
+      <c r="J94" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="K94" s="14" t="s">
+        <v>637</v>
+      </c>
+      <c r="L94" s="14">
         <v>1</v>
       </c>
       <c r="M94" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N94" s="20">
+      <c r="N94" s="14">
         <v>1100</v>
       </c>
       <c r="O94" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P94" s="21" t="s">
-        <v>744</v>
-      </c>
-      <c r="Q94" s="21">
-        <f t="shared" ref="Q94" si="42">P94*N94</f>
-        <v>0.65999999999999992</v>
-      </c>
-      <c r="R94" s="20"/>
+      <c r="P94" s="15" t="s">
+        <v>845</v>
+      </c>
+      <c r="Q94" s="15">
+        <f>P94*N94</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R94" s="14"/>
     </row>
     <row r="95" spans="1:18">
       <c r="A95" s="1"/>
-      <c r="B95" s="16">
-        <f>ROW(B95) - ROW($B$7)</f>
+      <c r="B95" s="17">
+        <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="C95" s="22" t="s">
+      <c r="C95" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D95" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E95" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="F95" s="14" t="s">
+      <c r="D95" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="E95" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="F95" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="G95" s="14" t="s">
-        <v>399</v>
-      </c>
-      <c r="H95" s="14" t="s">
+      <c r="G95" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="H95" s="20" t="s">
         <v>436</v>
       </c>
       <c r="I95" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J95" s="14" t="s">
-        <v>550</v>
-      </c>
-      <c r="K95" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="L95" s="14">
+      <c r="J95" s="20" t="s">
+        <v>549</v>
+      </c>
+      <c r="K95" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="L95" s="20">
         <v>1</v>
       </c>
       <c r="M95" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N95" s="14">
+      <c r="N95" s="20">
         <v>1100</v>
       </c>
       <c r="O95" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P95" s="15" t="s">
+      <c r="P95" s="21" t="s">
         <v>744</v>
       </c>
-      <c r="Q95" s="15">
-        <f>P95*N95</f>
+      <c r="Q95" s="21">
+        <f t="shared" ref="Q95" si="43">P95*N95</f>
         <v>0.65999999999999992</v>
       </c>
-      <c r="R95" s="14"/>
+      <c r="R95" s="20"/>
     </row>
     <row r="96" spans="1:18">
       <c r="A96" s="1"/>
-      <c r="B96" s="17">
-        <f t="shared" si="0"/>
+      <c r="B96" s="16">
+        <f>ROW(B96) - ROW($B$7)</f>
         <v>89</v>
       </c>
-      <c r="C96" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D96" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="E96" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="F96" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="G96" s="20" t="s">
-        <v>400</v>
-      </c>
-      <c r="H96" s="20" t="s">
+      <c r="C96" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E96" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="F96" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="G96" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="H96" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I96" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J96" s="20" t="s">
-        <v>551</v>
-      </c>
-      <c r="K96" s="20" t="s">
-        <v>640</v>
-      </c>
-      <c r="L96" s="20">
+      <c r="J96" s="14" t="s">
+        <v>550</v>
+      </c>
+      <c r="K96" s="14" t="s">
+        <v>639</v>
+      </c>
+      <c r="L96" s="14">
         <v>1</v>
       </c>
       <c r="M96" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N96" s="20">
+      <c r="N96" s="14">
         <v>1100</v>
       </c>
       <c r="O96" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P96" s="21" t="s">
-        <v>845</v>
-      </c>
-      <c r="Q96" s="21">
-        <f t="shared" ref="Q96" si="43">P96*N96</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="R96" s="20"/>
+      <c r="P96" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="Q96" s="15">
+        <f>P96*N96</f>
+        <v>0.65999999999999992</v>
+      </c>
+      <c r="R96" s="14"/>
     </row>
     <row r="97" spans="1:18">
       <c r="A97" s="1"/>
-      <c r="B97" s="16">
-        <f>ROW(B97) - ROW($B$7)</f>
+      <c r="B97" s="17">
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="C97" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D97" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="E97" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="F97" s="14" t="s">
+      <c r="C97" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D97" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E97" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="F97" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="G97" s="14" t="s">
-        <v>401</v>
-      </c>
-      <c r="H97" s="14" t="s">
+      <c r="G97" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="H97" s="20" t="s">
         <v>436</v>
       </c>
       <c r="I97" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J97" s="14" t="s">
-        <v>552</v>
-      </c>
-      <c r="K97" s="14" t="s">
-        <v>641</v>
-      </c>
-      <c r="L97" s="14">
-        <v>3</v>
+      <c r="J97" s="20" t="s">
+        <v>551</v>
+      </c>
+      <c r="K97" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="L97" s="20">
+        <v>1</v>
       </c>
       <c r="M97" s="14">
-        <f t="shared" si="31"/>
-        <v>3000</v>
-      </c>
-      <c r="N97" s="14">
-        <v>3100</v>
+        <f t="shared" si="32"/>
+        <v>1000</v>
+      </c>
+      <c r="N97" s="20">
+        <v>1100</v>
       </c>
       <c r="O97" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P97" s="15" t="s">
-        <v>841</v>
-      </c>
-      <c r="Q97" s="15">
-        <f>P97*N97</f>
-        <v>2.79</v>
-      </c>
-      <c r="R97" s="14"/>
+      <c r="P97" s="21" t="s">
+        <v>845</v>
+      </c>
+      <c r="Q97" s="21">
+        <f t="shared" ref="Q97" si="44">P97*N97</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R97" s="20"/>
     </row>
     <row r="98" spans="1:18">
       <c r="A98" s="1"/>
-      <c r="B98" s="17">
-        <f t="shared" si="0"/>
+      <c r="B98" s="16">
+        <f>ROW(B98) - ROW($B$7)</f>
         <v>91</v>
       </c>
-      <c r="C98" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D98" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="E98" s="20" t="s">
-        <v>243</v>
-      </c>
-      <c r="F98" s="20" t="s">
+      <c r="C98" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E98" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="F98" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="G98" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="H98" s="20" t="s">
+      <c r="G98" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="H98" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I98" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J98" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="K98" s="20" t="s">
-        <v>642</v>
-      </c>
-      <c r="L98" s="20">
-        <v>6</v>
+      <c r="J98" s="14" t="s">
+        <v>552</v>
+      </c>
+      <c r="K98" s="14" t="s">
+        <v>641</v>
+      </c>
+      <c r="L98" s="14">
+        <v>3</v>
       </c>
       <c r="M98" s="14">
-        <f t="shared" si="31"/>
-        <v>6000</v>
-      </c>
-      <c r="N98" s="20">
-        <v>6100</v>
+        <f t="shared" si="32"/>
+        <v>3000</v>
+      </c>
+      <c r="N98" s="14">
+        <v>3100</v>
       </c>
       <c r="O98" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P98" s="21" t="s">
-        <v>753</v>
-      </c>
-      <c r="Q98" s="21">
-        <f t="shared" ref="Q98" si="44">P98*N98</f>
-        <v>4.88</v>
-      </c>
-      <c r="R98" s="20"/>
+      <c r="P98" s="15" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q98" s="15">
+        <f>P98*N98</f>
+        <v>2.79</v>
+      </c>
+      <c r="R98" s="14"/>
     </row>
     <row r="99" spans="1:18">
       <c r="A99" s="1"/>
-      <c r="B99" s="16">
-        <f>ROW(B99) - ROW($B$7)</f>
+      <c r="B99" s="17">
+        <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="C99" s="22" t="s">
+      <c r="C99" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D99" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="E99" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="F99" s="14" t="s">
+      <c r="D99" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E99" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="F99" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="G99" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="H99" s="14" t="s">
+      <c r="G99" s="20" t="s">
+        <v>402</v>
+      </c>
+      <c r="H99" s="20" t="s">
         <v>436</v>
       </c>
       <c r="I99" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J99" s="14" t="s">
-        <v>554</v>
-      </c>
-      <c r="K99" s="14" t="s">
-        <v>643</v>
-      </c>
-      <c r="L99" s="14">
-        <v>1</v>
+      <c r="J99" s="20" t="s">
+        <v>553</v>
+      </c>
+      <c r="K99" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="L99" s="20">
+        <v>6</v>
       </c>
       <c r="M99" s="14">
-        <f t="shared" si="31"/>
-        <v>1000</v>
-      </c>
-      <c r="N99" s="14">
-        <v>1100</v>
+        <f t="shared" si="32"/>
+        <v>6000</v>
+      </c>
+      <c r="N99" s="20">
+        <v>6100</v>
       </c>
       <c r="O99" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P99" s="15" t="s">
-        <v>841</v>
-      </c>
-      <c r="Q99" s="15">
-        <f>P99*N99</f>
-        <v>0.99</v>
-      </c>
-      <c r="R99" s="14"/>
+      <c r="P99" s="21" t="s">
+        <v>753</v>
+      </c>
+      <c r="Q99" s="21">
+        <f t="shared" ref="Q99" si="45">P99*N99</f>
+        <v>4.88</v>
+      </c>
+      <c r="R99" s="20"/>
     </row>
     <row r="100" spans="1:18">
       <c r="A100" s="1"/>
-      <c r="B100" s="17">
-        <f t="shared" si="0"/>
+      <c r="B100" s="16">
+        <f>ROW(B100) - ROW($B$7)</f>
         <v>93</v>
       </c>
       <c r="C100" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D100" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="E100" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="F100" s="20" t="s">
+      <c r="D100" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E100" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="F100" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="G100" s="20" t="s">
-        <v>404</v>
-      </c>
-      <c r="H100" s="20" t="s">
+      <c r="G100" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="H100" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I100" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J100" s="20" t="s">
-        <v>555</v>
-      </c>
-      <c r="K100" s="20" t="s">
-        <v>644</v>
-      </c>
-      <c r="L100" s="20">
+      <c r="J100" s="14" t="s">
+        <v>554</v>
+      </c>
+      <c r="K100" s="14" t="s">
+        <v>643</v>
+      </c>
+      <c r="L100" s="14">
         <v>1</v>
       </c>
       <c r="M100" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N100" s="20">
+      <c r="N100" s="14">
         <v>1100</v>
       </c>
       <c r="O100" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P100" s="21" t="s">
+      <c r="P100" s="15" t="s">
         <v>841</v>
       </c>
-      <c r="Q100" s="21">
-        <f t="shared" ref="Q100" si="45">P100*N100</f>
+      <c r="Q100" s="15">
+        <f>P100*N100</f>
         <v>0.99</v>
       </c>
-      <c r="R100" s="20"/>
+      <c r="R100" s="14"/>
     </row>
     <row r="101" spans="1:18">
       <c r="A101" s="1"/>
-      <c r="B101" s="16">
-        <f>ROW(B101) - ROW($B$7)</f>
+      <c r="B101" s="17">
+        <f t="shared" si="0"/>
         <v>94</v>
       </c>
       <c r="C101" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D101" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="E101" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="F101" s="14" t="s">
+      <c r="D101" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="E101" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="F101" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="G101" s="14" t="s">
-        <v>405</v>
-      </c>
-      <c r="H101" s="14" t="s">
+      <c r="G101" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="H101" s="20" t="s">
         <v>436</v>
       </c>
       <c r="I101" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="J101" s="14" t="s">
-        <v>556</v>
-      </c>
-      <c r="K101" s="14" t="s">
-        <v>645</v>
-      </c>
-      <c r="L101" s="14">
+      <c r="J101" s="20" t="s">
+        <v>555</v>
+      </c>
+      <c r="K101" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="L101" s="20">
         <v>1</v>
       </c>
       <c r="M101" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N101" s="14">
+      <c r="N101" s="20">
         <v>1100</v>
       </c>
       <c r="O101" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P101" s="15" t="s">
-        <v>753</v>
-      </c>
-      <c r="Q101" s="15">
-        <f>P101*N101</f>
-        <v>0.88</v>
-      </c>
-      <c r="R101" s="14"/>
+      <c r="P101" s="21" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q101" s="21">
+        <f t="shared" ref="Q101" si="46">P101*N101</f>
+        <v>0.99</v>
+      </c>
+      <c r="R101" s="20"/>
     </row>
     <row r="102" spans="1:18">
       <c r="A102" s="1"/>
-      <c r="B102" s="17">
+      <c r="B102" s="16">
+        <f>ROW(B102) - ROW($B$7)</f>
+        <v>95</v>
+      </c>
+      <c r="C102" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D102" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E102" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="F102" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="G102" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="H102" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="I102" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="J102" s="14" t="s">
+        <v>556</v>
+      </c>
+      <c r="K102" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="L102" s="14">
+        <v>1</v>
+      </c>
+      <c r="M102" s="14">
+        <f t="shared" si="32"/>
+        <v>1000</v>
+      </c>
+      <c r="N102" s="14">
+        <v>1100</v>
+      </c>
+      <c r="O102" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P102" s="15" t="s">
+        <v>753</v>
+      </c>
+      <c r="Q102" s="15">
+        <f>P102*N102</f>
+        <v>0.88</v>
+      </c>
+      <c r="R102" s="14"/>
+    </row>
+    <row r="103" spans="1:18">
+      <c r="A103" s="1"/>
+      <c r="B103" s="17">
         <f t="shared" si="0"/>
-        <v>95</v>
-      </c>
-      <c r="C102" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C103" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D102" s="20" t="s">
+      <c r="D103" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="E102" s="20" t="s">
+      <c r="E103" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="F102" s="20" t="s">
+      <c r="F103" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="G102" s="20" t="s">
+      <c r="G103" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="H102" s="20" t="s">
+      <c r="H103" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="I102" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="J102" s="20" t="s">
+      <c r="I103" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="J103" s="20" t="s">
         <v>557</v>
       </c>
-      <c r="K102" s="20" t="s">
+      <c r="K103" s="20" t="s">
         <v>646</v>
       </c>
-      <c r="L102" s="20">
+      <c r="L103" s="20">
         <v>2</v>
       </c>
-      <c r="M102" s="14">
-        <f t="shared" si="31"/>
+      <c r="M103" s="14">
+        <f t="shared" si="32"/>
         <v>2000</v>
       </c>
-      <c r="N102" s="20">
+      <c r="N103" s="20">
         <v>2100</v>
       </c>
-      <c r="O102" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P102" s="21" t="s">
+      <c r="O103" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P103" s="21" t="s">
         <v>850</v>
       </c>
-      <c r="Q102" s="21">
-        <f t="shared" ref="Q102" si="46">P102*N102</f>
+      <c r="Q103" s="21">
+        <f t="shared" ref="Q103" si="47">P103*N103</f>
         <v>4.62</v>
       </c>
-      <c r="R102" s="20"/>
-    </row>
-    <row r="103" spans="1:18" ht="25.5">
-      <c r="A103" s="1"/>
-      <c r="B103" s="16">
-        <f>ROW(B103) - ROW($B$7)</f>
-        <v>96</v>
-      </c>
-      <c r="C103" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D103" s="46" t="s">
-        <v>882</v>
-      </c>
-      <c r="E103" s="46" t="s">
-        <v>225</v>
-      </c>
-      <c r="F103" s="46" t="s">
-        <v>304</v>
-      </c>
-      <c r="G103" s="46" t="s">
-        <v>385</v>
-      </c>
-      <c r="H103" s="46" t="s">
-        <v>436</v>
-      </c>
-      <c r="I103" s="46" t="s">
-        <v>670</v>
-      </c>
-      <c r="J103" s="46" t="s">
-        <v>535</v>
-      </c>
-      <c r="K103" s="46" t="s">
-        <v>607</v>
-      </c>
-      <c r="L103" s="46">
-        <v>2</v>
-      </c>
-      <c r="M103" s="14">
-        <f t="shared" si="31"/>
-        <v>2000</v>
-      </c>
-      <c r="N103" s="46" t="s">
-        <v>868</v>
-      </c>
-      <c r="O103" s="50" t="s">
-        <v>670</v>
-      </c>
-      <c r="P103" s="47" t="s">
-        <v>670</v>
-      </c>
-      <c r="Q103" s="47" t="s">
-        <v>670</v>
-      </c>
-      <c r="R103" s="49" t="s">
-        <v>686</v>
-      </c>
+      <c r="R103" s="20"/>
     </row>
     <row r="104" spans="1:18" ht="25.5">
       <c r="A104" s="1"/>
@@ -16856,29 +16867,29 @@
         <f>ROW(B104) - ROW($B$7)</f>
         <v>97</v>
       </c>
-      <c r="C104" s="23" t="s">
+      <c r="C104" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D104" s="42" t="s">
-        <v>884</v>
-      </c>
-      <c r="E104" s="52" t="s">
-        <v>231</v>
-      </c>
-      <c r="F104" s="42" t="s">
+      <c r="D104" s="46" t="s">
+        <v>882</v>
+      </c>
+      <c r="E104" s="46" t="s">
+        <v>225</v>
+      </c>
+      <c r="F104" s="46" t="s">
         <v>304</v>
       </c>
-      <c r="G104" s="52" t="s">
-        <v>391</v>
-      </c>
-      <c r="H104" s="42" t="s">
+      <c r="G104" s="46" t="s">
+        <v>385</v>
+      </c>
+      <c r="H104" s="46" t="s">
         <v>436</v>
       </c>
       <c r="I104" s="46" t="s">
         <v>670</v>
       </c>
       <c r="J104" s="46" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="K104" s="46" t="s">
         <v>607</v>
@@ -16887,11 +16898,11 @@
         <v>2</v>
       </c>
       <c r="M104" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>2000</v>
       </c>
-      <c r="N104" s="46">
-        <v>2000</v>
+      <c r="N104" s="46" t="s">
+        <v>868</v>
       </c>
       <c r="O104" s="50" t="s">
         <v>670</v>
@@ -16906,579 +16917,579 @@
         <v>686</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="36">
+    <row r="105" spans="1:18" ht="25.5">
       <c r="A105" s="1"/>
-      <c r="B105" s="17">
+      <c r="B105" s="16">
+        <f>ROW(B105) - ROW($B$7)</f>
+        <v>98</v>
+      </c>
+      <c r="C105" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D105" s="42" t="s">
+        <v>884</v>
+      </c>
+      <c r="E105" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="F105" s="42" t="s">
+        <v>304</v>
+      </c>
+      <c r="G105" s="52" t="s">
+        <v>391</v>
+      </c>
+      <c r="H105" s="42" t="s">
+        <v>436</v>
+      </c>
+      <c r="I105" s="46" t="s">
+        <v>670</v>
+      </c>
+      <c r="J105" s="46" t="s">
+        <v>541</v>
+      </c>
+      <c r="K105" s="46" t="s">
+        <v>607</v>
+      </c>
+      <c r="L105" s="46">
+        <v>2</v>
+      </c>
+      <c r="M105" s="14">
+        <f t="shared" si="32"/>
+        <v>2000</v>
+      </c>
+      <c r="N105" s="46">
+        <v>2000</v>
+      </c>
+      <c r="O105" s="50" t="s">
+        <v>670</v>
+      </c>
+      <c r="P105" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="Q105" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="R105" s="49" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" ht="36">
+      <c r="A106" s="1"/>
+      <c r="B106" s="17">
         <f t="shared" si="0"/>
-        <v>98</v>
-      </c>
-      <c r="C105" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="C106" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D105" s="20" t="s">
+      <c r="D106" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="E105" s="20" t="s">
+      <c r="E106" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="F105" s="20" t="s">
+      <c r="F106" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="G105" s="20" t="s">
+      <c r="G106" s="20" t="s">
         <v>407</v>
       </c>
-      <c r="H105" s="20" t="s">
+      <c r="H106" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="I105" s="20" t="s">
-        <v>670</v>
-      </c>
-      <c r="J105" s="20" t="s">
+      <c r="I106" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="J106" s="20" t="s">
         <v>558</v>
       </c>
-      <c r="K105" s="20" t="s">
+      <c r="K106" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="L105" s="20">
+      <c r="L106" s="20">
         <v>1</v>
       </c>
-      <c r="M105" s="14">
-        <f t="shared" si="31"/>
+      <c r="M106" s="14">
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N105" s="20">
+      <c r="N106" s="20">
         <v>1020</v>
       </c>
-      <c r="O105" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P105" s="21" t="s">
+      <c r="O106" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P106" s="21" t="s">
         <v>851</v>
       </c>
-      <c r="Q105" s="21">
-        <f t="shared" ref="Q105" si="47">P105*N105</f>
+      <c r="Q106" s="21">
+        <f t="shared" ref="Q106" si="48">P106*N106</f>
         <v>15.606</v>
       </c>
-      <c r="R105" s="20"/>
-    </row>
-    <row r="106" spans="1:18">
-      <c r="A106" s="1"/>
-      <c r="B106" s="16">
-        <f>ROW(B106) - ROW($B$7)</f>
-        <v>99</v>
-      </c>
-      <c r="C106" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D106" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="E106" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="F106" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="G106" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="H106" s="14" t="s">
-        <v>436</v>
-      </c>
-      <c r="I106" s="20" t="s">
-        <v>670</v>
-      </c>
-      <c r="J106" s="14" t="s">
-        <v>559</v>
-      </c>
-      <c r="K106" s="14" t="s">
-        <v>648</v>
-      </c>
-      <c r="L106" s="14">
-        <v>1</v>
-      </c>
-      <c r="M106" s="14">
-        <f t="shared" si="31"/>
-        <v>1000</v>
-      </c>
-      <c r="N106" s="14">
-        <v>1100</v>
-      </c>
-      <c r="O106" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P106" s="15" t="s">
-        <v>841</v>
-      </c>
-      <c r="Q106" s="15">
-        <f>P106*N106</f>
-        <v>0.99</v>
-      </c>
-      <c r="R106" s="14"/>
+      <c r="R106" s="20"/>
     </row>
     <row r="107" spans="1:18">
       <c r="A107" s="1"/>
-      <c r="B107" s="17">
-        <f t="shared" si="0"/>
+      <c r="B107" s="16">
+        <f>ROW(B107) - ROW($B$7)</f>
         <v>100</v>
       </c>
-      <c r="C107" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D107" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="E107" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="F107" s="20" t="s">
+      <c r="C107" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D107" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E107" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="F107" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="G107" s="20" t="s">
-        <v>409</v>
-      </c>
-      <c r="H107" s="20" t="s">
+      <c r="G107" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="H107" s="14" t="s">
         <v>436</v>
       </c>
       <c r="I107" s="20" t="s">
         <v>670</v>
       </c>
-      <c r="J107" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="K107" s="20" t="s">
-        <v>649</v>
-      </c>
-      <c r="L107" s="20">
+      <c r="J107" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="K107" s="14" t="s">
+        <v>648</v>
+      </c>
+      <c r="L107" s="14">
         <v>1</v>
       </c>
       <c r="M107" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N107" s="20">
+      <c r="N107" s="14">
         <v>1100</v>
       </c>
       <c r="O107" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P107" s="21" t="s">
-        <v>845</v>
-      </c>
-      <c r="Q107" s="21">
-        <f t="shared" ref="Q107" si="48">P107*N107</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="R107" s="20"/>
+      <c r="P107" s="15" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q107" s="15">
+        <f>P107*N107</f>
+        <v>0.99</v>
+      </c>
+      <c r="R107" s="14"/>
     </row>
     <row r="108" spans="1:18">
       <c r="A108" s="1"/>
-      <c r="B108" s="16">
-        <f>ROW(B108) - ROW($B$7)</f>
+      <c r="B108" s="17">
+        <f t="shared" si="0"/>
         <v>101</v>
       </c>
-      <c r="C108" s="22" t="s">
+      <c r="C108" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D108" s="14" t="s">
+      <c r="D108" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="E108" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="F108" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="G108" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="H108" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="I108" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="J108" s="20" t="s">
+        <v>560</v>
+      </c>
+      <c r="K108" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="L108" s="20">
+        <v>1</v>
+      </c>
+      <c r="M108" s="14">
+        <f t="shared" si="32"/>
+        <v>1000</v>
+      </c>
+      <c r="N108" s="20">
+        <v>1100</v>
+      </c>
+      <c r="O108" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P108" s="21" t="s">
+        <v>845</v>
+      </c>
+      <c r="Q108" s="21">
+        <f t="shared" ref="Q108" si="49">P108*N108</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R108" s="20"/>
+    </row>
+    <row r="109" spans="1:18">
+      <c r="A109" s="1"/>
+      <c r="B109" s="16">
+        <f>ROW(B109) - ROW($B$7)</f>
+        <v>102</v>
+      </c>
+      <c r="C109" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D109" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="E108" s="14" t="s">
+      <c r="E109" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="F108" s="14" t="s">
+      <c r="F109" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="G108" s="14" t="s">
+      <c r="G109" s="14" t="s">
         <v>410</v>
       </c>
-      <c r="H108" s="14" t="s">
+      <c r="H109" s="14" t="s">
         <v>436</v>
       </c>
-      <c r="I108" s="20" t="s">
-        <v>670</v>
-      </c>
-      <c r="J108" s="14" t="s">
+      <c r="I109" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="J109" s="14" t="s">
         <v>561</v>
       </c>
-      <c r="K108" s="14" t="s">
+      <c r="K109" s="14" t="s">
         <v>620</v>
       </c>
-      <c r="L108" s="14">
+      <c r="L109" s="14">
         <v>1</v>
       </c>
-      <c r="M108" s="14">
-        <f t="shared" si="31"/>
+      <c r="M109" s="14">
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N108" s="14">
+      <c r="N109" s="14">
         <v>1100</v>
       </c>
-      <c r="O108" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P108" s="15" t="s">
+      <c r="O109" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P109" s="15" t="s">
         <v>753</v>
       </c>
-      <c r="Q108" s="15">
-        <f>P108*N108</f>
+      <c r="Q109" s="15">
+        <f>P109*N109</f>
         <v>0.88</v>
       </c>
-      <c r="R108" s="14"/>
-    </row>
-    <row r="109" spans="1:18" ht="25.5">
-      <c r="A109" s="1"/>
-      <c r="B109" s="17">
+      <c r="R109" s="14"/>
+    </row>
+    <row r="110" spans="1:18" ht="25.5">
+      <c r="A110" s="1"/>
+      <c r="B110" s="17">
         <f t="shared" si="0"/>
-        <v>102</v>
-      </c>
-      <c r="C109" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="C110" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D109" s="46" t="s">
+      <c r="D110" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="E109" s="46" t="s">
+      <c r="E110" s="46" t="s">
         <v>243</v>
       </c>
-      <c r="F109" s="46" t="s">
+      <c r="F110" s="46" t="s">
         <v>304</v>
       </c>
-      <c r="G109" s="46" t="s">
+      <c r="G110" s="46" t="s">
         <v>402</v>
       </c>
-      <c r="H109" s="46" t="s">
+      <c r="H110" s="46" t="s">
         <v>436</v>
       </c>
-      <c r="I109" s="46" t="s">
-        <v>670</v>
-      </c>
-      <c r="J109" s="46" t="s">
+      <c r="I110" s="46" t="s">
+        <v>670</v>
+      </c>
+      <c r="J110" s="46" t="s">
         <v>553</v>
       </c>
-      <c r="K109" s="46" t="s">
+      <c r="K110" s="46" t="s">
         <v>607</v>
       </c>
-      <c r="L109" s="46">
+      <c r="L110" s="46">
         <v>1</v>
       </c>
-      <c r="M109" s="14">
-        <f t="shared" si="31"/>
+      <c r="M110" s="14">
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N109" s="46" t="s">
+      <c r="N110" s="46" t="s">
         <v>867</v>
       </c>
-      <c r="O109" s="50" t="s">
-        <v>670</v>
-      </c>
-      <c r="P109" s="47" t="s">
-        <v>670</v>
-      </c>
-      <c r="Q109" s="47" t="s">
-        <v>670</v>
-      </c>
-      <c r="R109" s="49" t="s">
+      <c r="O110" s="50" t="s">
+        <v>670</v>
+      </c>
+      <c r="P110" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="Q110" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="R110" s="49" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="110" spans="1:18">
-      <c r="A110" s="1"/>
-      <c r="B110" s="16">
-        <f>ROW(B110) - ROW($B$7)</f>
-        <v>103</v>
-      </c>
-      <c r="C110" s="22" t="s">
+    <row r="111" spans="1:18">
+      <c r="A111" s="1"/>
+      <c r="B111" s="16">
+        <f>ROW(B111) - ROW($B$7)</f>
+        <v>104</v>
+      </c>
+      <c r="C111" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D110" s="14" t="s">
+      <c r="D111" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E110" s="14" t="s">
+      <c r="E111" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="F110" s="14" t="s">
+      <c r="F111" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="G110" s="14" t="s">
+      <c r="G111" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="H110" s="14" t="s">
+      <c r="H111" s="14" t="s">
         <v>436</v>
       </c>
-      <c r="I110" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="J110" s="14" t="s">
+      <c r="I111" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="J111" s="14" t="s">
         <v>562</v>
       </c>
-      <c r="K110" s="14" t="s">
+      <c r="K111" s="14" t="s">
         <v>611</v>
       </c>
-      <c r="L110" s="14">
+      <c r="L111" s="14">
         <v>1</v>
       </c>
-      <c r="M110" s="14">
-        <f t="shared" si="31"/>
+      <c r="M111" s="14">
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N110" s="14">
+      <c r="N111" s="14">
         <v>1100</v>
       </c>
-      <c r="O110" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P110" s="15" t="s">
+      <c r="O111" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P111" s="15" t="s">
         <v>841</v>
       </c>
-      <c r="Q110" s="15">
-        <f>P110*N110</f>
+      <c r="Q111" s="15">
+        <f>P111*N111</f>
         <v>0.99</v>
       </c>
-      <c r="R110" s="14"/>
-    </row>
-    <row r="111" spans="1:18" ht="25.5">
-      <c r="A111" s="1"/>
-      <c r="B111" s="17">
+      <c r="R111" s="14"/>
+    </row>
+    <row r="112" spans="1:18" ht="25.5">
+      <c r="A112" s="1"/>
+      <c r="B112" s="17">
         <f t="shared" si="0"/>
-        <v>104</v>
-      </c>
-      <c r="C111" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C112" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D111" s="46" t="s">
+      <c r="D112" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="E111" s="46" t="s">
+      <c r="E112" s="46" t="s">
         <v>251</v>
       </c>
-      <c r="F111" s="46" t="s">
+      <c r="F112" s="46" t="s">
         <v>304</v>
       </c>
-      <c r="G111" s="46" t="s">
+      <c r="G112" s="46" t="s">
         <v>410</v>
       </c>
-      <c r="H111" s="46" t="s">
+      <c r="H112" s="46" t="s">
         <v>436</v>
       </c>
-      <c r="I111" s="46" t="s">
-        <v>670</v>
-      </c>
-      <c r="J111" s="46" t="s">
+      <c r="I112" s="46" t="s">
+        <v>670</v>
+      </c>
+      <c r="J112" s="46" t="s">
         <v>561</v>
       </c>
-      <c r="K111" s="46" t="s">
+      <c r="K112" s="46" t="s">
         <v>607</v>
       </c>
-      <c r="L111" s="46">
+      <c r="L112" s="46">
         <v>1</v>
       </c>
-      <c r="M111" s="14">
-        <f t="shared" si="31"/>
+      <c r="M112" s="14">
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N111" s="46" t="s">
+      <c r="N112" s="46" t="s">
         <v>867</v>
       </c>
-      <c r="O111" s="50" t="s">
-        <v>670</v>
-      </c>
-      <c r="P111" s="47" t="s">
-        <v>670</v>
-      </c>
-      <c r="Q111" s="47" t="s">
-        <v>670</v>
-      </c>
-      <c r="R111" s="49" t="s">
+      <c r="O112" s="50" t="s">
+        <v>670</v>
+      </c>
+      <c r="P112" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="Q112" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="R112" s="49" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="112" spans="1:18">
-      <c r="A112" s="1"/>
-      <c r="B112" s="16">
-        <f>ROW(B112) - ROW($B$7)</f>
-        <v>105</v>
-      </c>
-      <c r="C112" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D112" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="E112" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="F112" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="G112" s="14" t="s">
-        <v>412</v>
-      </c>
-      <c r="H112" s="14" t="s">
-        <v>436</v>
-      </c>
-      <c r="I112" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="J112" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="K112" s="14" t="s">
-        <v>650</v>
-      </c>
-      <c r="L112" s="14">
-        <v>4</v>
-      </c>
-      <c r="M112" s="14">
-        <f t="shared" si="31"/>
-        <v>4000</v>
-      </c>
-      <c r="N112" s="14">
-        <v>4100</v>
-      </c>
-      <c r="O112" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P112" s="15" t="s">
-        <v>841</v>
-      </c>
-      <c r="Q112" s="15">
-        <f>P112*N112</f>
-        <v>3.69</v>
-      </c>
-      <c r="R112" s="14"/>
     </row>
     <row r="113" spans="1:18">
       <c r="A113" s="1"/>
-      <c r="B113" s="17">
+      <c r="B113" s="16">
+        <f>ROW(B113) - ROW($B$7)</f>
+        <v>106</v>
+      </c>
+      <c r="C113" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D113" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E113" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="F113" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="G113" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="H113" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="I113" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="J113" s="14" t="s">
+        <v>563</v>
+      </c>
+      <c r="K113" s="14" t="s">
+        <v>650</v>
+      </c>
+      <c r="L113" s="14">
+        <v>4</v>
+      </c>
+      <c r="M113" s="14">
+        <f t="shared" si="32"/>
+        <v>4000</v>
+      </c>
+      <c r="N113" s="14">
+        <v>4100</v>
+      </c>
+      <c r="O113" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P113" s="15" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q113" s="15">
+        <f>P113*N113</f>
+        <v>3.69</v>
+      </c>
+      <c r="R113" s="14"/>
+    </row>
+    <row r="114" spans="1:18">
+      <c r="A114" s="1"/>
+      <c r="B114" s="17">
         <f t="shared" si="0"/>
-        <v>106</v>
-      </c>
-      <c r="C113" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C114" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D113" s="20" t="s">
+      <c r="D114" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="E113" s="20" t="s">
+      <c r="E114" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="F113" s="20" t="s">
+      <c r="F114" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="G113" s="20" t="s">
+      <c r="G114" s="20" t="s">
         <v>413</v>
       </c>
-      <c r="H113" s="20" t="s">
+      <c r="H114" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="I113" s="20" t="s">
-        <v>670</v>
-      </c>
-      <c r="J113" s="20" t="s">
+      <c r="I114" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="J114" s="20" t="s">
         <v>564</v>
       </c>
-      <c r="K113" s="20" t="s">
+      <c r="K114" s="20" t="s">
         <v>621</v>
       </c>
-      <c r="L113" s="20">
+      <c r="L114" s="20">
         <v>1</v>
       </c>
-      <c r="M113" s="14">
-        <f t="shared" si="31"/>
+      <c r="M114" s="14">
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N113" s="20">
+      <c r="N114" s="20">
         <v>1100</v>
       </c>
-      <c r="O113" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P113" s="21" t="s">
+      <c r="O114" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P114" s="21" t="s">
         <v>753</v>
       </c>
-      <c r="Q113" s="21">
-        <f t="shared" ref="Q113" si="49">P113*N113</f>
+      <c r="Q114" s="21">
+        <f t="shared" ref="Q114" si="50">P114*N114</f>
         <v>0.88</v>
       </c>
-      <c r="R113" s="20"/>
-    </row>
-    <row r="114" spans="1:18" ht="25.5">
-      <c r="A114" s="1"/>
-      <c r="B114" s="16">
-        <f>ROW(B114) - ROW($B$7)</f>
-        <v>107</v>
-      </c>
-      <c r="C114" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D114" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="E114" s="46" t="s">
-        <v>247</v>
-      </c>
-      <c r="F114" s="46" t="s">
-        <v>304</v>
-      </c>
-      <c r="G114" s="46" t="s">
-        <v>406</v>
-      </c>
-      <c r="H114" s="46" t="s">
-        <v>436</v>
-      </c>
-      <c r="I114" s="46" t="s">
-        <v>670</v>
-      </c>
-      <c r="J114" s="46" t="s">
-        <v>557</v>
-      </c>
-      <c r="K114" s="46" t="s">
-        <v>607</v>
-      </c>
-      <c r="L114" s="46">
-        <v>1</v>
-      </c>
-      <c r="M114" s="14">
-        <f t="shared" si="31"/>
-        <v>1000</v>
-      </c>
-      <c r="N114" s="46" t="s">
-        <v>867</v>
-      </c>
-      <c r="O114" s="50" t="s">
-        <v>670</v>
-      </c>
-      <c r="P114" s="47" t="s">
-        <v>670</v>
-      </c>
-      <c r="Q114" s="47" t="s">
-        <v>670</v>
-      </c>
-      <c r="R114" s="49" t="s">
-        <v>686</v>
-      </c>
+      <c r="R114" s="20"/>
     </row>
     <row r="115" spans="1:18" ht="25.5">
       <c r="A115" s="1"/>
-      <c r="B115" s="17">
-        <f t="shared" si="0"/>
+      <c r="B115" s="16">
+        <f>ROW(B115) - ROW($B$7)</f>
         <v>108</v>
       </c>
-      <c r="C115" s="23" t="s">
-        <v>23</v>
+      <c r="C115" s="22" t="s">
+        <v>22</v>
       </c>
       <c r="D115" s="46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E115" s="46" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="F115" s="46" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G115" s="46" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="H115" s="46" t="s">
         <v>436</v>
@@ -17487,20 +17498,20 @@
         <v>670</v>
       </c>
       <c r="J115" s="46" t="s">
-        <v>531</v>
+        <v>557</v>
       </c>
       <c r="K115" s="46" t="s">
         <v>607</v>
       </c>
       <c r="L115" s="46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M115" s="14">
-        <f t="shared" si="31"/>
-        <v>2000</v>
+        <f t="shared" si="32"/>
+        <v>1000</v>
       </c>
       <c r="N115" s="46" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O115" s="50" t="s">
         <v>670</v>
@@ -17515,7 +17526,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="116" spans="1:18">
+    <row r="116" spans="1:18" ht="25.5">
       <c r="A116" s="1"/>
       <c r="B116" s="17">
         <f t="shared" si="0"/>
@@ -17524,1080 +17535,1081 @@
       <c r="C116" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D116" s="14" t="s">
+      <c r="D116" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="E116" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="F116" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="G116" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="H116" s="46" t="s">
+        <v>436</v>
+      </c>
+      <c r="I116" s="46" t="s">
+        <v>670</v>
+      </c>
+      <c r="J116" s="46" t="s">
+        <v>531</v>
+      </c>
+      <c r="K116" s="46" t="s">
+        <v>607</v>
+      </c>
+      <c r="L116" s="46">
+        <v>2</v>
+      </c>
+      <c r="M116" s="14">
+        <f t="shared" si="32"/>
+        <v>2000</v>
+      </c>
+      <c r="N116" s="46" t="s">
+        <v>868</v>
+      </c>
+      <c r="O116" s="50" t="s">
+        <v>670</v>
+      </c>
+      <c r="P116" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="Q116" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="R116" s="49" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18">
+      <c r="A117" s="1"/>
+      <c r="B117" s="17">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="C117" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D117" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="E116" s="43" t="s">
+      <c r="E117" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="F116" s="14" t="s">
+      <c r="F117" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="G116" s="43" t="s">
+      <c r="G117" s="43" t="s">
         <v>414</v>
       </c>
-      <c r="H116" s="14" t="s">
+      <c r="H117" s="14" t="s">
         <v>436</v>
       </c>
-      <c r="I116" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="J116" s="14" t="s">
+      <c r="I117" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J117" s="14" t="s">
         <v>565</v>
       </c>
-      <c r="K116" s="14" t="s">
+      <c r="K117" s="14" t="s">
         <v>651</v>
       </c>
-      <c r="L116" s="20">
+      <c r="L117" s="20">
         <v>1</v>
       </c>
-      <c r="M116" s="14">
-        <f t="shared" si="31"/>
+      <c r="M117" s="14">
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N116" s="20">
+      <c r="N117" s="20">
         <v>1100</v>
       </c>
-      <c r="O116" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P116" s="21" t="s">
+      <c r="O117" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P117" s="21" t="s">
         <v>839</v>
       </c>
-      <c r="Q116" s="21">
-        <f t="shared" ref="Q116" si="50">P116*N116</f>
+      <c r="Q117" s="21">
+        <f t="shared" ref="Q117" si="51">P117*N117</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="R116" s="20"/>
-    </row>
-    <row r="117" spans="1:18" ht="24">
-      <c r="A117" s="1"/>
-      <c r="B117" s="16">
-        <f>ROW(B117) - ROW($B$7)</f>
-        <v>110</v>
-      </c>
-      <c r="C117" s="22" t="s">
+      <c r="R117" s="20"/>
+    </row>
+    <row r="118" spans="1:18" ht="24">
+      <c r="A118" s="1"/>
+      <c r="B118" s="16">
+        <f>ROW(B118) - ROW($B$7)</f>
+        <v>111</v>
+      </c>
+      <c r="C118" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D117" s="14" t="s">
+      <c r="D118" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="E117" s="14" t="s">
+      <c r="E118" s="14" t="s">
         <v>256</v>
-      </c>
-      <c r="F117" s="20" t="s">
-        <v>672</v>
-      </c>
-      <c r="G117" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="H117" s="14" t="s">
-        <v>455</v>
-      </c>
-      <c r="I117" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="J117" s="14" t="s">
-        <v>566</v>
-      </c>
-      <c r="K117" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="L117" s="14">
-        <v>1</v>
-      </c>
-      <c r="M117" s="14">
-        <f t="shared" si="31"/>
-        <v>1000</v>
-      </c>
-      <c r="N117" s="14">
-        <v>1002</v>
-      </c>
-      <c r="O117" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P117" s="15" t="s">
-        <v>852</v>
-      </c>
-      <c r="Q117" s="15">
-        <f>P117*N117</f>
-        <v>236.27160000000001</v>
-      </c>
-      <c r="R117" s="14"/>
-    </row>
-    <row r="118" spans="1:18" ht="48">
-      <c r="A118" s="1"/>
-      <c r="B118" s="17">
-        <f t="shared" si="0"/>
-        <v>111</v>
-      </c>
-      <c r="C118" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D118" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="E118" s="20" t="s">
-        <v>257</v>
       </c>
       <c r="F118" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="G118" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="H118" s="20" t="s">
-        <v>456</v>
+      <c r="G118" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="H118" s="14" t="s">
+        <v>455</v>
       </c>
       <c r="I118" s="43" t="s">
         <v>670</v>
       </c>
-      <c r="J118" s="20" t="s">
-        <v>567</v>
+      <c r="J118" s="14" t="s">
+        <v>566</v>
       </c>
       <c r="K118" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L118" s="20">
+      <c r="L118" s="14">
         <v>1</v>
       </c>
       <c r="M118" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N118" s="20">
-        <v>1010</v>
+      <c r="N118" s="14">
+        <v>1002</v>
       </c>
       <c r="O118" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P118" s="21" t="s">
-        <v>749</v>
-      </c>
-      <c r="Q118" s="21">
-        <f t="shared" ref="Q118" si="51">P118*N118</f>
-        <v>25.148999999999997</v>
-      </c>
-      <c r="R118" s="20"/>
-    </row>
-    <row r="119" spans="1:18" ht="36">
+      <c r="P118" s="15" t="s">
+        <v>852</v>
+      </c>
+      <c r="Q118" s="15">
+        <f>P118*N118</f>
+        <v>236.27160000000001</v>
+      </c>
+      <c r="R118" s="14"/>
+    </row>
+    <row r="119" spans="1:18" ht="48">
       <c r="A119" s="1"/>
-      <c r="B119" s="16">
-        <f>ROW(B119) - ROW($B$7)</f>
+      <c r="B119" s="17">
+        <f t="shared" si="0"/>
         <v>112</v>
       </c>
-      <c r="C119" s="22" t="s">
+      <c r="C119" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D119" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="E119" s="14" t="s">
-        <v>258</v>
+      <c r="D119" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E119" s="20" t="s">
+        <v>257</v>
       </c>
       <c r="F119" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="G119" s="14" t="s">
+      <c r="G119" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="H119" s="20" t="s">
+        <v>456</v>
+      </c>
+      <c r="I119" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J119" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="K119" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="L119" s="20">
+        <v>1</v>
+      </c>
+      <c r="M119" s="14">
+        <f t="shared" si="32"/>
+        <v>1000</v>
+      </c>
+      <c r="N119" s="20">
+        <v>1010</v>
+      </c>
+      <c r="O119" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P119" s="21" t="s">
+        <v>749</v>
+      </c>
+      <c r="Q119" s="21">
+        <f t="shared" ref="Q119" si="52">P119*N119</f>
+        <v>25.148999999999997</v>
+      </c>
+      <c r="R119" s="20"/>
+    </row>
+    <row r="120" spans="1:18" ht="36">
+      <c r="A120" s="1"/>
+      <c r="B120" s="16">
+        <f>ROW(B120) - ROW($B$7)</f>
+        <v>113</v>
+      </c>
+      <c r="C120" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D120" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E120" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="F120" s="20" t="s">
+        <v>672</v>
+      </c>
+      <c r="G120" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="H119" s="14" t="s">
+      <c r="H120" s="14" t="s">
         <v>456</v>
       </c>
-      <c r="I119" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="J119" s="14" t="s">
+      <c r="I120" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J120" s="14" t="s">
         <v>568</v>
       </c>
-      <c r="K119" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="L119" s="14">
+      <c r="K120" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="L120" s="14">
         <v>4</v>
       </c>
-      <c r="M119" s="14">
-        <f t="shared" si="31"/>
+      <c r="M120" s="14">
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
-      <c r="N119" s="14">
+      <c r="N120" s="14">
         <v>4010</v>
       </c>
-      <c r="O119" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P119" s="15" t="s">
+      <c r="O120" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P120" s="15" t="s">
         <v>853</v>
       </c>
-      <c r="Q119" s="15">
-        <f>P119*N119</f>
+      <c r="Q120" s="15">
+        <f>P120*N120</f>
         <v>124.711</v>
       </c>
-      <c r="R119" s="14"/>
-    </row>
-    <row r="120" spans="1:18" ht="24">
-      <c r="A120" s="1"/>
-      <c r="B120" s="17">
-        <f t="shared" si="0"/>
-        <v>113</v>
-      </c>
-      <c r="C120" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D120" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="E120" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="F120" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="G120" s="20" t="s">
-        <v>415</v>
-      </c>
-      <c r="H120" s="20" t="s">
-        <v>457</v>
-      </c>
-      <c r="I120" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="J120" s="20" t="s">
-        <v>569</v>
-      </c>
-      <c r="K120" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="L120" s="20">
-        <v>1</v>
-      </c>
-      <c r="M120" s="14">
-        <f t="shared" si="31"/>
-        <v>1000</v>
-      </c>
-      <c r="N120" s="20">
-        <v>1002</v>
-      </c>
-      <c r="O120" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P120" s="21" t="s">
-        <v>854</v>
-      </c>
-      <c r="Q120" s="21">
-        <f t="shared" ref="Q120" si="52">P120*N120</f>
-        <v>3458.904</v>
-      </c>
-      <c r="R120" s="20"/>
+      <c r="R120" s="14"/>
     </row>
     <row r="121" spans="1:18" ht="24">
       <c r="A121" s="1"/>
-      <c r="B121" s="16">
-        <f>ROW(B121) - ROW($B$7)</f>
+      <c r="B121" s="17">
+        <f t="shared" si="0"/>
         <v>114</v>
       </c>
-      <c r="C121" s="22" t="s">
+      <c r="C121" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D121" s="14" t="s">
+      <c r="D121" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="E121" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="F121" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="G121" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="H121" s="20" t="s">
+        <v>457</v>
+      </c>
+      <c r="I121" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J121" s="20" t="s">
+        <v>569</v>
+      </c>
+      <c r="K121" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="L121" s="20">
+        <v>1</v>
+      </c>
+      <c r="M121" s="14">
+        <f t="shared" si="32"/>
+        <v>1000</v>
+      </c>
+      <c r="N121" s="20">
+        <v>1002</v>
+      </c>
+      <c r="O121" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P121" s="21" t="s">
+        <v>854</v>
+      </c>
+      <c r="Q121" s="21">
+        <f t="shared" ref="Q121" si="53">P121*N121</f>
+        <v>3458.904</v>
+      </c>
+      <c r="R121" s="20"/>
+    </row>
+    <row r="122" spans="1:18" ht="24">
+      <c r="A122" s="1"/>
+      <c r="B122" s="16">
+        <f>ROW(B122) - ROW($B$7)</f>
+        <v>115</v>
+      </c>
+      <c r="C122" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D122" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="E121" s="14" t="s">
+      <c r="E122" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="F121" s="14" t="s">
+      <c r="F122" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="G121" s="14" t="s">
+      <c r="G122" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="H121" s="14" t="s">
+      <c r="H122" s="14" t="s">
         <v>458</v>
       </c>
-      <c r="I121" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="J121" s="14" t="s">
+      <c r="I122" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J122" s="14" t="s">
         <v>570</v>
       </c>
-      <c r="K121" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="L121" s="14">
+      <c r="K122" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="L122" s="14">
         <v>1</v>
       </c>
-      <c r="M121" s="14">
-        <f t="shared" si="31"/>
+      <c r="M122" s="14">
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N121" s="14">
+      <c r="N122" s="14">
         <v>1002</v>
       </c>
-      <c r="O121" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P121" s="15" t="s">
+      <c r="O122" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P122" s="15" t="s">
         <v>855</v>
       </c>
-      <c r="Q121" s="15">
-        <f>P121*N121</f>
+      <c r="Q122" s="15">
+        <f>P122*N122</f>
         <v>408.9162</v>
       </c>
-      <c r="R121" s="14"/>
-    </row>
-    <row r="122" spans="1:18" ht="36">
-      <c r="A122" s="1"/>
-      <c r="B122" s="17">
+      <c r="R122" s="14"/>
+    </row>
+    <row r="123" spans="1:18" ht="36">
+      <c r="A123" s="1"/>
+      <c r="B123" s="17">
         <f t="shared" si="0"/>
-        <v>115</v>
-      </c>
-      <c r="C122" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C123" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D122" s="20" t="s">
+      <c r="D123" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="E122" s="20" t="s">
+      <c r="E123" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="F122" s="20" t="s">
+      <c r="F123" s="20" t="s">
         <v>310</v>
       </c>
-      <c r="G122" s="20" t="s">
+      <c r="G123" s="20" t="s">
         <v>417</v>
       </c>
-      <c r="H122" s="20" t="s">
+      <c r="H123" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="I122" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="J122" s="20" t="s">
+      <c r="I123" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J123" s="20" t="s">
         <v>571</v>
       </c>
-      <c r="K122" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="L122" s="20">
+      <c r="K123" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="L123" s="20">
         <v>1</v>
       </c>
-      <c r="M122" s="14">
-        <f t="shared" si="31"/>
+      <c r="M123" s="14">
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N122" s="20">
+      <c r="N123" s="20">
         <v>1002</v>
       </c>
-      <c r="O122" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P122" s="21" t="s">
+      <c r="O123" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P123" s="21" t="s">
         <v>856</v>
       </c>
-      <c r="Q122" s="21">
-        <f t="shared" ref="Q122" si="53">P122*N122</f>
+      <c r="Q123" s="21">
+        <f t="shared" ref="Q123" si="54">P123*N123</f>
         <v>277.8546</v>
       </c>
-      <c r="R122" s="20"/>
-    </row>
-    <row r="123" spans="1:18" ht="24">
-      <c r="A123" s="1"/>
-      <c r="B123" s="16">
-        <f>ROW(B123) - ROW($B$7)</f>
-        <v>116</v>
-      </c>
-      <c r="C123" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D123" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="E123" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="F123" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="G123" s="14" t="s">
-        <v>418</v>
-      </c>
-      <c r="H123" s="14" t="s">
-        <v>460</v>
-      </c>
-      <c r="I123" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="J123" s="14" t="s">
-        <v>572</v>
-      </c>
-      <c r="K123" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="L123" s="14">
-        <v>1</v>
-      </c>
-      <c r="M123" s="14">
-        <f t="shared" si="31"/>
-        <v>1000</v>
-      </c>
-      <c r="N123" s="14">
-        <v>1002</v>
-      </c>
-      <c r="O123" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P123" s="15" t="s">
-        <v>857</v>
-      </c>
-      <c r="Q123" s="15">
-        <f>P123*N123</f>
-        <v>320.23919999999998</v>
-      </c>
-      <c r="R123" s="14"/>
+      <c r="R123" s="20"/>
     </row>
     <row r="124" spans="1:18" ht="24">
       <c r="A124" s="1"/>
-      <c r="B124" s="17">
-        <f t="shared" si="0"/>
+      <c r="B124" s="16">
+        <f>ROW(B124) - ROW($B$7)</f>
         <v>117</v>
       </c>
-      <c r="C124" s="23" t="s">
+      <c r="C124" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D124" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="E124" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="F124" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="G124" s="20" t="s">
-        <v>419</v>
-      </c>
-      <c r="H124" s="20" t="s">
-        <v>461</v>
+      <c r="D124" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="E124" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="F124" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="G124" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="H124" s="14" t="s">
+        <v>460</v>
       </c>
       <c r="I124" s="43" t="s">
         <v>670</v>
       </c>
-      <c r="J124" s="20" t="s">
-        <v>573</v>
+      <c r="J124" s="14" t="s">
+        <v>572</v>
       </c>
       <c r="K124" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L124" s="20">
+      <c r="L124" s="14">
         <v>1</v>
       </c>
       <c r="M124" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N124" s="20">
+      <c r="N124" s="14">
         <v>1002</v>
       </c>
       <c r="O124" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P124" s="21" t="s">
-        <v>858</v>
-      </c>
-      <c r="Q124" s="21">
-        <f t="shared" ref="Q124" si="54">P124*N124</f>
-        <v>239.77860000000001</v>
-      </c>
-      <c r="R124" s="20"/>
+      <c r="P124" s="15" t="s">
+        <v>857</v>
+      </c>
+      <c r="Q124" s="15">
+        <f>P124*N124</f>
+        <v>320.23919999999998</v>
+      </c>
+      <c r="R124" s="14"/>
     </row>
     <row r="125" spans="1:18" ht="24">
       <c r="A125" s="1"/>
-      <c r="B125" s="16">
-        <f>ROW(B125) - ROW($B$7)</f>
+      <c r="B125" s="17">
+        <f t="shared" si="0"/>
         <v>118</v>
       </c>
-      <c r="C125" s="22" t="s">
+      <c r="C125" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D125" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="E125" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="F125" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="G125" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="H125" s="14" t="s">
+      <c r="D125" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="E125" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="F125" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="G125" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="H125" s="20" t="s">
         <v>461</v>
       </c>
       <c r="I125" s="43" t="s">
         <v>670</v>
       </c>
-      <c r="J125" s="14" t="s">
-        <v>574</v>
+      <c r="J125" s="20" t="s">
+        <v>573</v>
       </c>
       <c r="K125" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L125" s="14">
+      <c r="L125" s="20">
         <v>1</v>
       </c>
       <c r="M125" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N125" s="14">
+      <c r="N125" s="20">
         <v>1002</v>
       </c>
       <c r="O125" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P125" s="15" t="s">
-        <v>859</v>
-      </c>
-      <c r="Q125" s="15">
-        <f>P125*N125</f>
-        <v>264.52800000000002</v>
-      </c>
-      <c r="R125" s="14"/>
+      <c r="P125" s="21" t="s">
+        <v>858</v>
+      </c>
+      <c r="Q125" s="21">
+        <f t="shared" ref="Q125" si="55">P125*N125</f>
+        <v>239.77860000000001</v>
+      </c>
+      <c r="R125" s="20"/>
     </row>
     <row r="126" spans="1:18" ht="24">
       <c r="A126" s="1"/>
-      <c r="B126" s="17">
-        <f t="shared" si="0"/>
+      <c r="B126" s="16">
+        <f>ROW(B126) - ROW($B$7)</f>
         <v>119</v>
       </c>
-      <c r="C126" s="23" t="s">
+      <c r="C126" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D126" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="E126" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="F126" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="G126" s="20" t="s">
-        <v>421</v>
-      </c>
-      <c r="H126" s="20" t="s">
+      <c r="D126" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E126" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="F126" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="G126" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="H126" s="14" t="s">
         <v>461</v>
       </c>
       <c r="I126" s="43" t="s">
         <v>670</v>
       </c>
-      <c r="J126" s="20" t="s">
-        <v>575</v>
+      <c r="J126" s="14" t="s">
+        <v>574</v>
       </c>
       <c r="K126" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L126" s="20">
+      <c r="L126" s="14">
         <v>1</v>
       </c>
       <c r="M126" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N126" s="20">
-        <v>1005</v>
+      <c r="N126" s="14">
+        <v>1002</v>
       </c>
       <c r="O126" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P126" s="21" t="s">
-        <v>860</v>
-      </c>
-      <c r="Q126" s="21">
-        <f t="shared" ref="Q126" si="55">P126*N126</f>
-        <v>53.164500000000004</v>
-      </c>
-      <c r="R126" s="20"/>
+      <c r="P126" s="15" t="s">
+        <v>859</v>
+      </c>
+      <c r="Q126" s="15">
+        <f>P126*N126</f>
+        <v>264.52800000000002</v>
+      </c>
+      <c r="R126" s="14"/>
     </row>
     <row r="127" spans="1:18" ht="24">
       <c r="A127" s="1"/>
-      <c r="B127" s="16">
-        <f>ROW(B127) - ROW($B$7)</f>
+      <c r="B127" s="17">
+        <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="C127" s="22" t="s">
+      <c r="C127" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D127" s="14" t="s">
+      <c r="D127" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="E127" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="F127" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="G127" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="H127" s="20" t="s">
+        <v>461</v>
+      </c>
+      <c r="I127" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J127" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="K127" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="L127" s="20">
+        <v>1</v>
+      </c>
+      <c r="M127" s="14">
+        <f t="shared" si="32"/>
+        <v>1000</v>
+      </c>
+      <c r="N127" s="20">
+        <v>1005</v>
+      </c>
+      <c r="O127" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P127" s="21" t="s">
+        <v>860</v>
+      </c>
+      <c r="Q127" s="21">
+        <f t="shared" ref="Q127" si="56">P127*N127</f>
+        <v>53.164500000000004</v>
+      </c>
+      <c r="R127" s="20"/>
+    </row>
+    <row r="128" spans="1:18" ht="24">
+      <c r="A128" s="1"/>
+      <c r="B128" s="16">
+        <f>ROW(B128) - ROW($B$7)</f>
+        <v>121</v>
+      </c>
+      <c r="C128" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D128" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E127" s="14" t="s">
+      <c r="E128" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="F127" s="14" t="s">
+      <c r="F128" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="G127" s="14" t="s">
+      <c r="G128" s="14" t="s">
         <v>422</v>
       </c>
-      <c r="H127" s="14" t="s">
+      <c r="H128" s="14" t="s">
         <v>461</v>
       </c>
-      <c r="I127" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="J127" s="14" t="s">
+      <c r="I128" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J128" s="14" t="s">
         <v>576</v>
       </c>
-      <c r="K127" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="L127" s="14">
+      <c r="K128" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="L128" s="14">
         <v>1</v>
       </c>
-      <c r="M127" s="14">
-        <f t="shared" si="31"/>
+      <c r="M128" s="14">
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N127" s="14">
+      <c r="N128" s="14">
         <v>1002</v>
       </c>
-      <c r="O127" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P127" s="15" t="s">
+      <c r="O128" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P128" s="15" t="s">
         <v>861</v>
       </c>
-      <c r="Q127" s="15">
-        <f>P127*N127</f>
+      <c r="Q128" s="15">
+        <f>P128*N128</f>
         <v>254.50800000000001</v>
       </c>
-      <c r="R127" s="14"/>
-    </row>
-    <row r="128" spans="1:18">
-      <c r="A128" s="1"/>
-      <c r="B128" s="17">
+      <c r="R128" s="14"/>
+    </row>
+    <row r="129" spans="1:18">
+      <c r="A129" s="1"/>
+      <c r="B129" s="17">
         <f t="shared" si="0"/>
-        <v>121</v>
-      </c>
-      <c r="C128" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C129" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D128" s="20" t="s">
+      <c r="D129" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="E128" s="20" t="s">
+      <c r="E129" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="F128" s="20" t="s">
+      <c r="F129" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="G128" s="20" t="s">
+      <c r="G129" s="20" t="s">
         <v>423</v>
       </c>
-      <c r="H128" s="20" t="s">
+      <c r="H129" s="20" t="s">
         <v>462</v>
       </c>
-      <c r="I128" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="J128" s="20" t="s">
+      <c r="I129" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J129" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="K128" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="L128" s="20">
+      <c r="K129" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="L129" s="20">
         <v>1</v>
       </c>
-      <c r="M128" s="14">
-        <f t="shared" si="31"/>
+      <c r="M129" s="14">
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N128" s="20">
+      <c r="N129" s="20">
         <v>1005</v>
       </c>
-      <c r="O128" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P128" s="21" t="s">
+      <c r="O129" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P129" s="21" t="s">
         <v>862</v>
       </c>
-      <c r="Q128" s="21">
-        <f t="shared" ref="Q128" si="56">P128*N128</f>
+      <c r="Q129" s="21">
+        <f t="shared" ref="Q129" si="57">P129*N129</f>
         <v>86.631</v>
       </c>
-      <c r="R128" s="20"/>
-    </row>
-    <row r="129" spans="1:18" ht="24">
-      <c r="A129" s="1"/>
-      <c r="B129" s="16">
-        <f>ROW(B129) - ROW($B$7)</f>
-        <v>122</v>
-      </c>
-      <c r="C129" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D129" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="E129" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="F129" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="G129" s="14" t="s">
-        <v>424</v>
-      </c>
-      <c r="H129" s="14" t="s">
-        <v>461</v>
-      </c>
-      <c r="I129" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="J129" s="14" t="s">
-        <v>690</v>
-      </c>
-      <c r="K129" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="L129" s="14">
-        <v>1</v>
-      </c>
-      <c r="M129" s="14">
-        <f t="shared" si="31"/>
-        <v>1000</v>
-      </c>
-      <c r="N129" s="14">
-        <v>1002</v>
-      </c>
-      <c r="O129" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P129" s="15" t="s">
-        <v>863</v>
-      </c>
-      <c r="Q129" s="15">
-        <f>P129*N129</f>
-        <v>1188.0714</v>
-      </c>
-      <c r="R129" s="14"/>
+      <c r="R129" s="20"/>
     </row>
     <row r="130" spans="1:18" ht="24">
       <c r="A130" s="1"/>
-      <c r="B130" s="17">
-        <f t="shared" si="0"/>
+      <c r="B130" s="16">
+        <f>ROW(B130) - ROW($B$7)</f>
         <v>123</v>
       </c>
-      <c r="C130" s="23" t="s">
+      <c r="C130" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D130" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="E130" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="F130" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="G130" s="20" t="s">
-        <v>425</v>
-      </c>
-      <c r="H130" s="20" t="s">
-        <v>463</v>
+      <c r="D130" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E130" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="F130" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="G130" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="H130" s="14" t="s">
+        <v>461</v>
       </c>
       <c r="I130" s="43" t="s">
         <v>670</v>
       </c>
-      <c r="J130" s="20" t="s">
-        <v>578</v>
+      <c r="J130" s="14" t="s">
+        <v>690</v>
       </c>
       <c r="K130" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L130" s="20">
+      <c r="L130" s="14">
         <v>1</v>
       </c>
       <c r="M130" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N130" s="20">
+      <c r="N130" s="14">
         <v>1002</v>
       </c>
       <c r="O130" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P130" s="21" t="s">
-        <v>864</v>
-      </c>
-      <c r="Q130" s="21">
-        <f t="shared" ref="Q130" si="57">P130*N130</f>
-        <v>205.41</v>
-      </c>
-      <c r="R130" s="20"/>
+      <c r="P130" s="15" t="s">
+        <v>863</v>
+      </c>
+      <c r="Q130" s="15">
+        <f>P130*N130</f>
+        <v>1188.0714</v>
+      </c>
+      <c r="R130" s="14"/>
     </row>
     <row r="131" spans="1:18" ht="24">
       <c r="A131" s="1"/>
-      <c r="B131" s="16">
-        <f>ROW(B131) - ROW($B$7)</f>
+      <c r="B131" s="17">
+        <f t="shared" si="0"/>
         <v>124</v>
       </c>
-      <c r="C131" s="22" t="s">
+      <c r="C131" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D131" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="E131" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="F131" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="G131" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="H131" s="14" t="s">
-        <v>461</v>
+      <c r="D131" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="E131" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="F131" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="G131" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="H131" s="20" t="s">
+        <v>463</v>
       </c>
       <c r="I131" s="43" t="s">
         <v>670</v>
       </c>
-      <c r="J131" s="14" t="s">
-        <v>579</v>
+      <c r="J131" s="20" t="s">
+        <v>578</v>
       </c>
       <c r="K131" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="L131" s="14">
+      <c r="L131" s="20">
         <v>1</v>
       </c>
       <c r="M131" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N131" s="14">
+      <c r="N131" s="20">
         <v>1002</v>
       </c>
       <c r="O131" s="50" t="s">
         <v>699</v>
       </c>
-      <c r="P131" s="15" t="s">
-        <v>865</v>
-      </c>
-      <c r="Q131" s="15">
-        <f>P131*N131</f>
-        <v>473.94599999999997</v>
-      </c>
-      <c r="R131" s="14"/>
+      <c r="P131" s="21" t="s">
+        <v>864</v>
+      </c>
+      <c r="Q131" s="21">
+        <f t="shared" ref="Q131" si="58">P131*N131</f>
+        <v>205.41</v>
+      </c>
+      <c r="R131" s="20"/>
     </row>
     <row r="132" spans="1:18" ht="24">
       <c r="A132" s="1"/>
-      <c r="B132" s="17">
+      <c r="B132" s="16">
+        <f>ROW(B132) - ROW($B$7)</f>
+        <v>125</v>
+      </c>
+      <c r="C132" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D132" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="E132" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="F132" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="G132" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="H132" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="I132" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J132" s="14" t="s">
+        <v>579</v>
+      </c>
+      <c r="K132" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="L132" s="14">
+        <v>1</v>
+      </c>
+      <c r="M132" s="14">
+        <f t="shared" si="32"/>
+        <v>1000</v>
+      </c>
+      <c r="N132" s="14">
+        <v>1002</v>
+      </c>
+      <c r="O132" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P132" s="15" t="s">
+        <v>865</v>
+      </c>
+      <c r="Q132" s="15">
+        <f>P132*N132</f>
+        <v>473.94599999999997</v>
+      </c>
+      <c r="R132" s="14"/>
+    </row>
+    <row r="133" spans="1:18" ht="24">
+      <c r="A133" s="1"/>
+      <c r="B133" s="17">
         <f t="shared" si="0"/>
-        <v>125</v>
-      </c>
-      <c r="C132" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C133" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D132" s="20" t="s">
+      <c r="D133" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="E132" s="20" t="s">
+      <c r="E133" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="F132" s="20" t="s">
+      <c r="F133" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="G132" s="20" t="s">
+      <c r="G133" s="20" t="s">
         <v>427</v>
       </c>
-      <c r="H132" s="20" t="s">
+      <c r="H133" s="20" t="s">
         <v>461</v>
       </c>
-      <c r="I132" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="J132" s="20" t="s">
+      <c r="I133" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J133" s="20" t="s">
         <v>580</v>
       </c>
-      <c r="K132" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="L132" s="20">
+      <c r="K133" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="L133" s="20">
         <v>1</v>
       </c>
-      <c r="M132" s="14">
-        <f t="shared" si="31"/>
+      <c r="M133" s="14">
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N132" s="20">
+      <c r="N133" s="20">
         <v>1002</v>
       </c>
-      <c r="O132" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P132" s="21" t="s">
+      <c r="O133" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P133" s="21" t="s">
         <v>866</v>
       </c>
-      <c r="Q132" s="21">
-        <f t="shared" ref="Q132" si="58">P132*N132</f>
+      <c r="Q133" s="21">
+        <f t="shared" ref="Q133" si="59">P133*N133</f>
         <v>2401.0925999999999</v>
       </c>
-      <c r="R132" s="20"/>
-    </row>
-    <row r="133" spans="1:18" ht="36">
-      <c r="A133" s="1"/>
-      <c r="B133" s="16">
-        <f>ROW(B133) - ROW($B$7)</f>
-        <v>126</v>
-      </c>
-      <c r="C133" s="22" t="s">
+      <c r="R133" s="20"/>
+    </row>
+    <row r="134" spans="1:18" ht="36">
+      <c r="A134" s="1"/>
+      <c r="B134" s="16">
+        <f>ROW(B134) - ROW($B$7)</f>
+        <v>127</v>
+      </c>
+      <c r="C134" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D133" s="14" t="s">
+      <c r="D134" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="E133" s="14" t="s">
+      <c r="E134" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="F133" s="20" t="s">
+      <c r="F134" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="G133" s="14" t="s">
+      <c r="G134" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="H133" s="14" t="s">
+      <c r="H134" s="14" t="s">
         <v>464</v>
       </c>
-      <c r="I133" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="J133" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="K133" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="L133" s="14">
+      <c r="I134" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J134" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="K134" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="L134" s="14">
         <v>1</v>
       </c>
-      <c r="M133" s="14">
-        <f t="shared" si="31"/>
+      <c r="M134" s="14">
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
-      <c r="N133" s="14">
+      <c r="N134" s="14">
         <v>1001</v>
       </c>
-      <c r="O133" s="50" t="s">
+      <c r="O134" s="50" t="s">
         <v>790</v>
       </c>
-      <c r="P133" s="15">
+      <c r="P134" s="15">
         <v>27.84</v>
       </c>
-      <c r="Q133" s="15">
-        <f>P133*N133</f>
+      <c r="Q134" s="15">
+        <f>P134*N134</f>
         <v>27867.84</v>
       </c>
-      <c r="R133" s="14"/>
-    </row>
-    <row r="134" spans="1:18" ht="24">
-      <c r="A134" s="1"/>
-      <c r="B134" s="17">
-        <f t="shared" si="0"/>
-        <v>127</v>
-      </c>
-      <c r="C134" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D134" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="E134" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="F134" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="G134" s="20" t="s">
-        <v>428</v>
-      </c>
-      <c r="H134" s="20" t="s">
-        <v>461</v>
-      </c>
-      <c r="I134" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="J134" s="20" t="s">
-        <v>581</v>
-      </c>
-      <c r="K134" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="L134" s="20">
-        <v>1</v>
-      </c>
-      <c r="M134" s="14">
-        <f t="shared" si="31"/>
-        <v>1000</v>
-      </c>
-      <c r="N134" s="20">
-        <v>1005</v>
-      </c>
-      <c r="O134" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P134" s="21" t="s">
-        <v>870</v>
-      </c>
-      <c r="Q134" s="21">
-        <f t="shared" ref="Q134:Q135" si="59">P134*N134</f>
-        <v>126.63</v>
-      </c>
-      <c r="R134" s="20"/>
-    </row>
-    <row r="135" spans="1:18" ht="36">
+      <c r="R134" s="14"/>
+    </row>
+    <row r="135" spans="1:18" ht="24">
       <c r="A135" s="1"/>
       <c r="B135" s="17">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
       <c r="C135" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D135" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E135" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F135" s="20" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G135" s="20" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H135" s="20" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="I135" s="43" t="s">
         <v>670</v>
       </c>
       <c r="J135" s="20" t="s">
-        <v>582</v>
-      </c>
-      <c r="K135" s="20" t="s">
-        <v>652</v>
+        <v>581</v>
+      </c>
+      <c r="K135" s="14" t="s">
+        <v>670</v>
       </c>
       <c r="L135" s="20">
         <v>1</v>
       </c>
       <c r="M135" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1000</v>
       </c>
       <c r="N135" s="20">
@@ -18607,183 +18619,183 @@
         <v>699</v>
       </c>
       <c r="P135" s="21" t="s">
+        <v>870</v>
+      </c>
+      <c r="Q135" s="21">
+        <f t="shared" ref="Q135:Q136" si="60">P135*N135</f>
+        <v>126.63</v>
+      </c>
+      <c r="R135" s="20"/>
+    </row>
+    <row r="136" spans="1:18" ht="36">
+      <c r="A136" s="1"/>
+      <c r="B136" s="17">
+        <f t="shared" si="0"/>
+        <v>129</v>
+      </c>
+      <c r="C136" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D136" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="E136" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="F136" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="G136" s="20" t="s">
+        <v>429</v>
+      </c>
+      <c r="H136" s="20" t="s">
+        <v>465</v>
+      </c>
+      <c r="I136" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J136" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="K136" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="L136" s="20">
+        <v>1</v>
+      </c>
+      <c r="M136" s="14">
+        <f t="shared" si="32"/>
+        <v>1000</v>
+      </c>
+      <c r="N136" s="20">
+        <v>1005</v>
+      </c>
+      <c r="O136" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P136" s="21" t="s">
         <v>871</v>
       </c>
-      <c r="Q135" s="21">
-        <f t="shared" si="59"/>
+      <c r="Q136" s="21">
+        <f t="shared" si="60"/>
         <v>91.957499999999996</v>
       </c>
-      <c r="R135" s="20"/>
-    </row>
-    <row r="136" spans="1:18">
-      <c r="A136" s="1"/>
-      <c r="B136" s="16">
-        <f>ROW(B136) - ROW($B$7)</f>
-        <v>129</v>
-      </c>
-      <c r="C136" s="22" t="s">
+      <c r="R136" s="20"/>
+    </row>
+    <row r="137" spans="1:18">
+      <c r="A137" s="1"/>
+      <c r="B137" s="16">
+        <f>ROW(B137) - ROW($B$7)</f>
+        <v>130</v>
+      </c>
+      <c r="C137" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D136" s="14" t="s">
+      <c r="D137" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E136" s="14" t="s">
+      <c r="E137" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="F136" s="14" t="s">
+      <c r="F137" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="G136" s="14" t="s">
+      <c r="G137" s="14" t="s">
         <v>430</v>
       </c>
-      <c r="H136" s="14" t="s">
+      <c r="H137" s="14" t="s">
         <v>466</v>
       </c>
-      <c r="I136" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="J136" s="14" t="s">
+      <c r="I137" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J137" s="14" t="s">
         <v>583</v>
       </c>
-      <c r="K136" s="14" t="s">
+      <c r="K137" s="14" t="s">
         <v>653</v>
       </c>
-      <c r="L136" s="14">
+      <c r="L137" s="14">
         <v>2</v>
       </c>
-      <c r="M136" s="14">
-        <f t="shared" si="31"/>
+      <c r="M137" s="14">
+        <f t="shared" si="32"/>
         <v>2000</v>
       </c>
-      <c r="N136" s="14">
+      <c r="N137" s="14">
         <v>2005</v>
       </c>
-      <c r="O136" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P136" s="15" t="s">
+      <c r="O137" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P137" s="15" t="s">
         <v>872</v>
       </c>
-      <c r="Q136" s="15">
-        <f>P136*N136</f>
+      <c r="Q137" s="15">
+        <f>P137*N137</f>
         <v>251.22649999999999</v>
       </c>
-      <c r="R136" s="14"/>
-    </row>
-    <row r="137" spans="1:18" ht="36">
-      <c r="A137" s="1"/>
-      <c r="B137" s="17">
-        <f t="shared" si="0"/>
-        <v>130</v>
-      </c>
-      <c r="C137" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D137" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="E137" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="F137" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="G137" s="20" t="s">
-        <v>431</v>
-      </c>
-      <c r="H137" s="20" t="s">
-        <v>467</v>
-      </c>
-      <c r="I137" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="J137" s="20" t="s">
-        <v>584</v>
-      </c>
-      <c r="K137" s="20" t="s">
-        <v>652</v>
-      </c>
-      <c r="L137" s="20">
-        <v>1</v>
-      </c>
-      <c r="M137" s="14">
-        <f t="shared" si="31"/>
-        <v>1000</v>
-      </c>
-      <c r="N137" s="20">
-        <v>1005</v>
-      </c>
-      <c r="O137" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P137" s="21" t="s">
-        <v>873</v>
-      </c>
-      <c r="Q137" s="21">
-        <f t="shared" ref="Q137:Q142" si="60">P137*N137</f>
-        <v>155.67450000000002</v>
-      </c>
-      <c r="R137" s="20"/>
-    </row>
-    <row r="138" spans="1:18" ht="24">
+      <c r="R137" s="14"/>
+    </row>
+    <row r="138" spans="1:18" ht="36">
       <c r="A138" s="1"/>
       <c r="B138" s="17">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-      <c r="C138" s="22" t="s">
-        <v>669</v>
-      </c>
-      <c r="D138" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="E138" s="43" t="s">
-        <v>671</v>
-      </c>
-      <c r="F138" s="14" t="s">
-        <v>672</v>
-      </c>
-      <c r="G138" s="43" t="s">
-        <v>673</v>
-      </c>
-      <c r="H138" s="14" t="s">
-        <v>674</v>
+      <c r="C138" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D138" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="E138" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="F138" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="G138" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="H138" s="20" t="s">
+        <v>467</v>
       </c>
       <c r="I138" s="43" t="s">
         <v>670</v>
       </c>
       <c r="J138" s="20" t="s">
-        <v>691</v>
-      </c>
-      <c r="K138" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="L138" s="14">
-        <v>2</v>
+        <v>584</v>
+      </c>
+      <c r="K138" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="L138" s="20">
+        <v>1</v>
       </c>
       <c r="M138" s="14">
-        <f t="shared" ref="M138:M142" si="61">L138*1000</f>
-        <v>2000</v>
+        <f t="shared" si="32"/>
+        <v>1000</v>
       </c>
       <c r="N138" s="20">
-        <v>2002</v>
+        <v>1005</v>
       </c>
       <c r="O138" s="50" t="s">
         <v>699</v>
       </c>
       <c r="P138" s="21" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="Q138" s="21">
-        <f t="shared" si="60"/>
-        <v>853.45260000000007</v>
+        <f t="shared" ref="Q138:Q143" si="61">P138*N138</f>
+        <v>155.67450000000002</v>
       </c>
       <c r="R138" s="20"/>
     </row>
-    <row r="139" spans="1:18" ht="89.25">
+    <row r="139" spans="1:18" ht="24">
       <c r="A139" s="1"/>
       <c r="B139" s="17">
-        <f t="shared" ref="B139:B143" si="62">ROW(B139) - ROW($B$7)</f>
+        <f t="shared" si="0"/>
         <v>132</v>
       </c>
       <c r="C139" s="22" t="s">
@@ -18793,54 +18805,52 @@
         <v>670</v>
       </c>
       <c r="E139" s="43" t="s">
-        <v>675</v>
-      </c>
-      <c r="F139" s="20" t="s">
+        <v>671</v>
+      </c>
+      <c r="F139" s="14" t="s">
         <v>672</v>
       </c>
       <c r="G139" s="43" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="H139" s="14" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="I139" s="43" t="s">
         <v>670</v>
       </c>
       <c r="J139" s="20" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="K139" s="43" t="s">
         <v>670</v>
       </c>
       <c r="L139" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M139" s="14">
+        <f t="shared" ref="M139:M143" si="62">L139*1000</f>
+        <v>2000</v>
+      </c>
+      <c r="N139" s="20">
+        <v>2002</v>
+      </c>
+      <c r="O139" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P139" s="21" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q139" s="21">
         <f t="shared" si="61"/>
-        <v>1000</v>
-      </c>
-      <c r="N139" s="20">
-        <v>1001</v>
-      </c>
-      <c r="O139" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P139" s="21" t="s">
-        <v>778</v>
-      </c>
-      <c r="Q139" s="21">
-        <f t="shared" si="60"/>
-        <v>5639.634</v>
-      </c>
-      <c r="R139" s="45" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="140" spans="1:18" ht="36">
+        <v>853.45260000000007</v>
+      </c>
+      <c r="R139" s="20"/>
+    </row>
+    <row r="140" spans="1:18" ht="89.25">
       <c r="A140" s="1"/>
       <c r="B140" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" ref="B140:B144" si="63">ROW(B140) - ROW($B$7)</f>
         <v>133</v>
       </c>
       <c r="C140" s="22" t="s">
@@ -18849,53 +18859,55 @@
       <c r="D140" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="E140" s="44" t="s">
-        <v>678</v>
+      <c r="E140" s="43" t="s">
+        <v>675</v>
       </c>
       <c r="F140" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="G140" s="44" t="s">
-        <v>679</v>
-      </c>
-      <c r="H140" s="20" t="s">
-        <v>680</v>
+      <c r="G140" s="43" t="s">
+        <v>676</v>
+      </c>
+      <c r="H140" s="14" t="s">
+        <v>677</v>
       </c>
       <c r="I140" s="43" t="s">
         <v>670</v>
       </c>
       <c r="J140" s="20" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K140" s="43" t="s">
         <v>670</v>
       </c>
-      <c r="L140" s="20">
+      <c r="L140" s="14">
         <v>1</v>
       </c>
       <c r="M140" s="14">
+        <f t="shared" si="62"/>
+        <v>1000</v>
+      </c>
+      <c r="N140" s="20">
+        <v>1001</v>
+      </c>
+      <c r="O140" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P140" s="21" t="s">
+        <v>778</v>
+      </c>
+      <c r="Q140" s="21">
         <f t="shared" si="61"/>
-        <v>1000</v>
-      </c>
-      <c r="N140" s="20">
-        <v>1005</v>
-      </c>
-      <c r="O140" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P140" s="21" t="s">
-        <v>875</v>
-      </c>
-      <c r="Q140" s="21">
-        <f t="shared" si="60"/>
-        <v>75.777000000000001</v>
-      </c>
-      <c r="R140" s="20"/>
-    </row>
-    <row r="141" spans="1:18" ht="24">
+        <v>5639.634</v>
+      </c>
+      <c r="R140" s="45" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" ht="36">
       <c r="A141" s="1"/>
       <c r="B141" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>134</v>
       </c>
       <c r="C141" s="22" t="s">
@@ -18905,52 +18917,52 @@
         <v>670</v>
       </c>
       <c r="E141" s="44" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="F141" s="20" t="s">
         <v>672</v>
       </c>
       <c r="G141" s="44" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="H141" s="20" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="I141" s="43" t="s">
         <v>670</v>
       </c>
       <c r="J141" s="20" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="K141" s="43" t="s">
         <v>670</v>
       </c>
       <c r="L141" s="20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M141" s="14">
+        <f t="shared" si="62"/>
+        <v>1000</v>
+      </c>
+      <c r="N141" s="20">
+        <v>1005</v>
+      </c>
+      <c r="O141" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P141" s="21" t="s">
+        <v>875</v>
+      </c>
+      <c r="Q141" s="21">
         <f t="shared" si="61"/>
-        <v>2000</v>
-      </c>
-      <c r="N141" s="20">
-        <v>2002</v>
-      </c>
-      <c r="O141" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="P141" s="21" t="s">
-        <v>876</v>
-      </c>
-      <c r="Q141" s="21">
-        <f t="shared" si="60"/>
-        <v>2088.8868000000002</v>
+        <v>75.777000000000001</v>
       </c>
       <c r="R141" s="20"/>
     </row>
-    <row r="142" spans="1:18" ht="36">
+    <row r="142" spans="1:18" ht="24">
       <c r="A142" s="1"/>
       <c r="B142" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>135</v>
       </c>
       <c r="C142" s="22" t="s">
@@ -18960,52 +18972,52 @@
         <v>670</v>
       </c>
       <c r="E142" s="44" t="s">
-        <v>878</v>
+        <v>681</v>
       </c>
       <c r="F142" s="20" t="s">
         <v>672</v>
       </c>
       <c r="G142" s="44" t="s">
-        <v>879</v>
+        <v>682</v>
       </c>
       <c r="H142" s="20" t="s">
-        <v>880</v>
+        <v>683</v>
       </c>
       <c r="I142" s="43" t="s">
         <v>670</v>
       </c>
       <c r="J142" s="20" t="s">
-        <v>670</v>
-      </c>
-      <c r="K142" s="44" t="s">
+        <v>694</v>
+      </c>
+      <c r="K142" s="43" t="s">
         <v>670</v>
       </c>
       <c r="L142" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M142" s="14">
+        <f t="shared" si="62"/>
+        <v>2000</v>
+      </c>
+      <c r="N142" s="20">
+        <v>2002</v>
+      </c>
+      <c r="O142" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="P142" s="21" t="s">
+        <v>876</v>
+      </c>
+      <c r="Q142" s="21">
         <f t="shared" si="61"/>
-        <v>1000</v>
-      </c>
-      <c r="N142" s="20">
-        <v>1001</v>
-      </c>
-      <c r="O142" s="50" t="s">
-        <v>881</v>
-      </c>
-      <c r="P142" s="21">
-        <v>2.4</v>
-      </c>
-      <c r="Q142" s="21">
-        <f t="shared" si="60"/>
-        <v>2402.4</v>
+        <v>2088.8868000000002</v>
       </c>
       <c r="R142" s="20"/>
     </row>
-    <row r="143" spans="1:18" ht="30.75" thickBot="1">
+    <row r="143" spans="1:18" ht="36">
       <c r="A143" s="1"/>
       <c r="B143" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>136</v>
       </c>
       <c r="C143" s="22" t="s">
@@ -19015,16 +19027,16 @@
         <v>670</v>
       </c>
       <c r="E143" s="44" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="F143" s="20" t="s">
         <v>672</v>
       </c>
       <c r="G143" s="44" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="H143" s="20" t="s">
-        <v>887</v>
+        <v>880</v>
       </c>
       <c r="I143" s="43" t="s">
         <v>670</v>
@@ -19039,7 +19051,7 @@
         <v>1</v>
       </c>
       <c r="M143" s="14">
-        <f t="shared" ref="M143" si="63">L143*1000</f>
+        <f t="shared" si="62"/>
         <v>1000</v>
       </c>
       <c r="N143" s="20">
@@ -19049,47 +19061,102 @@
         <v>881</v>
       </c>
       <c r="P143" s="21">
+        <v>2.4</v>
+      </c>
+      <c r="Q143" s="21">
+        <f t="shared" si="61"/>
+        <v>2402.4</v>
+      </c>
+      <c r="R143" s="20"/>
+    </row>
+    <row r="144" spans="1:18" ht="30.75" thickBot="1">
+      <c r="A144" s="1"/>
+      <c r="B144" s="17">
+        <f t="shared" si="63"/>
+        <v>137</v>
+      </c>
+      <c r="C144" s="22" t="s">
+        <v>669</v>
+      </c>
+      <c r="D144" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="E144" s="44" t="s">
+        <v>885</v>
+      </c>
+      <c r="F144" s="20" t="s">
+        <v>672</v>
+      </c>
+      <c r="G144" s="44" t="s">
+        <v>886</v>
+      </c>
+      <c r="H144" s="20" t="s">
+        <v>887</v>
+      </c>
+      <c r="I144" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="J144" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="K144" s="44" t="s">
+        <v>670</v>
+      </c>
+      <c r="L144" s="20">
+        <v>1</v>
+      </c>
+      <c r="M144" s="14">
+        <f t="shared" ref="M144" si="64">L144*1000</f>
+        <v>1000</v>
+      </c>
+      <c r="N144" s="20">
+        <v>1001</v>
+      </c>
+      <c r="O144" s="50" t="s">
+        <v>881</v>
+      </c>
+      <c r="P144" s="21">
         <v>8.8699999999999992</v>
       </c>
-      <c r="Q143" s="21">
-        <f t="shared" ref="Q143" si="64">P143*N143</f>
+      <c r="Q144" s="21">
+        <f t="shared" ref="Q144" si="65">P144*N144</f>
         <v>8878.869999999999</v>
       </c>
-      <c r="R143" s="20"/>
-    </row>
-    <row r="144" spans="1:18" ht="19.5" thickBot="1">
-      <c r="A144" s="1"/>
-      <c r="B144" s="10"/>
-      <c r="C144" s="10"/>
-      <c r="N144" s="54" t="s">
-        <v>3</v>
-      </c>
-      <c r="O144" s="55"/>
-      <c r="P144" s="55"/>
-      <c r="Q144" s="18">
-        <f>SUM(Q8:Q143)</f>
-        <v>65247.1201</v>
-      </c>
+      <c r="R144" s="20"/>
     </row>
     <row r="145" spans="1:17" ht="19.5" thickBot="1">
       <c r="A145" s="1"/>
       <c r="B145" s="10"/>
       <c r="C145" s="10"/>
       <c r="N145" s="54" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O145" s="55"/>
       <c r="P145" s="55"/>
-      <c r="Q145" s="19">
-        <f>Q144/1000</f>
-        <v>65.247120100000004</v>
+      <c r="Q145" s="18">
+        <f>SUM(Q8:Q144)</f>
+        <v>65267.92809999999</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" ht="19.5" thickBot="1">
+      <c r="A146" s="1"/>
+      <c r="B146" s="10"/>
+      <c r="C146" s="10"/>
+      <c r="N146" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="O146" s="55"/>
+      <c r="P146" s="55"/>
+      <c r="Q146" s="19">
+        <f>Q145/1000</f>
+        <v>65.267928099999992</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N144:P144"/>
     <mergeCell ref="N145:P145"/>
+    <mergeCell ref="N146:P146"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O8" r:id="rId1"/>
@@ -19121,111 +19188,112 @@
     <hyperlink ref="O35" r:id="rId27"/>
     <hyperlink ref="O36" r:id="rId28"/>
     <hyperlink ref="O37" r:id="rId29" display="LCSC"/>
-    <hyperlink ref="O40" r:id="rId30"/>
-    <hyperlink ref="O41" r:id="rId31" display="LCSC"/>
-    <hyperlink ref="O42" r:id="rId32"/>
-    <hyperlink ref="O44" r:id="rId33"/>
-    <hyperlink ref="O45" r:id="rId34"/>
-    <hyperlink ref="O46" r:id="rId35"/>
-    <hyperlink ref="O47" r:id="rId36"/>
-    <hyperlink ref="O48" r:id="rId37" display="LCSC"/>
-    <hyperlink ref="O49" r:id="rId38"/>
-    <hyperlink ref="O50" r:id="rId39"/>
-    <hyperlink ref="O51" r:id="rId40"/>
-    <hyperlink ref="O52" r:id="rId41"/>
-    <hyperlink ref="O53" r:id="rId42"/>
-    <hyperlink ref="O54" r:id="rId43" display="LCSC"/>
-    <hyperlink ref="O56" r:id="rId44"/>
-    <hyperlink ref="O57" r:id="rId45"/>
-    <hyperlink ref="O58" r:id="rId46"/>
-    <hyperlink ref="O59" r:id="rId47"/>
-    <hyperlink ref="O60" r:id="rId48"/>
-    <hyperlink ref="O61" r:id="rId49"/>
-    <hyperlink ref="O62" r:id="rId50"/>
-    <hyperlink ref="O63" r:id="rId51"/>
-    <hyperlink ref="O64" r:id="rId52"/>
-    <hyperlink ref="O65" r:id="rId53"/>
-    <hyperlink ref="O66" r:id="rId54"/>
-    <hyperlink ref="O67" r:id="rId55"/>
-    <hyperlink ref="O68" r:id="rId56"/>
-    <hyperlink ref="O69" r:id="rId57"/>
-    <hyperlink ref="O70" r:id="rId58"/>
-    <hyperlink ref="O71" r:id="rId59"/>
-    <hyperlink ref="O72" r:id="rId60"/>
-    <hyperlink ref="O73" r:id="rId61"/>
-    <hyperlink ref="O74" r:id="rId62"/>
-    <hyperlink ref="O75" r:id="rId63"/>
-    <hyperlink ref="O76" r:id="rId64"/>
-    <hyperlink ref="O77" r:id="rId65"/>
-    <hyperlink ref="O78" r:id="rId66"/>
-    <hyperlink ref="O79" r:id="rId67"/>
-    <hyperlink ref="O80" r:id="rId68"/>
-    <hyperlink ref="O81" r:id="rId69"/>
-    <hyperlink ref="O82" r:id="rId70"/>
-    <hyperlink ref="O83" r:id="rId71"/>
-    <hyperlink ref="O84" r:id="rId72"/>
-    <hyperlink ref="O85" r:id="rId73"/>
-    <hyperlink ref="O86" r:id="rId74"/>
-    <hyperlink ref="O87" r:id="rId75"/>
-    <hyperlink ref="O88" r:id="rId76"/>
-    <hyperlink ref="O89" r:id="rId77"/>
-    <hyperlink ref="O90" r:id="rId78"/>
-    <hyperlink ref="O91" r:id="rId79"/>
-    <hyperlink ref="O92" r:id="rId80"/>
-    <hyperlink ref="O93" r:id="rId81"/>
-    <hyperlink ref="O94" r:id="rId82"/>
-    <hyperlink ref="O95" r:id="rId83"/>
-    <hyperlink ref="O96" r:id="rId84"/>
-    <hyperlink ref="O97" r:id="rId85"/>
-    <hyperlink ref="O98" r:id="rId86"/>
-    <hyperlink ref="O99" r:id="rId87"/>
-    <hyperlink ref="O100" r:id="rId88"/>
-    <hyperlink ref="O101" r:id="rId89"/>
-    <hyperlink ref="O102" r:id="rId90"/>
-    <hyperlink ref="O103" r:id="rId91" display="LCSC"/>
-    <hyperlink ref="O106" r:id="rId92"/>
-    <hyperlink ref="O107" r:id="rId93"/>
-    <hyperlink ref="O108" r:id="rId94"/>
-    <hyperlink ref="O109" r:id="rId95" display="LCSC"/>
-    <hyperlink ref="O111" r:id="rId96" display="LCSC"/>
-    <hyperlink ref="O113" r:id="rId97"/>
-    <hyperlink ref="O114" r:id="rId98" display="LCSC"/>
-    <hyperlink ref="O115" r:id="rId99" display="url"/>
-    <hyperlink ref="O117" r:id="rId100"/>
-    <hyperlink ref="O118" r:id="rId101"/>
-    <hyperlink ref="O119" r:id="rId102"/>
-    <hyperlink ref="O120" r:id="rId103"/>
-    <hyperlink ref="O121" r:id="rId104"/>
-    <hyperlink ref="O122" r:id="rId105"/>
-    <hyperlink ref="O123" r:id="rId106"/>
-    <hyperlink ref="O124" r:id="rId107"/>
-    <hyperlink ref="O125" r:id="rId108"/>
-    <hyperlink ref="O126" r:id="rId109"/>
-    <hyperlink ref="O127" r:id="rId110"/>
-    <hyperlink ref="O128" r:id="rId111"/>
-    <hyperlink ref="O129" r:id="rId112"/>
-    <hyperlink ref="O130" r:id="rId113"/>
-    <hyperlink ref="O131" r:id="rId114"/>
-    <hyperlink ref="O43" r:id="rId115"/>
-    <hyperlink ref="O134" r:id="rId116"/>
-    <hyperlink ref="O135" r:id="rId117"/>
-    <hyperlink ref="O136" r:id="rId118"/>
-    <hyperlink ref="O137" r:id="rId119"/>
-    <hyperlink ref="O138" r:id="rId120"/>
-    <hyperlink ref="O139" r:id="rId121"/>
-    <hyperlink ref="O140" r:id="rId122"/>
-    <hyperlink ref="O141" r:id="rId123"/>
-    <hyperlink ref="O132" r:id="rId124"/>
+    <hyperlink ref="O41" r:id="rId30"/>
+    <hyperlink ref="O42" r:id="rId31" display="LCSC"/>
+    <hyperlink ref="O43" r:id="rId32"/>
+    <hyperlink ref="O45" r:id="rId33"/>
+    <hyperlink ref="O46" r:id="rId34"/>
+    <hyperlink ref="O47" r:id="rId35"/>
+    <hyperlink ref="O48" r:id="rId36"/>
+    <hyperlink ref="O49" r:id="rId37" display="LCSC"/>
+    <hyperlink ref="O50" r:id="rId38"/>
+    <hyperlink ref="O51" r:id="rId39"/>
+    <hyperlink ref="O52" r:id="rId40"/>
+    <hyperlink ref="O53" r:id="rId41"/>
+    <hyperlink ref="O54" r:id="rId42"/>
+    <hyperlink ref="O55" r:id="rId43" display="LCSC"/>
+    <hyperlink ref="O57" r:id="rId44"/>
+    <hyperlink ref="O58" r:id="rId45"/>
+    <hyperlink ref="O59" r:id="rId46"/>
+    <hyperlink ref="O60" r:id="rId47"/>
+    <hyperlink ref="O61" r:id="rId48"/>
+    <hyperlink ref="O62" r:id="rId49"/>
+    <hyperlink ref="O63" r:id="rId50"/>
+    <hyperlink ref="O64" r:id="rId51"/>
+    <hyperlink ref="O65" r:id="rId52"/>
+    <hyperlink ref="O66" r:id="rId53"/>
+    <hyperlink ref="O67" r:id="rId54"/>
+    <hyperlink ref="O68" r:id="rId55"/>
+    <hyperlink ref="O69" r:id="rId56"/>
+    <hyperlink ref="O70" r:id="rId57"/>
+    <hyperlink ref="O71" r:id="rId58"/>
+    <hyperlink ref="O72" r:id="rId59"/>
+    <hyperlink ref="O73" r:id="rId60"/>
+    <hyperlink ref="O74" r:id="rId61"/>
+    <hyperlink ref="O75" r:id="rId62"/>
+    <hyperlink ref="O76" r:id="rId63"/>
+    <hyperlink ref="O77" r:id="rId64"/>
+    <hyperlink ref="O78" r:id="rId65"/>
+    <hyperlink ref="O79" r:id="rId66"/>
+    <hyperlink ref="O80" r:id="rId67"/>
+    <hyperlink ref="O81" r:id="rId68"/>
+    <hyperlink ref="O82" r:id="rId69"/>
+    <hyperlink ref="O83" r:id="rId70"/>
+    <hyperlink ref="O84" r:id="rId71"/>
+    <hyperlink ref="O85" r:id="rId72"/>
+    <hyperlink ref="O86" r:id="rId73"/>
+    <hyperlink ref="O87" r:id="rId74"/>
+    <hyperlink ref="O88" r:id="rId75"/>
+    <hyperlink ref="O89" r:id="rId76"/>
+    <hyperlink ref="O90" r:id="rId77"/>
+    <hyperlink ref="O91" r:id="rId78"/>
+    <hyperlink ref="O92" r:id="rId79"/>
+    <hyperlink ref="O93" r:id="rId80"/>
+    <hyperlink ref="O94" r:id="rId81"/>
+    <hyperlink ref="O95" r:id="rId82"/>
+    <hyperlink ref="O96" r:id="rId83"/>
+    <hyperlink ref="O97" r:id="rId84"/>
+    <hyperlink ref="O98" r:id="rId85"/>
+    <hyperlink ref="O99" r:id="rId86"/>
+    <hyperlink ref="O100" r:id="rId87"/>
+    <hyperlink ref="O101" r:id="rId88"/>
+    <hyperlink ref="O102" r:id="rId89"/>
+    <hyperlink ref="O103" r:id="rId90"/>
+    <hyperlink ref="O104" r:id="rId91" display="LCSC"/>
+    <hyperlink ref="O107" r:id="rId92"/>
+    <hyperlink ref="O108" r:id="rId93"/>
+    <hyperlink ref="O109" r:id="rId94"/>
+    <hyperlink ref="O110" r:id="rId95" display="LCSC"/>
+    <hyperlink ref="O112" r:id="rId96" display="LCSC"/>
+    <hyperlink ref="O114" r:id="rId97"/>
+    <hyperlink ref="O115" r:id="rId98" display="LCSC"/>
+    <hyperlink ref="O116" r:id="rId99" display="url"/>
+    <hyperlink ref="O118" r:id="rId100"/>
+    <hyperlink ref="O119" r:id="rId101"/>
+    <hyperlink ref="O120" r:id="rId102"/>
+    <hyperlink ref="O121" r:id="rId103"/>
+    <hyperlink ref="O122" r:id="rId104"/>
+    <hyperlink ref="O123" r:id="rId105"/>
+    <hyperlink ref="O124" r:id="rId106"/>
+    <hyperlink ref="O125" r:id="rId107"/>
+    <hyperlink ref="O126" r:id="rId108"/>
+    <hyperlink ref="O127" r:id="rId109"/>
+    <hyperlink ref="O128" r:id="rId110"/>
+    <hyperlink ref="O129" r:id="rId111"/>
+    <hyperlink ref="O130" r:id="rId112"/>
+    <hyperlink ref="O131" r:id="rId113"/>
+    <hyperlink ref="O132" r:id="rId114"/>
+    <hyperlink ref="O44" r:id="rId115"/>
+    <hyperlink ref="O135" r:id="rId116"/>
+    <hyperlink ref="O136" r:id="rId117"/>
+    <hyperlink ref="O137" r:id="rId118"/>
+    <hyperlink ref="O138" r:id="rId119"/>
+    <hyperlink ref="O139" r:id="rId120"/>
+    <hyperlink ref="O140" r:id="rId121"/>
+    <hyperlink ref="O141" r:id="rId122"/>
+    <hyperlink ref="O142" r:id="rId123"/>
+    <hyperlink ref="O133" r:id="rId124"/>
     <hyperlink ref="O12" r:id="rId125"/>
-    <hyperlink ref="O55" r:id="rId126"/>
-    <hyperlink ref="O105" r:id="rId127"/>
-    <hyperlink ref="O110" r:id="rId128"/>
-    <hyperlink ref="O112" r:id="rId129"/>
-    <hyperlink ref="O133" r:id="rId130"/>
-    <hyperlink ref="O39" r:id="rId131"/>
-    <hyperlink ref="O116" r:id="rId132"/>
-    <hyperlink ref="O142" r:id="rId133" location="nav-specification"/>
-    <hyperlink ref="O143" r:id="rId134" location="nav-specification"/>
+    <hyperlink ref="O56" r:id="rId126"/>
+    <hyperlink ref="O106" r:id="rId127"/>
+    <hyperlink ref="O111" r:id="rId128"/>
+    <hyperlink ref="O113" r:id="rId129"/>
+    <hyperlink ref="O134" r:id="rId130"/>
+    <hyperlink ref="O40" r:id="rId131"/>
+    <hyperlink ref="O117" r:id="rId132"/>
+    <hyperlink ref="O143" r:id="rId133" location="nav-specification"/>
+    <hyperlink ref="O144" r:id="rId134" location="nav-specification"/>
+    <hyperlink ref="O39" r:id="rId135"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
